--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E05B8F56-15BC-3B46-AEF1-F2FAB66D4ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1D701F-00E1-FC40-BFA0-DB41C9C233F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -2586,12 +2586,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF356854"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2696,7 +2698,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2790,7 +2792,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
@@ -2801,27 +2802,6 @@
     <cellStyle name="Percent 2" xfId="4" xr:uid="{E6DE421D-B06A-DB4D-BCE7-D696BB42B3F4}"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2844,6 +2824,12 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF1F3A2E"/>
       </font>
@@ -2853,7 +2839,37 @@
       <font>
         <color rgb="FF1F3A2E"/>
       </font>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2878,6 +2894,97 @@
         <color rgb="FF1F3A2E"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F3A2E"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2937,119 +3044,13 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF1F3A2E"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Light and Airy" count="4" xr9:uid="{9857ACD9-B079-C44A-A030-69F7726DB419}">
-      <tableStyleElement type="wholeTable" dxfId="15"/>
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="totalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="wholeTable" dxfId="31"/>
+      <tableStyleElement type="headerRow" dxfId="30"/>
+      <tableStyleElement type="totalRow" dxfId="29"/>
+      <tableStyleElement type="firstRowStripe" dxfId="28"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3091,7 +3092,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V94" totalsRowCount="1" headerRowDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V94" totalsRowCount="1" headerRowDxfId="26">
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First"/>
@@ -3099,8 +3100,8 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="average" totalsRowDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="average" totalsRowDxfId="24"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2"/>
@@ -3121,25 +3122,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="20" dataDxfId="18" totalsRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="25"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3149,7 +3150,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3160,7 +3161,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3172,7 +3173,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3408,9 +3409,8 @@
   <cols>
     <col min="1" max="3" width="22.6640625" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="15" width="10.1640625" customWidth="1"/>
-    <col min="16" max="16" width="10.1640625" customWidth="1" collapsed="1"/>
-    <col min="17" max="22" width="10.1640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="22" width="10.1640625" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="16" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10161,7 +10161,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:O93">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Q2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10189,10 +10189,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="3" max="3" width="37.6640625" customWidth="1"/>
-    <col min="4" max="4" width="37.6640625" style="29" customWidth="1"/>
+    <col min="3" max="4" width="37.6640625" customWidth="1"/>
     <col min="5" max="5" width="10.1640625" customWidth="1"/>
-    <col min="6" max="9" width="25.1640625" style="29" customWidth="1"/>
+    <col min="6" max="9" width="25.1640625" customWidth="1"/>
     <col min="10" max="10" width="19.1640625" customWidth="1"/>
     <col min="11" max="11" width="17.83203125" customWidth="1"/>
     <col min="12" max="12" width="17.6640625" customWidth="1"/>
@@ -10601,7 +10600,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11327,7 +11326,7 @@
       <c r="C1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>840</v>
       </c>
     </row>

--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD16CD88-69E2-7442-ABB5-94B9E26D02D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034BA313-8A5F-0646-A667-B76D8BE8D570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -3184,7 +3184,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3252,12 +3252,6 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3333,26 +3327,166 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{D605B4E0-7730-4D43-A011-6A0EF9292E1A}"/>
     <cellStyle name="Percent 2" xfId="4" xr:uid="{E6DE421D-B06A-DB4D-BCE7-D696BB42B3F4}"/>
   </cellStyles>
-  <dxfs count="77">
+  <dxfs count="76">
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F3A2E"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF1F3A2E"/>
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3599,174 +3733,24 @@
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1F3A2E"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color rgb="FF1F3A2E"/>
+        <color theme="1"/>
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -3829,10 +3813,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Light and Airy" count="4" xr9:uid="{9857ACD9-B079-C44A-A030-69F7726DB419}">
-      <tableStyleElement type="wholeTable" dxfId="76"/>
-      <tableStyleElement type="headerRow" dxfId="75"/>
-      <tableStyleElement type="totalRow" dxfId="74"/>
-      <tableStyleElement type="firstRowStripe" dxfId="73"/>
+      <tableStyleElement type="wholeTable" dxfId="75"/>
+      <tableStyleElement type="headerRow" dxfId="74"/>
+      <tableStyleElement type="totalRow" dxfId="73"/>
+      <tableStyleElement type="firstRowStripe" dxfId="72"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3875,57 +3859,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V121" totalsRowCount="1" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V121" totalsRowCount="1" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="36" totalsRowDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="54" totalsRowDxfId="53">
       <totalsRowFormula>AVERAGE(Scores[MC])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="6" totalsRowDxfId="5"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="26" totalsRowDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="57"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="55"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="54"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="53"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3935,7 +3919,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3946,7 +3930,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3958,7 +3942,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="50">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4192,20 +4176,20 @@
   <dimension ref="A1:V121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="3" width="22.6640625" style="32" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="34" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" style="39" customWidth="1"/>
-    <col min="7" max="7" width="10.1640625" style="40" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="34" customWidth="1"/>
-    <col min="9" max="9" width="10.1640625" style="37" customWidth="1"/>
-    <col min="10" max="15" width="10.1640625" style="34" customWidth="1"/>
-    <col min="16" max="16" width="10.1640625" style="38" customWidth="1"/>
-    <col min="17" max="22" width="10.1640625" style="34" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="16384" width="12.6640625" style="32"/>
+    <col min="1" max="3" width="22.6640625" style="30" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" style="37" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" style="38" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" style="32" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" style="35" customWidth="1"/>
+    <col min="10" max="15" width="10.1640625" style="32" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" style="36" customWidth="1"/>
+    <col min="17" max="22" width="10.1640625" style="32" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="16384" width="12.6640625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="31" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:22" s="29" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="15" t="s">
         <v>9</v>
       </c>
@@ -4224,16 +4208,16 @@
       <c r="F1" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="10" t="s">
         <v>21</v>
       </c>
       <c r="K1" s="10" t="s">
@@ -4251,10 +4235,10 @@
       <c r="O1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="Q1" s="10" t="s">
         <v>60</v>
       </c>
       <c r="R1" s="10" t="s">
@@ -4278,11 +4262,11 @@
         <v>70</v>
       </c>
       <c r="B2" s="3" t="str">
-        <f t="shared" ref="B2:B93" si="0">LEFT(A2,FIND(" ",A2))</f>
+        <f t="shared" ref="B2:B46" si="0">LEFT(A2,FIND(" ",A2))</f>
         <v xml:space="preserve">SEAN </v>
       </c>
       <c r="C2" s="3" t="str">
-        <f t="shared" ref="C2:C93" si="1">RIGHT(A2,LEN(A2)-LEN(B2))</f>
+        <f t="shared" ref="C2:C46" si="1">RIGHT(A2,LEN(A2)-LEN(B2))</f>
         <v>ALEXIS</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -4294,15 +4278,15 @@
       <c r="F2" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="24">
-        <f t="shared" ref="H2:H93" si="2">SUM(Q2:V2)</f>
-        <v>4</v>
-      </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="24">
+      <c r="G2" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <f t="shared" ref="H2:H46" si="2">SUM(Q2:V2)</f>
+        <v>5</v>
+      </c>
+      <c r="I2" s="26"/>
+      <c r="J2" s="1">
         <v>3</v>
       </c>
       <c r="K2" s="1">
@@ -4320,8 +4304,8 @@
       <c r="O2" s="1">
         <v>2</v>
       </c>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="24">
+      <c r="P2" s="28"/>
+      <c r="Q2" s="1">
         <f>IF(J2=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -4339,7 +4323,7 @@
       </c>
       <c r="U2" s="1">
         <f>IF(N2=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="1">
         <f>IF(O2=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -4367,15 +4351,15 @@
       <c r="F3" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G3" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="24">
+      <c r="G3" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I3" s="28"/>
-      <c r="J3" s="24">
+        <v>4</v>
+      </c>
+      <c r="I3" s="26"/>
+      <c r="J3" s="1">
         <v>3</v>
       </c>
       <c r="K3" s="1">
@@ -4393,8 +4377,8 @@
       <c r="O3" s="1">
         <v>3</v>
       </c>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="24">
+      <c r="P3" s="28"/>
+      <c r="Q3" s="1">
         <f>IF(J3=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -4412,7 +4396,7 @@
       </c>
       <c r="U3" s="1">
         <f>IF(N3=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="1">
         <f>IF(O3=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -4440,15 +4424,15 @@
       <c r="F4" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="24">
+      <c r="G4" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="I4" s="28"/>
-      <c r="J4" s="24">
+      <c r="I4" s="26"/>
+      <c r="J4" s="1">
         <v>3</v>
       </c>
       <c r="K4" s="1">
@@ -4466,8 +4450,8 @@
       <c r="O4" s="1">
         <v>1</v>
       </c>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="24">
+      <c r="P4" s="28"/>
+      <c r="Q4" s="1">
         <f>IF(J4=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -4513,15 +4497,15 @@
       <c r="F5" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="24">
+      <c r="G5" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I5" s="28"/>
-      <c r="J5" s="24">
+        <v>6</v>
+      </c>
+      <c r="I5" s="26"/>
+      <c r="J5" s="1">
         <v>3</v>
       </c>
       <c r="K5" s="1">
@@ -4539,8 +4523,8 @@
       <c r="O5" s="1">
         <v>2</v>
       </c>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="24">
+      <c r="P5" s="28"/>
+      <c r="Q5" s="1">
         <f>IF(J5=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -4558,7 +4542,7 @@
       </c>
       <c r="U5" s="1">
         <f>IF(N5=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="1">
         <f>IF(O5=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -4586,15 +4570,15 @@
       <c r="F6" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" s="24">
+      <c r="G6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="24">
+      <c r="I6" s="26"/>
+      <c r="J6" s="1">
         <v>3</v>
       </c>
       <c r="K6" s="1">
@@ -4612,8 +4596,8 @@
       <c r="O6" s="1">
         <v>2</v>
       </c>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="24">
+      <c r="P6" s="28"/>
+      <c r="Q6" s="1">
         <f>IF(J6=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -4659,15 +4643,15 @@
       <c r="F7" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G7" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="24">
+      <c r="G7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I7" s="28"/>
-      <c r="J7" s="24">
+        <v>2</v>
+      </c>
+      <c r="I7" s="26"/>
+      <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="1">
@@ -4685,8 +4669,8 @@
       <c r="O7" s="1">
         <v>3</v>
       </c>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="24">
+      <c r="P7" s="28"/>
+      <c r="Q7" s="1">
         <f>IF(J7=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -4704,7 +4688,7 @@
       </c>
       <c r="U7" s="1">
         <f>IF(N7=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="1">
         <f>IF(O7=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -4732,15 +4716,15 @@
       <c r="F8" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G8" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="24">
+      <c r="G8" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="I8" s="28"/>
-      <c r="J8" s="24">
+        <v>3</v>
+      </c>
+      <c r="I8" s="26"/>
+      <c r="J8" s="1">
         <v>1</v>
       </c>
       <c r="K8" s="1">
@@ -4758,8 +4742,8 @@
       <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="24">
+      <c r="P8" s="28"/>
+      <c r="Q8" s="1">
         <f>IF(J8=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -4777,7 +4761,7 @@
       </c>
       <c r="U8" s="1">
         <f>IF(N8=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="1">
         <f>IF(O8=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -4805,15 +4789,15 @@
       <c r="F9" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="24">
+      <c r="G9" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="24">
+      <c r="I9" s="26"/>
+      <c r="J9" s="1">
         <v>3</v>
       </c>
       <c r="K9" s="1">
@@ -4831,8 +4815,8 @@
       <c r="O9" s="1">
         <v>2</v>
       </c>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="24">
+      <c r="P9" s="28"/>
+      <c r="Q9" s="1">
         <f>IF(J9=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -4878,15 +4862,15 @@
       <c r="F10" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G10" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="24">
+      <c r="G10" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I10" s="28"/>
-      <c r="J10" s="24">
+      <c r="I10" s="26"/>
+      <c r="J10" s="1">
         <v>4</v>
       </c>
       <c r="K10" s="1">
@@ -4904,8 +4888,8 @@
       <c r="O10" s="1">
         <v>2</v>
       </c>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="24">
+      <c r="P10" s="28"/>
+      <c r="Q10" s="1">
         <f>IF(J10=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -4951,15 +4935,15 @@
       <c r="F11" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G11" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="24">
+      <c r="G11" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I11" s="28"/>
-      <c r="J11" s="24">
+      <c r="I11" s="26"/>
+      <c r="J11" s="1">
         <v>2</v>
       </c>
       <c r="K11" s="1">
@@ -4975,8 +4959,8 @@
       <c r="O11" s="1">
         <v>3</v>
       </c>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="24">
+      <c r="P11" s="28"/>
+      <c r="Q11" s="1">
         <f>IF(J11=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5022,15 +5006,15 @@
       <c r="F12" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G12" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="24">
+      <c r="G12" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I12" s="28"/>
-      <c r="J12" s="24">
+      <c r="I12" s="26"/>
+      <c r="J12" s="1">
         <v>2</v>
       </c>
       <c r="K12" s="1">
@@ -5048,8 +5032,8 @@
       <c r="O12" s="1">
         <v>1</v>
       </c>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="24">
+      <c r="P12" s="28"/>
+      <c r="Q12" s="1">
         <f>IF(J12=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5095,15 +5079,15 @@
       <c r="F13" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G13" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="24">
+      <c r="G13" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I13" s="28"/>
-      <c r="J13" s="24">
+        <v>6</v>
+      </c>
+      <c r="I13" s="26"/>
+      <c r="J13" s="1">
         <v>3</v>
       </c>
       <c r="K13" s="1">
@@ -5121,8 +5105,8 @@
       <c r="O13" s="1">
         <v>2</v>
       </c>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="24">
+      <c r="P13" s="28"/>
+      <c r="Q13" s="1">
         <f>IF(J13=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -5140,7 +5124,7 @@
       </c>
       <c r="U13" s="1">
         <f>IF(N13=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="1">
         <f>IF(O13=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5168,15 +5152,15 @@
       <c r="F14" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G14" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="24">
+      <c r="G14" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I14" s="28"/>
-      <c r="J14" s="24">
+      <c r="I14" s="26"/>
+      <c r="J14" s="1">
         <v>4</v>
       </c>
       <c r="K14" s="1">
@@ -5194,8 +5178,8 @@
       <c r="O14" s="1">
         <v>1</v>
       </c>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="24">
+      <c r="P14" s="28"/>
+      <c r="Q14" s="1">
         <f>IF(J14=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5241,15 +5225,15 @@
       <c r="F15" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G15" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="24">
+      <c r="G15" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I15" s="28"/>
-      <c r="J15" s="24">
+      <c r="I15" s="26"/>
+      <c r="J15" s="1">
         <v>4</v>
       </c>
       <c r="K15" s="1">
@@ -5267,8 +5251,8 @@
       <c r="O15" s="1">
         <v>4</v>
       </c>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="24">
+      <c r="P15" s="28"/>
+      <c r="Q15" s="1">
         <f>IF(J15=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5314,15 +5298,15 @@
       <c r="F16" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G16" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="24">
+      <c r="G16" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I16" s="28"/>
-      <c r="J16" s="24">
+        <v>6</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="1">
         <v>3</v>
       </c>
       <c r="K16" s="1">
@@ -5340,8 +5324,8 @@
       <c r="O16" s="1">
         <v>2</v>
       </c>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="24">
+      <c r="P16" s="28"/>
+      <c r="Q16" s="1">
         <f>IF(J16=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -5359,7 +5343,7 @@
       </c>
       <c r="U16" s="1">
         <f>IF(N16=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="1">
         <f>IF(O16=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5387,15 +5371,15 @@
       <c r="F17" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G17" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="24">
+      <c r="G17" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I17" s="28"/>
-      <c r="J17" s="24">
+      <c r="I17" s="26"/>
+      <c r="J17" s="1">
         <v>3</v>
       </c>
       <c r="K17" s="1">
@@ -5413,8 +5397,8 @@
       <c r="O17" s="1">
         <v>2</v>
       </c>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="24">
+      <c r="P17" s="28"/>
+      <c r="Q17" s="1">
         <f>IF(J17=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -5460,15 +5444,15 @@
       <c r="F18" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G18" s="26" t="b">
+      <c r="G18" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I18" s="28"/>
-      <c r="J18" s="24">
+        <v>2</v>
+      </c>
+      <c r="I18" s="26"/>
+      <c r="J18" s="1">
         <v>2</v>
       </c>
       <c r="K18" s="1">
@@ -5486,8 +5470,8 @@
       <c r="O18" s="1">
         <v>4</v>
       </c>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="24">
+      <c r="P18" s="28"/>
+      <c r="Q18" s="1">
         <f>IF(J18=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5505,7 +5489,7 @@
       </c>
       <c r="U18" s="1">
         <f>IF(N18=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="1">
         <f>IF(O18=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5533,15 +5517,15 @@
       <c r="F19" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="26" t="b">
+      <c r="G19" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I19" s="28"/>
-      <c r="J19" s="24">
+      <c r="I19" s="26"/>
+      <c r="J19" s="1">
         <v>2</v>
       </c>
       <c r="K19" s="1">
@@ -5559,8 +5543,8 @@
       <c r="O19" s="1">
         <v>2</v>
       </c>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="24">
+      <c r="P19" s="28"/>
+      <c r="Q19" s="1">
         <f>IF(J19=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5606,22 +5590,22 @@
       <c r="F20" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G20" s="26" t="b">
+      <c r="G20" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="28"/>
-      <c r="J20" s="24"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="24">
+      <c r="P20" s="28"/>
+      <c r="Q20" s="1">
         <f>IF(J20=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5667,15 +5651,15 @@
       <c r="F21" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="26" t="b">
+      <c r="G21" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I21" s="28"/>
-      <c r="J21" s="24">
+      <c r="I21" s="26"/>
+      <c r="J21" s="1">
         <v>3</v>
       </c>
       <c r="K21" s="1">
@@ -5691,8 +5675,8 @@
         <v>1</v>
       </c>
       <c r="O21" s="1"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="24">
+      <c r="P21" s="28"/>
+      <c r="Q21" s="1">
         <f>IF(J21=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -5738,15 +5722,15 @@
       <c r="F22" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="26" t="b">
+      <c r="G22" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I22" s="28"/>
-      <c r="J22" s="24">
+        <v>5</v>
+      </c>
+      <c r="I22" s="26"/>
+      <c r="J22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1">
@@ -5764,8 +5748,8 @@
       <c r="O22" s="1">
         <v>2</v>
       </c>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="24">
+      <c r="P22" s="28"/>
+      <c r="Q22" s="1">
         <f>IF(J22=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5783,7 +5767,7 @@
       </c>
       <c r="U22" s="1">
         <f>IF(N22=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="1">
         <f>IF(O22=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5811,15 +5795,15 @@
       <c r="F23" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="26" t="b">
+      <c r="G23" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I23" s="28"/>
-      <c r="J23" s="24">
+      <c r="I23" s="26"/>
+      <c r="J23" s="1">
         <v>4</v>
       </c>
       <c r="K23" s="1">
@@ -5837,8 +5821,8 @@
       <c r="O23" s="1">
         <v>2</v>
       </c>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="24">
+      <c r="P23" s="28"/>
+      <c r="Q23" s="1">
         <f>IF(J23=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5884,15 +5868,15 @@
       <c r="F24" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G24" s="26" t="b">
+      <c r="G24" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I24" s="28"/>
-      <c r="J24" s="24">
+        <v>4</v>
+      </c>
+      <c r="I24" s="26"/>
+      <c r="J24" s="1">
         <v>1</v>
       </c>
       <c r="K24" s="1">
@@ -5910,8 +5894,8 @@
       <c r="O24" s="1">
         <v>2</v>
       </c>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="24">
+      <c r="P24" s="28"/>
+      <c r="Q24" s="1">
         <f>IF(J24=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -5929,7 +5913,7 @@
       </c>
       <c r="U24" s="1">
         <f>IF(N24=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="1">
         <f>IF(O24=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5957,15 +5941,15 @@
       <c r="F25" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G25" s="26" t="b">
+      <c r="G25" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I25" s="28"/>
-      <c r="J25" s="24">
+        <v>4</v>
+      </c>
+      <c r="I25" s="26"/>
+      <c r="J25" s="1">
         <v>2</v>
       </c>
       <c r="K25" s="1">
@@ -5983,8 +5967,8 @@
       <c r="O25" s="1">
         <v>4</v>
       </c>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="24">
+      <c r="P25" s="28"/>
+      <c r="Q25" s="1">
         <f>IF(J25=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -6002,7 +5986,7 @@
       </c>
       <c r="U25" s="1">
         <f>IF(N25=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="1">
         <f>IF(O25=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6030,15 +6014,15 @@
       <c r="F26" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G26" s="26" t="b">
+      <c r="G26" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I26" s="28"/>
-      <c r="J26" s="24">
+      <c r="I26" s="26"/>
+      <c r="J26" s="1">
         <v>3</v>
       </c>
       <c r="K26" s="1">
@@ -6056,8 +6040,8 @@
       <c r="O26" s="1">
         <v>4</v>
       </c>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="24">
+      <c r="P26" s="28"/>
+      <c r="Q26" s="1">
         <f>IF(J26=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -6103,15 +6087,15 @@
       <c r="F27" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G27" s="26" t="b">
+      <c r="G27" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="28"/>
-      <c r="J27" s="24">
+        <v>1</v>
+      </c>
+      <c r="I27" s="26"/>
+      <c r="J27" s="1">
         <v>4</v>
       </c>
       <c r="K27" s="1">
@@ -6129,8 +6113,8 @@
       <c r="O27" s="1">
         <v>1</v>
       </c>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="24">
+      <c r="P27" s="28"/>
+      <c r="Q27" s="1">
         <f>IF(J27=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -6148,7 +6132,7 @@
       </c>
       <c r="U27" s="1">
         <f>IF(N27=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="1">
         <f>IF(O27=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6176,15 +6160,15 @@
       <c r="F28" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G28" s="26" t="b">
+      <c r="G28" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I28" s="28"/>
-      <c r="J28" s="24">
+      <c r="I28" s="26"/>
+      <c r="J28" s="1">
         <v>3</v>
       </c>
       <c r="K28" s="1">
@@ -6202,8 +6186,8 @@
       <c r="O28" s="1">
         <v>2</v>
       </c>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="24">
+      <c r="P28" s="28"/>
+      <c r="Q28" s="1">
         <f>IF(J28=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -6249,15 +6233,15 @@
       <c r="F29" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G29" s="26" t="b">
+      <c r="G29" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I29" s="28"/>
-      <c r="J29" s="24">
+      <c r="I29" s="26"/>
+      <c r="J29" s="1">
         <v>3</v>
       </c>
       <c r="K29" s="1">
@@ -6275,8 +6259,8 @@
       <c r="O29" s="1">
         <v>2</v>
       </c>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="24">
+      <c r="P29" s="28"/>
+      <c r="Q29" s="1">
         <f>IF(J29=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -6322,15 +6306,15 @@
       <c r="F30" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G30" s="26" t="b">
+      <c r="G30" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I30" s="28"/>
-      <c r="J30" s="24">
+      <c r="I30" s="26"/>
+      <c r="J30" s="1">
         <v>4</v>
       </c>
       <c r="K30" s="1">
@@ -6346,8 +6330,8 @@
         <v>1</v>
       </c>
       <c r="O30" s="1"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="24">
+      <c r="P30" s="28"/>
+      <c r="Q30" s="1">
         <f>IF(J30=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -6393,15 +6377,15 @@
       <c r="F31" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G31" s="26" t="b">
+      <c r="G31" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I31" s="28"/>
-      <c r="J31" s="24">
+      <c r="I31" s="26"/>
+      <c r="J31" s="1">
         <v>3</v>
       </c>
       <c r="K31" s="1">
@@ -6419,8 +6403,8 @@
       <c r="O31" s="1">
         <v>2</v>
       </c>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="24">
+      <c r="P31" s="28"/>
+      <c r="Q31" s="1">
         <f>IF(J31=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -6466,15 +6450,15 @@
       <c r="F32" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G32" s="26" t="b">
+      <c r="G32" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="I32" s="28"/>
-      <c r="J32" s="24">
+        <v>3</v>
+      </c>
+      <c r="I32" s="26"/>
+      <c r="J32" s="1">
         <v>3</v>
       </c>
       <c r="K32" s="1">
@@ -6492,8 +6476,8 @@
       <c r="O32" s="1">
         <v>4</v>
       </c>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="24">
+      <c r="P32" s="28"/>
+      <c r="Q32" s="1">
         <f>IF(J32=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -6511,7 +6495,7 @@
       </c>
       <c r="U32" s="1">
         <f>IF(N32=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="1">
         <f>IF(O32=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6539,15 +6523,15 @@
       <c r="F33" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G33" s="26" t="b">
+      <c r="G33" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I33" s="28"/>
-      <c r="J33" s="24">
+      <c r="I33" s="26"/>
+      <c r="J33" s="1">
         <v>2</v>
       </c>
       <c r="K33" s="1">
@@ -6565,8 +6549,8 @@
       <c r="O33" s="1">
         <v>3</v>
       </c>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="24">
+      <c r="P33" s="28"/>
+      <c r="Q33" s="1">
         <f>IF(J33=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -6612,15 +6596,15 @@
       <c r="F34" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G34" s="26" t="b">
+      <c r="G34" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I34" s="28"/>
-      <c r="J34" s="24">
+        <v>3</v>
+      </c>
+      <c r="I34" s="26"/>
+      <c r="J34" s="1">
         <v>3</v>
       </c>
       <c r="K34" s="1">
@@ -6638,8 +6622,8 @@
       <c r="O34" s="1">
         <v>1</v>
       </c>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="24">
+      <c r="P34" s="28"/>
+      <c r="Q34" s="1">
         <f>IF(J34=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -6657,7 +6641,7 @@
       </c>
       <c r="U34" s="1">
         <f>IF(N34=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="1">
         <f>IF(O34=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6685,15 +6669,15 @@
       <c r="F35" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G35" s="26" t="b">
+      <c r="G35" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I35" s="28"/>
-      <c r="J35" s="24">
+      <c r="I35" s="26"/>
+      <c r="J35" s="1">
         <v>3</v>
       </c>
       <c r="K35" s="1">
@@ -6711,8 +6695,8 @@
       <c r="O35" s="1">
         <v>2</v>
       </c>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="24">
+      <c r="P35" s="28"/>
+      <c r="Q35" s="1">
         <f>IF(J35=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -6758,15 +6742,15 @@
       <c r="F36" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G36" s="26" t="b">
+      <c r="G36" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I36" s="28"/>
-      <c r="J36" s="24">
+      <c r="I36" s="26"/>
+      <c r="J36" s="1">
         <v>4</v>
       </c>
       <c r="K36" s="1">
@@ -6784,8 +6768,8 @@
       <c r="O36" s="1">
         <v>2</v>
       </c>
-      <c r="P36" s="30"/>
-      <c r="Q36" s="24">
+      <c r="P36" s="28"/>
+      <c r="Q36" s="1">
         <f>IF(J36=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -6831,15 +6815,15 @@
       <c r="F37" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G37" s="26" t="b">
+      <c r="G37" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I37" s="28"/>
-      <c r="J37" s="24">
+      <c r="I37" s="26"/>
+      <c r="J37" s="1">
         <v>2</v>
       </c>
       <c r="K37" s="1">
@@ -6857,8 +6841,8 @@
       <c r="O37" s="1">
         <v>2</v>
       </c>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="24">
+      <c r="P37" s="28"/>
+      <c r="Q37" s="1">
         <f>IF(J37=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -6904,15 +6888,15 @@
       <c r="F38" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G38" s="26" t="b">
+      <c r="G38" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I38" s="28"/>
-      <c r="J38" s="24">
+      <c r="I38" s="26"/>
+      <c r="J38" s="1">
         <v>4</v>
       </c>
       <c r="K38" s="1">
@@ -6930,8 +6914,8 @@
       <c r="O38" s="1">
         <v>2</v>
       </c>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="24">
+      <c r="P38" s="28"/>
+      <c r="Q38" s="1">
         <f>IF(J38=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -6977,15 +6961,15 @@
       <c r="F39" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G39" s="26" t="b">
+      <c r="G39" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="I39" s="28"/>
-      <c r="J39" s="24">
+      <c r="I39" s="26"/>
+      <c r="J39" s="1">
         <v>4</v>
       </c>
       <c r="K39" s="1">
@@ -7003,8 +6987,8 @@
       <c r="O39" s="1">
         <v>2</v>
       </c>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="24">
+      <c r="P39" s="28"/>
+      <c r="Q39" s="1">
         <f>IF(J39=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -7050,15 +7034,15 @@
       <c r="F40" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G40" s="26" t="b">
+      <c r="G40" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I40" s="28"/>
-      <c r="J40" s="24">
+      <c r="I40" s="26"/>
+      <c r="J40" s="1">
         <v>2</v>
       </c>
       <c r="K40" s="1">
@@ -7076,8 +7060,8 @@
       <c r="O40" s="1">
         <v>1</v>
       </c>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="24">
+      <c r="P40" s="28"/>
+      <c r="Q40" s="1">
         <f>IF(J40=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -7123,15 +7107,15 @@
       <c r="F41" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G41" s="26" t="b">
+      <c r="G41" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I41" s="28"/>
-      <c r="J41" s="24">
+        <v>4</v>
+      </c>
+      <c r="I41" s="26"/>
+      <c r="J41" s="1">
         <v>2</v>
       </c>
       <c r="K41" s="1">
@@ -7149,8 +7133,8 @@
       <c r="O41" s="1">
         <v>2</v>
       </c>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="24">
+      <c r="P41" s="28"/>
+      <c r="Q41" s="1">
         <f>IF(J41=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -7168,7 +7152,7 @@
       </c>
       <c r="U41" s="1">
         <f>IF(N41=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="1">
         <f>IF(O41=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7196,15 +7180,15 @@
       <c r="F42" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G42" s="26" t="b">
+      <c r="G42" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I42" s="28"/>
-      <c r="J42" s="24">
+      <c r="I42" s="26"/>
+      <c r="J42" s="1">
         <v>3</v>
       </c>
       <c r="K42" s="1">
@@ -7222,8 +7206,8 @@
       <c r="O42" s="1">
         <v>2</v>
       </c>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="24">
+      <c r="P42" s="28"/>
+      <c r="Q42" s="1">
         <f>IF(J42=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -7269,15 +7253,15 @@
       <c r="F43" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G43" s="26" t="b">
+      <c r="G43" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I43" s="28"/>
-      <c r="J43" s="24">
+      <c r="I43" s="26"/>
+      <c r="J43" s="1">
         <v>3</v>
       </c>
       <c r="K43" s="1">
@@ -7295,8 +7279,8 @@
       <c r="O43" s="1">
         <v>2</v>
       </c>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="24">
+      <c r="P43" s="28"/>
+      <c r="Q43" s="1">
         <f>IF(J43=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -7342,15 +7326,15 @@
       <c r="F44" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G44" s="26" t="b">
+      <c r="G44" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I44" s="28"/>
-      <c r="J44" s="24">
+        <v>4</v>
+      </c>
+      <c r="I44" s="26"/>
+      <c r="J44" s="1">
         <v>2</v>
       </c>
       <c r="K44" s="1">
@@ -7368,8 +7352,8 @@
       <c r="O44" s="1">
         <v>4</v>
       </c>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="24">
+      <c r="P44" s="28"/>
+      <c r="Q44" s="1">
         <f>IF(J44=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
@@ -7387,7 +7371,7 @@
       </c>
       <c r="U44" s="1">
         <f>IF(N44=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="1">
         <f>IF(O44=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7415,15 +7399,15 @@
       <c r="F45" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G45" s="26" t="b">
+      <c r="G45" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I45" s="28"/>
-      <c r="J45" s="24">
+      <c r="I45" s="26"/>
+      <c r="J45" s="1">
         <v>3</v>
       </c>
       <c r="K45" s="1">
@@ -7433,8 +7417,8 @@
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="24">
+      <c r="P45" s="28"/>
+      <c r="Q45" s="1">
         <f>IF(J45=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -7480,15 +7464,15 @@
       <c r="F46" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G46" s="26" t="b">
+      <c r="G46" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="I46" s="28"/>
-      <c r="J46" s="24">
+      <c r="I46" s="26"/>
+      <c r="J46" s="1">
         <v>3</v>
       </c>
       <c r="K46" s="1">
@@ -7506,8 +7490,8 @@
       <c r="O46" s="1">
         <v>2</v>
       </c>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="24">
+      <c r="P46" s="28"/>
+      <c r="Q46" s="1">
         <f>IF(J46=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
@@ -7551,14 +7535,14 @@
       <c r="F47" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G47" s="26" t="b">
+      <c r="G47" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="1">
         <v>2</v>
       </c>
-      <c r="I47" s="28"/>
-      <c r="J47" s="24">
+      <c r="I47" s="26"/>
+      <c r="J47" s="1">
         <v>1</v>
       </c>
       <c r="K47" s="1">
@@ -7572,8 +7556,8 @@
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="24">
+      <c r="P47" s="28"/>
+      <c r="Q47" s="1">
         <v>0</v>
       </c>
       <c r="R47" s="1">
@@ -7609,14 +7593,14 @@
       <c r="F48" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G48" s="26" t="b">
+      <c r="G48" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="1">
         <v>3</v>
       </c>
-      <c r="I48" s="28"/>
-      <c r="J48" s="24">
+      <c r="I48" s="26"/>
+      <c r="J48" s="1">
         <v>1</v>
       </c>
       <c r="K48" s="1">
@@ -7634,8 +7618,8 @@
       <c r="O48" s="1">
         <v>2</v>
       </c>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="24">
+      <c r="P48" s="28"/>
+      <c r="Q48" s="1">
         <v>0</v>
       </c>
       <c r="R48" s="1">
@@ -7673,14 +7657,14 @@
       <c r="F49" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G49" s="26" t="b">
+      <c r="G49" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="1">
         <v>4</v>
       </c>
-      <c r="I49" s="28"/>
-      <c r="J49" s="24">
+      <c r="I49" s="26"/>
+      <c r="J49" s="1">
         <v>3</v>
       </c>
       <c r="K49" s="1">
@@ -7698,8 +7682,8 @@
       <c r="O49" s="1">
         <v>4</v>
       </c>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="24">
+      <c r="P49" s="28"/>
+      <c r="Q49" s="1">
         <v>1</v>
       </c>
       <c r="R49" s="1">
@@ -7737,14 +7721,14 @@
       <c r="F50" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G50" s="26" t="b">
+      <c r="G50" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="1">
         <v>3</v>
       </c>
-      <c r="I50" s="28"/>
-      <c r="J50" s="24">
+      <c r="I50" s="26"/>
+      <c r="J50" s="1">
         <v>4</v>
       </c>
       <c r="K50" s="1">
@@ -7762,8 +7746,8 @@
       <c r="O50" s="1">
         <v>2</v>
       </c>
-      <c r="P50" s="30"/>
-      <c r="Q50" s="24">
+      <c r="P50" s="28"/>
+      <c r="Q50" s="1">
         <v>0</v>
       </c>
       <c r="R50" s="1">
@@ -7801,14 +7785,14 @@
       <c r="F51" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G51" s="26" t="b">
+      <c r="G51" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="1">
         <v>3</v>
       </c>
-      <c r="I51" s="28"/>
-      <c r="J51" s="24">
+      <c r="I51" s="26"/>
+      <c r="J51" s="1">
         <v>4</v>
       </c>
       <c r="K51" s="1">
@@ -7826,8 +7810,8 @@
       <c r="O51" s="1">
         <v>2</v>
       </c>
-      <c r="P51" s="30"/>
-      <c r="Q51" s="24">
+      <c r="P51" s="28"/>
+      <c r="Q51" s="1">
         <v>0</v>
       </c>
       <c r="R51" s="1">
@@ -7865,14 +7849,14 @@
       <c r="F52" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G52" s="26" t="b">
+      <c r="G52" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="1">
         <v>2</v>
       </c>
-      <c r="I52" s="28"/>
-      <c r="J52" s="24">
+      <c r="I52" s="26"/>
+      <c r="J52" s="1">
         <v>2</v>
       </c>
       <c r="K52" s="1">
@@ -7890,8 +7874,8 @@
       <c r="O52" s="1">
         <v>2</v>
       </c>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="24">
+      <c r="P52" s="28"/>
+      <c r="Q52" s="1">
         <v>0</v>
       </c>
       <c r="R52" s="1">
@@ -7929,14 +7913,14 @@
       <c r="F53" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G53" s="26" t="b">
+      <c r="G53" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="1">
         <v>4</v>
       </c>
-      <c r="I53" s="28"/>
-      <c r="J53" s="24">
+      <c r="I53" s="26"/>
+      <c r="J53" s="1">
         <v>2</v>
       </c>
       <c r="K53" s="1">
@@ -7954,8 +7938,8 @@
       <c r="O53" s="1">
         <v>2</v>
       </c>
-      <c r="P53" s="30"/>
-      <c r="Q53" s="24">
+      <c r="P53" s="28"/>
+      <c r="Q53" s="1">
         <v>0</v>
       </c>
       <c r="R53" s="1">
@@ -7993,14 +7977,14 @@
       <c r="F54" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G54" s="26" t="b">
+      <c r="G54" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H54" s="1">
         <v>5</v>
       </c>
-      <c r="I54" s="28"/>
-      <c r="J54" s="24">
+      <c r="I54" s="26"/>
+      <c r="J54" s="1">
         <v>3</v>
       </c>
       <c r="K54" s="1">
@@ -8018,8 +8002,8 @@
       <c r="O54" s="1">
         <v>2</v>
       </c>
-      <c r="P54" s="30"/>
-      <c r="Q54" s="24">
+      <c r="P54" s="28"/>
+      <c r="Q54" s="1">
         <v>1</v>
       </c>
       <c r="R54" s="1">
@@ -8057,14 +8041,14 @@
       <c r="F55" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G55" s="26" t="b">
+      <c r="G55" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="1">
         <v>5</v>
       </c>
-      <c r="I55" s="28"/>
-      <c r="J55" s="24">
+      <c r="I55" s="26"/>
+      <c r="J55" s="1">
         <v>3</v>
       </c>
       <c r="K55" s="1">
@@ -8082,8 +8066,8 @@
       <c r="O55" s="1">
         <v>2</v>
       </c>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="24">
+      <c r="P55" s="28"/>
+      <c r="Q55" s="1">
         <v>1</v>
       </c>
       <c r="R55" s="1">
@@ -8121,14 +8105,14 @@
       <c r="F56" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G56" s="26" t="b">
+      <c r="G56" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="1">
         <v>5</v>
       </c>
-      <c r="I56" s="28"/>
-      <c r="J56" s="24">
+      <c r="I56" s="26"/>
+      <c r="J56" s="1">
         <v>3</v>
       </c>
       <c r="K56" s="1">
@@ -8146,8 +8130,8 @@
       <c r="O56" s="1">
         <v>2</v>
       </c>
-      <c r="P56" s="30"/>
-      <c r="Q56" s="24">
+      <c r="P56" s="28"/>
+      <c r="Q56" s="1">
         <v>1</v>
       </c>
       <c r="R56" s="1">
@@ -8185,14 +8169,14 @@
       <c r="F57" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G57" s="26" t="b">
+      <c r="G57" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="1">
         <v>4</v>
       </c>
-      <c r="I57" s="28"/>
-      <c r="J57" s="24">
+      <c r="I57" s="26"/>
+      <c r="J57" s="1">
         <v>3</v>
       </c>
       <c r="K57" s="1">
@@ -8210,8 +8194,8 @@
       <c r="O57" s="1">
         <v>2</v>
       </c>
-      <c r="P57" s="30"/>
-      <c r="Q57" s="24">
+      <c r="P57" s="28"/>
+      <c r="Q57" s="1">
         <v>1</v>
       </c>
       <c r="R57" s="1">
@@ -8249,14 +8233,14 @@
       <c r="F58" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G58" s="26" t="b">
+      <c r="G58" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H58" s="1">
         <v>5</v>
       </c>
-      <c r="I58" s="28"/>
-      <c r="J58" s="24">
+      <c r="I58" s="26"/>
+      <c r="J58" s="1">
         <v>3</v>
       </c>
       <c r="K58" s="1">
@@ -8274,8 +8258,8 @@
       <c r="O58" s="1">
         <v>2</v>
       </c>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="24">
+      <c r="P58" s="28"/>
+      <c r="Q58" s="1">
         <v>1</v>
       </c>
       <c r="R58" s="1">
@@ -8313,14 +8297,14 @@
       <c r="F59" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G59" s="26" t="b">
+      <c r="G59" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="1">
         <v>4</v>
       </c>
-      <c r="I59" s="28"/>
-      <c r="J59" s="24">
+      <c r="I59" s="26"/>
+      <c r="J59" s="1">
         <v>3</v>
       </c>
       <c r="K59" s="1">
@@ -8334,8 +8318,8 @@
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
-      <c r="P59" s="30"/>
-      <c r="Q59" s="24">
+      <c r="P59" s="28"/>
+      <c r="Q59" s="1">
         <v>1</v>
       </c>
       <c r="R59" s="1">
@@ -8373,14 +8357,14 @@
       <c r="F60" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G60" s="26" t="b">
+      <c r="G60" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="1">
         <v>3</v>
       </c>
-      <c r="I60" s="28"/>
-      <c r="J60" s="24">
+      <c r="I60" s="26"/>
+      <c r="J60" s="1">
         <v>1</v>
       </c>
       <c r="K60" s="1">
@@ -8398,8 +8382,8 @@
       <c r="O60" s="1">
         <v>2</v>
       </c>
-      <c r="P60" s="30"/>
-      <c r="Q60" s="24">
+      <c r="P60" s="28"/>
+      <c r="Q60" s="1">
         <v>0</v>
       </c>
       <c r="R60" s="1">
@@ -8437,14 +8421,14 @@
       <c r="F61" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G61" s="26" t="b">
+      <c r="G61" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="1">
         <v>3</v>
       </c>
-      <c r="I61" s="28"/>
-      <c r="J61" s="24">
+      <c r="I61" s="26"/>
+      <c r="J61" s="1">
         <v>2</v>
       </c>
       <c r="K61" s="1">
@@ -8462,8 +8446,8 @@
       <c r="O61" s="1">
         <v>2</v>
       </c>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="24">
+      <c r="P61" s="28"/>
+      <c r="Q61" s="1">
         <v>0</v>
       </c>
       <c r="R61" s="1">
@@ -8501,14 +8485,14 @@
       <c r="F62" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G62" s="26" t="b">
+      <c r="G62" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H62" s="1">
         <v>4</v>
       </c>
-      <c r="I62" s="28"/>
-      <c r="J62" s="24">
+      <c r="I62" s="26"/>
+      <c r="J62" s="1">
         <v>3</v>
       </c>
       <c r="K62" s="1">
@@ -8526,8 +8510,8 @@
       <c r="O62" s="1">
         <v>2</v>
       </c>
-      <c r="P62" s="30"/>
-      <c r="Q62" s="24">
+      <c r="P62" s="28"/>
+      <c r="Q62" s="1">
         <v>1</v>
       </c>
       <c r="R62" s="1">
@@ -8565,14 +8549,14 @@
       <c r="F63" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G63" s="26" t="b">
+      <c r="G63" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H63" s="1">
         <v>5</v>
       </c>
-      <c r="I63" s="28"/>
-      <c r="J63" s="24">
+      <c r="I63" s="26"/>
+      <c r="J63" s="1">
         <v>3</v>
       </c>
       <c r="K63" s="1">
@@ -8590,8 +8574,8 @@
       <c r="O63" s="1">
         <v>2</v>
       </c>
-      <c r="P63" s="30"/>
-      <c r="Q63" s="24">
+      <c r="P63" s="28"/>
+      <c r="Q63" s="1">
         <v>1</v>
       </c>
       <c r="R63" s="1">
@@ -8629,14 +8613,14 @@
       <c r="F64" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G64" s="26" t="b">
+      <c r="G64" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H64" s="1">
         <v>3</v>
       </c>
-      <c r="I64" s="28"/>
-      <c r="J64" s="24">
+      <c r="I64" s="26"/>
+      <c r="J64" s="1">
         <v>3</v>
       </c>
       <c r="K64" s="1">
@@ -8654,8 +8638,8 @@
       <c r="O64" s="1">
         <v>4</v>
       </c>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="24">
+      <c r="P64" s="28"/>
+      <c r="Q64" s="1">
         <v>1</v>
       </c>
       <c r="R64" s="1">
@@ -8693,14 +8677,14 @@
       <c r="F65" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G65" s="26" t="b">
+      <c r="G65" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H65" s="1">
         <v>5</v>
       </c>
-      <c r="I65" s="28"/>
-      <c r="J65" s="24">
+      <c r="I65" s="26"/>
+      <c r="J65" s="1">
         <v>3</v>
       </c>
       <c r="K65" s="1">
@@ -8718,8 +8702,8 @@
       <c r="O65" s="1">
         <v>2</v>
       </c>
-      <c r="P65" s="30"/>
-      <c r="Q65" s="24">
+      <c r="P65" s="28"/>
+      <c r="Q65" s="1">
         <v>1</v>
       </c>
       <c r="R65" s="1">
@@ -8757,14 +8741,14 @@
       <c r="F66" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G66" s="26" t="b">
+      <c r="G66" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H66" s="1">
         <v>5</v>
       </c>
-      <c r="I66" s="28"/>
-      <c r="J66" s="24">
+      <c r="I66" s="26"/>
+      <c r="J66" s="1">
         <v>3</v>
       </c>
       <c r="K66" s="1">
@@ -8782,8 +8766,8 @@
       <c r="O66" s="1">
         <v>2</v>
       </c>
-      <c r="P66" s="30"/>
-      <c r="Q66" s="24">
+      <c r="P66" s="28"/>
+      <c r="Q66" s="1">
         <v>1</v>
       </c>
       <c r="R66" s="1">
@@ -8819,14 +8803,14 @@
       <c r="F67" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G67" s="26" t="b">
+      <c r="G67" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="1">
         <v>5</v>
       </c>
-      <c r="I67" s="28"/>
-      <c r="J67" s="24">
+      <c r="I67" s="26"/>
+      <c r="J67" s="1">
         <v>3</v>
       </c>
       <c r="K67" s="1">
@@ -8844,8 +8828,8 @@
       <c r="O67" s="1">
         <v>2</v>
       </c>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="24">
+      <c r="P67" s="28"/>
+      <c r="Q67" s="1">
         <v>1</v>
       </c>
       <c r="R67" s="1">
@@ -8883,14 +8867,14 @@
       <c r="F68" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G68" s="26" t="b">
+      <c r="G68" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H68" s="1">
         <v>3</v>
       </c>
-      <c r="I68" s="28"/>
-      <c r="J68" s="24">
+      <c r="I68" s="26"/>
+      <c r="J68" s="1">
         <v>4</v>
       </c>
       <c r="K68" s="1">
@@ -8908,10 +8892,10 @@
       <c r="O68" s="1">
         <v>2</v>
       </c>
-      <c r="P68" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="24">
+      <c r="P68" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="1">
         <v>0</v>
       </c>
       <c r="R68" s="1">
@@ -8949,14 +8933,14 @@
       <c r="F69" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G69" s="26" t="b">
+      <c r="G69" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H69" s="1">
         <v>5</v>
       </c>
-      <c r="I69" s="28"/>
-      <c r="J69" s="24">
+      <c r="I69" s="26"/>
+      <c r="J69" s="1">
         <v>3</v>
       </c>
       <c r="K69" s="1">
@@ -8974,10 +8958,10 @@
       <c r="O69" s="1">
         <v>2</v>
       </c>
-      <c r="P69" s="30">
-        <v>2</v>
-      </c>
-      <c r="Q69" s="24">
+      <c r="P69" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q69" s="1">
         <v>1</v>
       </c>
       <c r="R69" s="1">
@@ -9015,14 +8999,14 @@
       <c r="F70" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G70" s="26" t="b">
+      <c r="G70" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H70" s="1">
         <v>6</v>
       </c>
-      <c r="I70" s="28"/>
-      <c r="J70" s="24">
+      <c r="I70" s="26"/>
+      <c r="J70" s="1">
         <v>3</v>
       </c>
       <c r="K70" s="1">
@@ -9040,10 +9024,10 @@
       <c r="O70" s="1">
         <v>2</v>
       </c>
-      <c r="P70" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q70" s="24">
+      <c r="P70" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="1">
         <v>1</v>
       </c>
       <c r="R70" s="1">
@@ -9081,14 +9065,14 @@
       <c r="F71" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G71" s="26" t="b">
+      <c r="G71" s="24" t="b">
         <v>1</v>
       </c>
       <c r="H71" s="1">
         <v>2</v>
       </c>
-      <c r="I71" s="28"/>
-      <c r="J71" s="24">
+      <c r="I71" s="26"/>
+      <c r="J71" s="1">
         <v>2</v>
       </c>
       <c r="K71" s="1">
@@ -9102,10 +9086,10 @@
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
-      <c r="P71" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q71" s="24">
+      <c r="P71" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q71" s="1">
         <v>0</v>
       </c>
       <c r="R71" s="1">
@@ -9143,14 +9127,14 @@
       <c r="F72" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G72" s="26" t="b">
+      <c r="G72" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="1">
         <v>4</v>
       </c>
-      <c r="I72" s="28"/>
-      <c r="J72" s="24">
+      <c r="I72" s="26"/>
+      <c r="J72" s="1">
         <v>3</v>
       </c>
       <c r="K72" s="1">
@@ -9168,10 +9152,10 @@
       <c r="O72" s="1">
         <v>2</v>
       </c>
-      <c r="P72" s="30">
+      <c r="P72" s="28">
         <v>5</v>
       </c>
-      <c r="Q72" s="24">
+      <c r="Q72" s="1">
         <v>1</v>
       </c>
       <c r="R72" s="1">
@@ -9209,14 +9193,14 @@
       <c r="F73" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G73" s="26" t="b">
+      <c r="G73" s="24" t="b">
         <v>1</v>
       </c>
       <c r="H73" s="1">
         <v>5</v>
       </c>
-      <c r="I73" s="28"/>
-      <c r="J73" s="24">
+      <c r="I73" s="26"/>
+      <c r="J73" s="1">
         <v>3</v>
       </c>
       <c r="K73" s="1">
@@ -9234,10 +9218,10 @@
       <c r="O73" s="1">
         <v>2</v>
       </c>
-      <c r="P73" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q73" s="24">
+      <c r="P73" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q73" s="1">
         <v>1</v>
       </c>
       <c r="R73" s="1">
@@ -9275,14 +9259,14 @@
       <c r="F74" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G74" s="26" t="b">
+      <c r="G74" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H74" s="1">
         <v>3</v>
       </c>
-      <c r="I74" s="28"/>
-      <c r="J74" s="24">
+      <c r="I74" s="26"/>
+      <c r="J74" s="1">
         <v>4</v>
       </c>
       <c r="K74" s="1">
@@ -9300,10 +9284,10 @@
       <c r="O74" s="1">
         <v>2</v>
       </c>
-      <c r="P74" s="30">
-        <v>2</v>
-      </c>
-      <c r="Q74" s="24">
+      <c r="P74" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q74" s="1">
         <v>0</v>
       </c>
       <c r="R74" s="1">
@@ -9341,14 +9325,14 @@
       <c r="F75" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G75" s="26" t="b">
+      <c r="G75" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H75" s="1">
         <v>3</v>
       </c>
-      <c r="I75" s="28"/>
-      <c r="J75" s="24">
+      <c r="I75" s="26"/>
+      <c r="J75" s="1">
         <v>3</v>
       </c>
       <c r="K75" s="1">
@@ -9366,10 +9350,10 @@
       <c r="O75" s="1">
         <v>1</v>
       </c>
-      <c r="P75" s="30">
+      <c r="P75" s="28">
         <v>5</v>
       </c>
-      <c r="Q75" s="24">
+      <c r="Q75" s="1">
         <v>1</v>
       </c>
       <c r="R75" s="1">
@@ -9407,14 +9391,14 @@
       <c r="F76" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G76" s="26" t="b">
+      <c r="G76" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H76" s="1">
         <v>4</v>
       </c>
-      <c r="I76" s="28"/>
-      <c r="J76" s="24">
+      <c r="I76" s="26"/>
+      <c r="J76" s="1">
         <v>4</v>
       </c>
       <c r="K76" s="1">
@@ -9432,10 +9416,10 @@
       <c r="O76" s="1">
         <v>2</v>
       </c>
-      <c r="P76" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="24">
+      <c r="P76" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="1">
         <v>0</v>
       </c>
       <c r="R76" s="1">
@@ -9473,14 +9457,14 @@
       <c r="F77" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G77" s="26" t="b">
+      <c r="G77" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="1">
         <v>6</v>
       </c>
-      <c r="I77" s="28"/>
-      <c r="J77" s="24">
+      <c r="I77" s="26"/>
+      <c r="J77" s="1">
         <v>3</v>
       </c>
       <c r="K77" s="1">
@@ -9498,10 +9482,10 @@
       <c r="O77" s="1">
         <v>2</v>
       </c>
-      <c r="P77" s="30">
+      <c r="P77" s="28">
         <v>5</v>
       </c>
-      <c r="Q77" s="24">
+      <c r="Q77" s="1">
         <v>1</v>
       </c>
       <c r="R77" s="1">
@@ -9539,14 +9523,14 @@
       <c r="F78" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G78" s="26" t="b">
+      <c r="G78" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="1">
         <v>6</v>
       </c>
-      <c r="I78" s="28"/>
-      <c r="J78" s="24">
+      <c r="I78" s="26"/>
+      <c r="J78" s="1">
         <v>3</v>
       </c>
       <c r="K78" s="1">
@@ -9564,10 +9548,10 @@
       <c r="O78" s="1">
         <v>2</v>
       </c>
-      <c r="P78" s="30">
+      <c r="P78" s="28">
         <v>5</v>
       </c>
-      <c r="Q78" s="24">
+      <c r="Q78" s="1">
         <v>1</v>
       </c>
       <c r="R78" s="1">
@@ -9605,14 +9589,14 @@
       <c r="F79" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G79" s="26" t="b">
+      <c r="G79" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H79" s="1">
         <v>5</v>
       </c>
-      <c r="I79" s="28"/>
-      <c r="J79" s="24">
+      <c r="I79" s="26"/>
+      <c r="J79" s="1">
         <v>3</v>
       </c>
       <c r="K79" s="1">
@@ -9630,10 +9614,10 @@
       <c r="O79" s="1">
         <v>2</v>
       </c>
-      <c r="P79" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q79" s="24">
+      <c r="P79" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q79" s="1">
         <v>1</v>
       </c>
       <c r="R79" s="1">
@@ -9671,14 +9655,14 @@
       <c r="F80" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G80" s="26" t="b">
+      <c r="G80" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="1">
         <v>4</v>
       </c>
-      <c r="I80" s="28"/>
-      <c r="J80" s="24">
+      <c r="I80" s="26"/>
+      <c r="J80" s="1">
         <v>3</v>
       </c>
       <c r="K80" s="1">
@@ -9696,10 +9680,10 @@
       <c r="O80" s="1">
         <v>2</v>
       </c>
-      <c r="P80" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="24">
+      <c r="P80" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="1">
         <v>1</v>
       </c>
       <c r="R80" s="1">
@@ -9737,14 +9721,14 @@
       <c r="F81" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G81" s="26" t="b">
+      <c r="G81" s="24" t="b">
         <v>1</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
       </c>
-      <c r="I81" s="28"/>
-      <c r="J81" s="24">
+      <c r="I81" s="26"/>
+      <c r="J81" s="1">
         <v>4</v>
       </c>
       <c r="K81" s="1">
@@ -9762,10 +9746,10 @@
       <c r="O81" s="1">
         <v>3</v>
       </c>
-      <c r="P81" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q81" s="24">
+      <c r="P81" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="1">
         <v>0</v>
       </c>
       <c r="R81" s="1">
@@ -9803,14 +9787,14 @@
       <c r="F82" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G82" s="26" t="b">
+      <c r="G82" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H82" s="1">
         <v>4</v>
       </c>
-      <c r="I82" s="28"/>
-      <c r="J82" s="24">
+      <c r="I82" s="26"/>
+      <c r="J82" s="1">
         <v>4</v>
       </c>
       <c r="K82" s="1"/>
@@ -9826,10 +9810,10 @@
       <c r="O82" s="1">
         <v>2</v>
       </c>
-      <c r="P82" s="30">
+      <c r="P82" s="28">
         <v>4</v>
       </c>
-      <c r="Q82" s="24">
+      <c r="Q82" s="1">
         <v>0</v>
       </c>
       <c r="R82" s="1">
@@ -9867,13 +9851,13 @@
       <c r="F83" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G83" s="26" t="b">
+      <c r="G83" s="24" t="b">
         <v>1</v>
       </c>
       <c r="H83" s="1">
         <v>3</v>
       </c>
-      <c r="I83" s="28"/>
+      <c r="I83" s="26"/>
       <c r="J83" s="1">
         <v>2</v>
       </c>
@@ -9892,7 +9876,7 @@
       <c r="O83" s="1">
         <v>4</v>
       </c>
-      <c r="P83" s="30">
+      <c r="P83" s="28">
         <v>3</v>
       </c>
       <c r="Q83" s="1">
@@ -9933,13 +9917,13 @@
       <c r="F84" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G84" s="26" t="b">
+      <c r="G84" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H84" s="1">
         <v>5</v>
       </c>
-      <c r="I84" s="28"/>
+      <c r="I84" s="26"/>
       <c r="J84" s="1">
         <v>3</v>
       </c>
@@ -9958,7 +9942,7 @@
       <c r="O84" s="1">
         <v>2</v>
       </c>
-      <c r="P84" s="30">
+      <c r="P84" s="28">
         <v>4</v>
       </c>
       <c r="Q84" s="1">
@@ -9999,13 +9983,13 @@
       <c r="F85" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G85" s="26" t="b">
+      <c r="G85" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H85" s="1">
         <v>6</v>
       </c>
-      <c r="I85" s="28"/>
+      <c r="I85" s="26"/>
       <c r="J85" s="1">
         <v>3</v>
       </c>
@@ -10024,7 +10008,7 @@
       <c r="O85" s="1">
         <v>2</v>
       </c>
-      <c r="P85" s="30">
+      <c r="P85" s="28">
         <v>3</v>
       </c>
       <c r="Q85" s="1">
@@ -10065,13 +10049,13 @@
       <c r="F86" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G86" s="26" t="b">
+      <c r="G86" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H86" s="1">
         <v>5</v>
       </c>
-      <c r="I86" s="28"/>
+      <c r="I86" s="26"/>
       <c r="J86" s="1">
         <v>3</v>
       </c>
@@ -10090,7 +10074,7 @@
       <c r="O86" s="1">
         <v>2</v>
       </c>
-      <c r="P86" s="30">
+      <c r="P86" s="28">
         <v>4</v>
       </c>
       <c r="Q86" s="1">
@@ -10131,13 +10115,13 @@
       <c r="F87" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G87" s="26" t="b">
+      <c r="G87" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H87" s="1">
         <v>5</v>
       </c>
-      <c r="I87" s="28"/>
+      <c r="I87" s="26"/>
       <c r="J87" s="1">
         <v>3</v>
       </c>
@@ -10156,7 +10140,7 @@
       <c r="O87" s="1">
         <v>2</v>
       </c>
-      <c r="P87" s="30">
+      <c r="P87" s="28">
         <v>2</v>
       </c>
       <c r="Q87" s="1">
@@ -10197,13 +10181,13 @@
       <c r="F88" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G88" s="26" t="b">
+      <c r="G88" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H88" s="1">
         <v>5</v>
       </c>
-      <c r="I88" s="28"/>
+      <c r="I88" s="26"/>
       <c r="J88" s="1">
         <v>3</v>
       </c>
@@ -10222,7 +10206,7 @@
       <c r="O88" s="1">
         <v>2</v>
       </c>
-      <c r="P88" s="30">
+      <c r="P88" s="28">
         <v>3</v>
       </c>
       <c r="Q88" s="1">
@@ -10263,13 +10247,13 @@
       <c r="F89" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G89" s="26" t="b">
+      <c r="G89" s="24" t="b">
         <v>1</v>
       </c>
       <c r="H89" s="1">
         <v>2</v>
       </c>
-      <c r="I89" s="28"/>
+      <c r="I89" s="26"/>
       <c r="J89" s="1">
         <v>2</v>
       </c>
@@ -10288,7 +10272,7 @@
       <c r="O89" s="1">
         <v>4</v>
       </c>
-      <c r="P89" s="30">
+      <c r="P89" s="28">
         <v>2</v>
       </c>
       <c r="Q89" s="1">
@@ -10329,13 +10313,13 @@
       <c r="F90" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G90" s="26" t="b">
+      <c r="G90" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H90" s="1">
         <v>5</v>
       </c>
-      <c r="I90" s="28"/>
+      <c r="I90" s="26"/>
       <c r="J90" s="1">
         <v>3</v>
       </c>
@@ -10354,7 +10338,7 @@
       <c r="O90" s="1">
         <v>2</v>
       </c>
-      <c r="P90" s="30">
+      <c r="P90" s="28">
         <v>4</v>
       </c>
       <c r="Q90" s="1">
@@ -10395,13 +10379,13 @@
       <c r="F91" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G91" s="26" t="b">
+      <c r="G91" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H91" s="1">
         <v>5</v>
       </c>
-      <c r="I91" s="28"/>
+      <c r="I91" s="26"/>
       <c r="J91" s="1">
         <v>3</v>
       </c>
@@ -10420,7 +10404,7 @@
       <c r="O91" s="1">
         <v>2</v>
       </c>
-      <c r="P91" s="30">
+      <c r="P91" s="28">
         <v>4</v>
       </c>
       <c r="Q91" s="1">
@@ -10461,13 +10445,13 @@
       <c r="F92" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G92" s="26" t="b">
+      <c r="G92" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H92" s="1">
         <v>6</v>
       </c>
-      <c r="I92" s="28"/>
+      <c r="I92" s="26"/>
       <c r="J92" s="1">
         <v>3</v>
       </c>
@@ -10486,7 +10470,7 @@
       <c r="O92" s="1">
         <v>2</v>
       </c>
-      <c r="P92" s="30">
+      <c r="P92" s="28">
         <v>4</v>
       </c>
       <c r="Q92" s="1">
@@ -10527,13 +10511,13 @@
       <c r="F93" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G93" s="26" t="b">
+      <c r="G93" s="24" t="b">
         <v>0</v>
       </c>
       <c r="H93" s="1">
         <v>5</v>
       </c>
-      <c r="I93" s="28"/>
+      <c r="I93" s="26"/>
       <c r="J93" s="1">
         <v>3</v>
       </c>
@@ -10552,7 +10536,7 @@
       <c r="O93" s="1">
         <v>2</v>
       </c>
-      <c r="P93" s="30"/>
+      <c r="P93" s="28"/>
       <c r="Q93" s="1">
         <v>1</v>
       </c>
@@ -10573,1688 +10557,1688 @@
       </c>
     </row>
     <row r="94" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="33" t="s">
+      <c r="A94" s="31" t="s">
         <v>929</v>
       </c>
-      <c r="B94" s="33" t="s">
+      <c r="B94" s="31" t="s">
         <v>930</v>
       </c>
-      <c r="C94" s="33" t="s">
+      <c r="C94" s="31" t="s">
         <v>931</v>
       </c>
-      <c r="D94" s="33" t="s">
+      <c r="D94" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E94" s="34">
-        <v>2</v>
-      </c>
-      <c r="F94" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G94" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="34">
+      <c r="E94" s="32">
+        <v>2</v>
+      </c>
+      <c r="F94" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G94" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="32">
         <v>6</v>
       </c>
-      <c r="J94" s="34">
-        <v>3</v>
-      </c>
-      <c r="K94" s="34">
-        <v>1</v>
-      </c>
-      <c r="L94" s="34">
-        <v>3</v>
-      </c>
-      <c r="M94" s="34">
-        <v>2</v>
-      </c>
-      <c r="N94" s="34">
-        <v>3</v>
-      </c>
-      <c r="O94" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q94" s="34">
-        <v>1</v>
-      </c>
-      <c r="R94" s="34">
-        <v>1</v>
-      </c>
-      <c r="S94" s="34">
-        <v>1</v>
-      </c>
-      <c r="T94" s="34">
-        <v>1</v>
-      </c>
-      <c r="U94" s="34">
-        <v>1</v>
-      </c>
-      <c r="V94" s="34">
+      <c r="J94" s="32">
+        <v>3</v>
+      </c>
+      <c r="K94" s="32">
+        <v>1</v>
+      </c>
+      <c r="L94" s="32">
+        <v>3</v>
+      </c>
+      <c r="M94" s="32">
+        <v>2</v>
+      </c>
+      <c r="N94" s="32">
+        <v>3</v>
+      </c>
+      <c r="O94" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q94" s="32">
+        <v>1</v>
+      </c>
+      <c r="R94" s="32">
+        <v>1</v>
+      </c>
+      <c r="S94" s="32">
+        <v>1</v>
+      </c>
+      <c r="T94" s="32">
+        <v>1</v>
+      </c>
+      <c r="U94" s="32">
+        <v>1</v>
+      </c>
+      <c r="V94" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="33" t="s">
+      <c r="A95" s="31" t="s">
         <v>932</v>
       </c>
-      <c r="B95" s="33" t="s">
+      <c r="B95" s="31" t="s">
         <v>933</v>
       </c>
-      <c r="C95" s="33" t="s">
+      <c r="C95" s="31" t="s">
         <v>934</v>
       </c>
-      <c r="D95" s="33" t="s">
+      <c r="D95" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E95" s="34">
-        <v>2</v>
-      </c>
-      <c r="F95" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G95" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="34">
+      <c r="E95" s="32">
+        <v>2</v>
+      </c>
+      <c r="F95" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G95" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="32">
         <v>6</v>
       </c>
-      <c r="J95" s="34">
-        <v>3</v>
-      </c>
-      <c r="K95" s="34">
-        <v>1</v>
-      </c>
-      <c r="L95" s="34">
-        <v>3</v>
-      </c>
-      <c r="M95" s="34">
-        <v>2</v>
-      </c>
-      <c r="N95" s="34">
-        <v>3</v>
-      </c>
-      <c r="O95" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q95" s="34">
-        <v>1</v>
-      </c>
-      <c r="R95" s="34">
-        <v>1</v>
-      </c>
-      <c r="S95" s="34">
-        <v>1</v>
-      </c>
-      <c r="T95" s="34">
-        <v>1</v>
-      </c>
-      <c r="U95" s="34">
-        <v>1</v>
-      </c>
-      <c r="V95" s="34">
+      <c r="J95" s="32">
+        <v>3</v>
+      </c>
+      <c r="K95" s="32">
+        <v>1</v>
+      </c>
+      <c r="L95" s="32">
+        <v>3</v>
+      </c>
+      <c r="M95" s="32">
+        <v>2</v>
+      </c>
+      <c r="N95" s="32">
+        <v>3</v>
+      </c>
+      <c r="O95" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q95" s="32">
+        <v>1</v>
+      </c>
+      <c r="R95" s="32">
+        <v>1</v>
+      </c>
+      <c r="S95" s="32">
+        <v>1</v>
+      </c>
+      <c r="T95" s="32">
+        <v>1</v>
+      </c>
+      <c r="U95" s="32">
+        <v>1</v>
+      </c>
+      <c r="V95" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="33" t="s">
+      <c r="A96" s="31" t="s">
         <v>935</v>
       </c>
-      <c r="B96" s="33" t="s">
+      <c r="B96" s="31" t="s">
         <v>851</v>
       </c>
-      <c r="C96" s="33" t="s">
+      <c r="C96" s="31" t="s">
         <v>936</v>
       </c>
-      <c r="D96" s="33" t="s">
+      <c r="D96" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E96" s="34">
-        <v>2</v>
-      </c>
-      <c r="F96" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G96" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" s="34">
-        <v>2</v>
-      </c>
-      <c r="J96" s="34">
-        <v>2</v>
-      </c>
-      <c r="K96" s="34">
-        <v>2</v>
-      </c>
-      <c r="L96" s="34">
-        <v>3</v>
-      </c>
-      <c r="M96" s="34">
-        <v>1</v>
-      </c>
-      <c r="N96" s="34">
+      <c r="E96" s="32">
+        <v>2</v>
+      </c>
+      <c r="F96" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G96" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="32">
+        <v>2</v>
+      </c>
+      <c r="J96" s="32">
+        <v>2</v>
+      </c>
+      <c r="K96" s="32">
+        <v>2</v>
+      </c>
+      <c r="L96" s="32">
+        <v>3</v>
+      </c>
+      <c r="M96" s="32">
+        <v>1</v>
+      </c>
+      <c r="N96" s="32">
         <v>4</v>
       </c>
-      <c r="O96" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q96" s="34">
-        <v>0</v>
-      </c>
-      <c r="R96" s="34">
-        <v>0</v>
-      </c>
-      <c r="S96" s="34">
-        <v>1</v>
-      </c>
-      <c r="T96" s="34">
-        <v>0</v>
-      </c>
-      <c r="U96" s="34">
-        <v>0</v>
-      </c>
-      <c r="V96" s="34">
+      <c r="O96" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q96" s="32">
+        <v>0</v>
+      </c>
+      <c r="R96" s="32">
+        <v>0</v>
+      </c>
+      <c r="S96" s="32">
+        <v>1</v>
+      </c>
+      <c r="T96" s="32">
+        <v>0</v>
+      </c>
+      <c r="U96" s="32">
+        <v>0</v>
+      </c>
+      <c r="V96" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="33" t="s">
+      <c r="A97" s="31" t="s">
         <v>937</v>
       </c>
-      <c r="B97" s="33" t="s">
+      <c r="B97" s="31" t="s">
         <v>938</v>
       </c>
-      <c r="C97" s="33" t="s">
+      <c r="C97" s="31" t="s">
         <v>939</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D97" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E97" s="34">
-        <v>2</v>
-      </c>
-      <c r="F97" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G97" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="34">
+      <c r="E97" s="32">
+        <v>2</v>
+      </c>
+      <c r="F97" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G97" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="32">
         <v>6</v>
       </c>
-      <c r="J97" s="34">
-        <v>3</v>
-      </c>
-      <c r="K97" s="34">
-        <v>1</v>
-      </c>
-      <c r="L97" s="34">
-        <v>3</v>
-      </c>
-      <c r="M97" s="34">
-        <v>2</v>
-      </c>
-      <c r="N97" s="34">
-        <v>3</v>
-      </c>
-      <c r="O97" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q97" s="34">
-        <v>1</v>
-      </c>
-      <c r="R97" s="34">
-        <v>1</v>
-      </c>
-      <c r="S97" s="34">
-        <v>1</v>
-      </c>
-      <c r="T97" s="34">
-        <v>1</v>
-      </c>
-      <c r="U97" s="34">
-        <v>1</v>
-      </c>
-      <c r="V97" s="34">
+      <c r="J97" s="32">
+        <v>3</v>
+      </c>
+      <c r="K97" s="32">
+        <v>1</v>
+      </c>
+      <c r="L97" s="32">
+        <v>3</v>
+      </c>
+      <c r="M97" s="32">
+        <v>2</v>
+      </c>
+      <c r="N97" s="32">
+        <v>3</v>
+      </c>
+      <c r="O97" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q97" s="32">
+        <v>1</v>
+      </c>
+      <c r="R97" s="32">
+        <v>1</v>
+      </c>
+      <c r="S97" s="32">
+        <v>1</v>
+      </c>
+      <c r="T97" s="32">
+        <v>1</v>
+      </c>
+      <c r="U97" s="32">
+        <v>1</v>
+      </c>
+      <c r="V97" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="33" t="s">
+      <c r="A98" s="31" t="s">
         <v>940</v>
       </c>
-      <c r="B98" s="33" t="s">
+      <c r="B98" s="31" t="s">
         <v>941</v>
       </c>
-      <c r="C98" s="33" t="s">
+      <c r="C98" s="31" t="s">
         <v>942</v>
       </c>
-      <c r="D98" s="33" t="s">
+      <c r="D98" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E98" s="34">
-        <v>2</v>
-      </c>
-      <c r="F98" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G98" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="34">
+      <c r="E98" s="32">
+        <v>2</v>
+      </c>
+      <c r="F98" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G98" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="32">
         <v>4</v>
       </c>
-      <c r="J98" s="34">
-        <v>3</v>
-      </c>
-      <c r="K98" s="34">
-        <v>1</v>
-      </c>
-      <c r="L98" s="34">
-        <v>2</v>
-      </c>
-      <c r="M98" s="34">
-        <v>3</v>
-      </c>
-      <c r="N98" s="34">
-        <v>3</v>
-      </c>
-      <c r="O98" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q98" s="34">
-        <v>1</v>
-      </c>
-      <c r="R98" s="34">
-        <v>1</v>
-      </c>
-      <c r="S98" s="34">
-        <v>0</v>
-      </c>
-      <c r="T98" s="34">
-        <v>0</v>
-      </c>
-      <c r="U98" s="34">
-        <v>1</v>
-      </c>
-      <c r="V98" s="34">
+      <c r="J98" s="32">
+        <v>3</v>
+      </c>
+      <c r="K98" s="32">
+        <v>1</v>
+      </c>
+      <c r="L98" s="32">
+        <v>2</v>
+      </c>
+      <c r="M98" s="32">
+        <v>3</v>
+      </c>
+      <c r="N98" s="32">
+        <v>3</v>
+      </c>
+      <c r="O98" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q98" s="32">
+        <v>1</v>
+      </c>
+      <c r="R98" s="32">
+        <v>1</v>
+      </c>
+      <c r="S98" s="32">
+        <v>0</v>
+      </c>
+      <c r="T98" s="32">
+        <v>0</v>
+      </c>
+      <c r="U98" s="32">
+        <v>1</v>
+      </c>
+      <c r="V98" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="33" t="s">
+      <c r="A99" s="31" t="s">
         <v>943</v>
       </c>
-      <c r="B99" s="33" t="s">
+      <c r="B99" s="31" t="s">
         <v>944</v>
       </c>
-      <c r="C99" s="33" t="s">
+      <c r="C99" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="D99" s="33" t="s">
+      <c r="D99" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E99" s="34">
-        <v>2</v>
-      </c>
-      <c r="F99" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G99" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="34">
+      <c r="E99" s="32">
+        <v>2</v>
+      </c>
+      <c r="F99" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G99" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="32">
         <v>4</v>
       </c>
-      <c r="J99" s="34">
-        <v>2</v>
-      </c>
-      <c r="K99" s="34">
-        <v>2</v>
-      </c>
-      <c r="L99" s="34">
-        <v>3</v>
-      </c>
-      <c r="M99" s="34">
-        <v>2</v>
-      </c>
-      <c r="N99" s="34">
-        <v>3</v>
-      </c>
-      <c r="O99" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q99" s="34">
-        <v>0</v>
-      </c>
-      <c r="R99" s="34">
-        <v>0</v>
-      </c>
-      <c r="S99" s="34">
-        <v>1</v>
-      </c>
-      <c r="T99" s="34">
-        <v>1</v>
-      </c>
-      <c r="U99" s="34">
-        <v>1</v>
-      </c>
-      <c r="V99" s="34">
+      <c r="J99" s="32">
+        <v>2</v>
+      </c>
+      <c r="K99" s="32">
+        <v>2</v>
+      </c>
+      <c r="L99" s="32">
+        <v>3</v>
+      </c>
+      <c r="M99" s="32">
+        <v>2</v>
+      </c>
+      <c r="N99" s="32">
+        <v>3</v>
+      </c>
+      <c r="O99" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q99" s="32">
+        <v>0</v>
+      </c>
+      <c r="R99" s="32">
+        <v>0</v>
+      </c>
+      <c r="S99" s="32">
+        <v>1</v>
+      </c>
+      <c r="T99" s="32">
+        <v>1</v>
+      </c>
+      <c r="U99" s="32">
+        <v>1</v>
+      </c>
+      <c r="V99" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="33" t="s">
+      <c r="A100" s="31" t="s">
         <v>945</v>
       </c>
-      <c r="B100" s="33" t="s">
+      <c r="B100" s="31" t="s">
         <v>946</v>
       </c>
-      <c r="C100" s="33" t="s">
+      <c r="C100" s="31" t="s">
         <v>947</v>
       </c>
-      <c r="D100" s="33" t="s">
+      <c r="D100" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E100" s="34">
-        <v>2</v>
-      </c>
-      <c r="F100" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G100" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="34">
-        <v>0</v>
-      </c>
-      <c r="J100" s="34">
-        <v>2</v>
-      </c>
-      <c r="K100" s="34">
-        <v>3</v>
-      </c>
-      <c r="L100" s="34">
-        <v>2</v>
-      </c>
-      <c r="M100" s="34">
-        <v>3</v>
-      </c>
-      <c r="N100" s="34">
-        <v>1</v>
-      </c>
-      <c r="O100" s="34">
+      <c r="E100" s="32">
+        <v>2</v>
+      </c>
+      <c r="F100" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G100" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="32">
+        <v>0</v>
+      </c>
+      <c r="J100" s="32">
+        <v>2</v>
+      </c>
+      <c r="K100" s="32">
+        <v>3</v>
+      </c>
+      <c r="L100" s="32">
+        <v>2</v>
+      </c>
+      <c r="M100" s="32">
+        <v>3</v>
+      </c>
+      <c r="N100" s="32">
+        <v>1</v>
+      </c>
+      <c r="O100" s="32">
         <v>4</v>
       </c>
-      <c r="Q100" s="34">
-        <v>0</v>
-      </c>
-      <c r="R100" s="34">
-        <v>0</v>
-      </c>
-      <c r="S100" s="34">
-        <v>0</v>
-      </c>
-      <c r="T100" s="34">
-        <v>0</v>
-      </c>
-      <c r="U100" s="34">
-        <v>0</v>
-      </c>
-      <c r="V100" s="34">
+      <c r="Q100" s="32">
+        <v>0</v>
+      </c>
+      <c r="R100" s="32">
+        <v>0</v>
+      </c>
+      <c r="S100" s="32">
+        <v>0</v>
+      </c>
+      <c r="T100" s="32">
+        <v>0</v>
+      </c>
+      <c r="U100" s="32">
+        <v>0</v>
+      </c>
+      <c r="V100" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="33" t="s">
+      <c r="A101" s="31" t="s">
         <v>948</v>
       </c>
-      <c r="B101" s="33" t="s">
+      <c r="B101" s="31" t="s">
         <v>949</v>
       </c>
-      <c r="C101" s="33" t="s">
+      <c r="C101" s="31" t="s">
         <v>950</v>
       </c>
-      <c r="D101" s="33" t="s">
+      <c r="D101" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E101" s="34">
-        <v>2</v>
-      </c>
-      <c r="F101" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G101" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="34">
+      <c r="E101" s="32">
+        <v>2</v>
+      </c>
+      <c r="F101" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G101" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="32">
         <v>5</v>
       </c>
-      <c r="J101" s="34">
-        <v>3</v>
-      </c>
-      <c r="K101" s="34">
-        <v>2</v>
-      </c>
-      <c r="L101" s="34">
-        <v>3</v>
-      </c>
-      <c r="M101" s="34">
-        <v>2</v>
-      </c>
-      <c r="N101" s="34">
-        <v>3</v>
-      </c>
-      <c r="O101" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q101" s="34">
-        <v>1</v>
-      </c>
-      <c r="R101" s="34">
-        <v>0</v>
-      </c>
-      <c r="S101" s="34">
-        <v>1</v>
-      </c>
-      <c r="T101" s="34">
-        <v>1</v>
-      </c>
-      <c r="U101" s="34">
-        <v>1</v>
-      </c>
-      <c r="V101" s="34">
+      <c r="J101" s="32">
+        <v>3</v>
+      </c>
+      <c r="K101" s="32">
+        <v>2</v>
+      </c>
+      <c r="L101" s="32">
+        <v>3</v>
+      </c>
+      <c r="M101" s="32">
+        <v>2</v>
+      </c>
+      <c r="N101" s="32">
+        <v>3</v>
+      </c>
+      <c r="O101" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q101" s="32">
+        <v>1</v>
+      </c>
+      <c r="R101" s="32">
+        <v>0</v>
+      </c>
+      <c r="S101" s="32">
+        <v>1</v>
+      </c>
+      <c r="T101" s="32">
+        <v>1</v>
+      </c>
+      <c r="U101" s="32">
+        <v>1</v>
+      </c>
+      <c r="V101" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="33" t="s">
+      <c r="A102" s="31" t="s">
         <v>948</v>
       </c>
-      <c r="B102" s="33" t="s">
+      <c r="B102" s="31" t="s">
         <v>949</v>
       </c>
-      <c r="C102" s="33" t="s">
+      <c r="C102" s="31" t="s">
         <v>950</v>
       </c>
-      <c r="D102" s="33" t="s">
+      <c r="D102" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E102" s="34">
-        <v>2</v>
-      </c>
-      <c r="F102" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G102" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="34">
+      <c r="E102" s="32">
+        <v>2</v>
+      </c>
+      <c r="F102" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G102" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="32">
         <v>5</v>
       </c>
-      <c r="J102" s="34">
-        <v>3</v>
-      </c>
-      <c r="K102" s="34">
-        <v>2</v>
-      </c>
-      <c r="L102" s="34">
-        <v>3</v>
-      </c>
-      <c r="M102" s="34">
-        <v>2</v>
-      </c>
-      <c r="N102" s="34">
-        <v>3</v>
-      </c>
-      <c r="O102" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q102" s="34">
-        <v>1</v>
-      </c>
-      <c r="R102" s="34">
-        <v>0</v>
-      </c>
-      <c r="S102" s="34">
-        <v>1</v>
-      </c>
-      <c r="T102" s="34">
-        <v>1</v>
-      </c>
-      <c r="U102" s="34">
-        <v>1</v>
-      </c>
-      <c r="V102" s="34">
+      <c r="J102" s="32">
+        <v>3</v>
+      </c>
+      <c r="K102" s="32">
+        <v>2</v>
+      </c>
+      <c r="L102" s="32">
+        <v>3</v>
+      </c>
+      <c r="M102" s="32">
+        <v>2</v>
+      </c>
+      <c r="N102" s="32">
+        <v>3</v>
+      </c>
+      <c r="O102" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q102" s="32">
+        <v>1</v>
+      </c>
+      <c r="R102" s="32">
+        <v>0</v>
+      </c>
+      <c r="S102" s="32">
+        <v>1</v>
+      </c>
+      <c r="T102" s="32">
+        <v>1</v>
+      </c>
+      <c r="U102" s="32">
+        <v>1</v>
+      </c>
+      <c r="V102" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="33" t="s">
+      <c r="A103" s="31" t="s">
         <v>951</v>
       </c>
-      <c r="B103" s="33" t="s">
+      <c r="B103" s="31" t="s">
         <v>952</v>
       </c>
-      <c r="C103" s="33" t="s">
+      <c r="C103" s="31" t="s">
         <v>953</v>
       </c>
-      <c r="D103" s="33" t="s">
+      <c r="D103" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E103" s="34">
-        <v>2</v>
-      </c>
-      <c r="F103" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G103" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="34">
-        <v>3</v>
-      </c>
-      <c r="J103" s="34">
-        <v>2</v>
-      </c>
-      <c r="K103" s="34">
-        <v>2</v>
-      </c>
-      <c r="L103" s="34">
-        <v>3</v>
-      </c>
-      <c r="M103" s="34">
-        <v>2</v>
-      </c>
-      <c r="N103" s="34">
-        <v>2</v>
-      </c>
-      <c r="O103" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q103" s="34">
-        <v>0</v>
-      </c>
-      <c r="R103" s="34">
-        <v>0</v>
-      </c>
-      <c r="S103" s="34">
-        <v>1</v>
-      </c>
-      <c r="T103" s="34">
-        <v>1</v>
-      </c>
-      <c r="U103" s="34">
-        <v>0</v>
-      </c>
-      <c r="V103" s="34">
+      <c r="E103" s="32">
+        <v>2</v>
+      </c>
+      <c r="F103" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G103" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="32">
+        <v>3</v>
+      </c>
+      <c r="J103" s="32">
+        <v>2</v>
+      </c>
+      <c r="K103" s="32">
+        <v>2</v>
+      </c>
+      <c r="L103" s="32">
+        <v>3</v>
+      </c>
+      <c r="M103" s="32">
+        <v>2</v>
+      </c>
+      <c r="N103" s="32">
+        <v>2</v>
+      </c>
+      <c r="O103" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q103" s="32">
+        <v>0</v>
+      </c>
+      <c r="R103" s="32">
+        <v>0</v>
+      </c>
+      <c r="S103" s="32">
+        <v>1</v>
+      </c>
+      <c r="T103" s="32">
+        <v>1</v>
+      </c>
+      <c r="U103" s="32">
+        <v>0</v>
+      </c>
+      <c r="V103" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="33" t="s">
+      <c r="A104" s="31" t="s">
         <v>954</v>
       </c>
-      <c r="B104" s="33" t="s">
+      <c r="B104" s="31" t="s">
         <v>955</v>
       </c>
-      <c r="C104" s="33" t="s">
+      <c r="C104" s="31" t="s">
         <v>956</v>
       </c>
-      <c r="D104" s="33" t="s">
+      <c r="D104" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E104" s="34">
-        <v>2</v>
-      </c>
-      <c r="F104" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G104" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" s="34">
+      <c r="E104" s="32">
+        <v>2</v>
+      </c>
+      <c r="F104" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G104" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="32">
         <v>4</v>
       </c>
-      <c r="J104" s="34">
-        <v>1</v>
-      </c>
-      <c r="K104" s="34">
-        <v>1</v>
-      </c>
-      <c r="L104" s="34">
-        <v>3</v>
-      </c>
-      <c r="M104" s="34">
-        <v>2</v>
-      </c>
-      <c r="N104" s="34">
-        <v>1</v>
-      </c>
-      <c r="O104" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q104" s="34">
-        <v>0</v>
-      </c>
-      <c r="R104" s="34">
-        <v>1</v>
-      </c>
-      <c r="S104" s="34">
-        <v>1</v>
-      </c>
-      <c r="T104" s="34">
-        <v>1</v>
-      </c>
-      <c r="U104" s="34">
-        <v>0</v>
-      </c>
-      <c r="V104" s="34">
+      <c r="J104" s="32">
+        <v>1</v>
+      </c>
+      <c r="K104" s="32">
+        <v>1</v>
+      </c>
+      <c r="L104" s="32">
+        <v>3</v>
+      </c>
+      <c r="M104" s="32">
+        <v>2</v>
+      </c>
+      <c r="N104" s="32">
+        <v>1</v>
+      </c>
+      <c r="O104" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q104" s="32">
+        <v>0</v>
+      </c>
+      <c r="R104" s="32">
+        <v>1</v>
+      </c>
+      <c r="S104" s="32">
+        <v>1</v>
+      </c>
+      <c r="T104" s="32">
+        <v>1</v>
+      </c>
+      <c r="U104" s="32">
+        <v>0</v>
+      </c>
+      <c r="V104" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="33" t="s">
+      <c r="A105" s="31" t="s">
         <v>957</v>
       </c>
-      <c r="B105" s="33" t="s">
+      <c r="B105" s="31" t="s">
         <v>958</v>
       </c>
-      <c r="C105" s="33" t="s">
+      <c r="C105" s="31" t="s">
         <v>959</v>
       </c>
-      <c r="D105" s="33" t="s">
+      <c r="D105" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E105" s="34">
-        <v>1</v>
-      </c>
-      <c r="F105" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G105" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="34">
-        <v>2</v>
-      </c>
-      <c r="J105" s="34">
-        <v>3</v>
-      </c>
-      <c r="K105" s="34">
-        <v>2</v>
-      </c>
-      <c r="L105" s="34">
-        <v>3</v>
-      </c>
-      <c r="M105" s="34">
-        <v>3</v>
-      </c>
-      <c r="N105" s="34">
-        <v>1</v>
-      </c>
-      <c r="O105" s="34">
-        <v>3</v>
-      </c>
-      <c r="Q105" s="34">
-        <v>1</v>
-      </c>
-      <c r="R105" s="34">
-        <v>0</v>
-      </c>
-      <c r="S105" s="34">
-        <v>1</v>
-      </c>
-      <c r="T105" s="34">
-        <v>0</v>
-      </c>
-      <c r="U105" s="34">
-        <v>0</v>
-      </c>
-      <c r="V105" s="34">
+      <c r="E105" s="32">
+        <v>1</v>
+      </c>
+      <c r="F105" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G105" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="32">
+        <v>2</v>
+      </c>
+      <c r="J105" s="32">
+        <v>3</v>
+      </c>
+      <c r="K105" s="32">
+        <v>2</v>
+      </c>
+      <c r="L105" s="32">
+        <v>3</v>
+      </c>
+      <c r="M105" s="32">
+        <v>3</v>
+      </c>
+      <c r="N105" s="32">
+        <v>1</v>
+      </c>
+      <c r="O105" s="32">
+        <v>3</v>
+      </c>
+      <c r="Q105" s="32">
+        <v>1</v>
+      </c>
+      <c r="R105" s="32">
+        <v>0</v>
+      </c>
+      <c r="S105" s="32">
+        <v>1</v>
+      </c>
+      <c r="T105" s="32">
+        <v>0</v>
+      </c>
+      <c r="U105" s="32">
+        <v>0</v>
+      </c>
+      <c r="V105" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="33" t="s">
+      <c r="A106" s="31" t="s">
         <v>960</v>
       </c>
-      <c r="B106" s="33" t="s">
+      <c r="B106" s="31" t="s">
         <v>961</v>
       </c>
-      <c r="C106" s="33" t="s">
+      <c r="C106" s="31" t="s">
         <v>962</v>
       </c>
-      <c r="D106" s="33" t="s">
+      <c r="D106" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E106" s="34">
-        <v>1</v>
-      </c>
-      <c r="F106" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G106" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="34">
-        <v>3</v>
-      </c>
-      <c r="J106" s="34">
+      <c r="E106" s="32">
+        <v>1</v>
+      </c>
+      <c r="F106" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G106" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="32">
+        <v>3</v>
+      </c>
+      <c r="J106" s="32">
         <v>4</v>
       </c>
-      <c r="K106" s="34">
-        <v>2</v>
-      </c>
-      <c r="L106" s="34">
-        <v>3</v>
-      </c>
-      <c r="M106" s="34">
-        <v>1</v>
-      </c>
-      <c r="N106" s="34">
-        <v>3</v>
-      </c>
-      <c r="O106" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q106" s="34">
-        <v>0</v>
-      </c>
-      <c r="R106" s="34">
-        <v>0</v>
-      </c>
-      <c r="S106" s="34">
-        <v>1</v>
-      </c>
-      <c r="T106" s="34">
-        <v>0</v>
-      </c>
-      <c r="U106" s="34">
-        <v>1</v>
-      </c>
-      <c r="V106" s="34">
+      <c r="K106" s="32">
+        <v>2</v>
+      </c>
+      <c r="L106" s="32">
+        <v>3</v>
+      </c>
+      <c r="M106" s="32">
+        <v>1</v>
+      </c>
+      <c r="N106" s="32">
+        <v>3</v>
+      </c>
+      <c r="O106" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q106" s="32">
+        <v>0</v>
+      </c>
+      <c r="R106" s="32">
+        <v>0</v>
+      </c>
+      <c r="S106" s="32">
+        <v>1</v>
+      </c>
+      <c r="T106" s="32">
+        <v>0</v>
+      </c>
+      <c r="U106" s="32">
+        <v>1</v>
+      </c>
+      <c r="V106" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="33" t="s">
+      <c r="A107" s="31" t="s">
         <v>963</v>
       </c>
-      <c r="B107" s="33" t="s">
+      <c r="B107" s="31" t="s">
         <v>938</v>
       </c>
-      <c r="C107" s="33" t="s">
+      <c r="C107" s="31" t="s">
         <v>964</v>
       </c>
-      <c r="D107" s="33" t="s">
+      <c r="D107" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E107" s="34">
-        <v>1</v>
-      </c>
-      <c r="F107" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G107" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="34">
-        <v>3</v>
-      </c>
-      <c r="J107" s="34">
+      <c r="E107" s="32">
+        <v>1</v>
+      </c>
+      <c r="F107" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G107" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="32">
+        <v>3</v>
+      </c>
+      <c r="J107" s="32">
         <v>4</v>
       </c>
-      <c r="K107" s="34">
-        <v>2</v>
-      </c>
-      <c r="L107" s="34">
-        <v>3</v>
-      </c>
-      <c r="M107" s="34">
-        <v>2</v>
-      </c>
-      <c r="N107" s="34">
-        <v>1</v>
-      </c>
-      <c r="O107" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q107" s="34">
-        <v>0</v>
-      </c>
-      <c r="R107" s="34">
-        <v>0</v>
-      </c>
-      <c r="S107" s="34">
-        <v>1</v>
-      </c>
-      <c r="T107" s="34">
-        <v>1</v>
-      </c>
-      <c r="U107" s="34">
-        <v>0</v>
-      </c>
-      <c r="V107" s="34">
+      <c r="K107" s="32">
+        <v>2</v>
+      </c>
+      <c r="L107" s="32">
+        <v>3</v>
+      </c>
+      <c r="M107" s="32">
+        <v>2</v>
+      </c>
+      <c r="N107" s="32">
+        <v>1</v>
+      </c>
+      <c r="O107" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q107" s="32">
+        <v>0</v>
+      </c>
+      <c r="R107" s="32">
+        <v>0</v>
+      </c>
+      <c r="S107" s="32">
+        <v>1</v>
+      </c>
+      <c r="T107" s="32">
+        <v>1</v>
+      </c>
+      <c r="U107" s="32">
+        <v>0</v>
+      </c>
+      <c r="V107" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="33" t="s">
+      <c r="A108" s="31" t="s">
         <v>965</v>
       </c>
-      <c r="B108" s="33" t="s">
+      <c r="B108" s="31" t="s">
         <v>966</v>
       </c>
-      <c r="C108" s="33" t="s">
+      <c r="C108" s="31" t="s">
         <v>967</v>
       </c>
-      <c r="D108" s="33" t="s">
+      <c r="D108" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E108" s="34">
-        <v>1</v>
-      </c>
-      <c r="F108" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G108" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" s="34">
-        <v>1</v>
-      </c>
-      <c r="J108" s="34">
-        <v>3</v>
-      </c>
-      <c r="K108" s="34">
-        <v>2</v>
-      </c>
-      <c r="L108" s="34">
+      <c r="E108" s="32">
+        <v>1</v>
+      </c>
+      <c r="F108" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G108" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="32">
+        <v>1</v>
+      </c>
+      <c r="J108" s="32">
+        <v>3</v>
+      </c>
+      <c r="K108" s="32">
+        <v>2</v>
+      </c>
+      <c r="L108" s="32">
         <v>4</v>
       </c>
-      <c r="M108" s="34">
-        <v>1</v>
-      </c>
-      <c r="N108" s="34">
-        <v>1</v>
-      </c>
-      <c r="O108" s="34">
-        <v>1</v>
-      </c>
-      <c r="Q108" s="34">
-        <v>1</v>
-      </c>
-      <c r="R108" s="34">
-        <v>0</v>
-      </c>
-      <c r="S108" s="34">
-        <v>0</v>
-      </c>
-      <c r="T108" s="34">
-        <v>0</v>
-      </c>
-      <c r="U108" s="34">
-        <v>0</v>
-      </c>
-      <c r="V108" s="34">
+      <c r="M108" s="32">
+        <v>1</v>
+      </c>
+      <c r="N108" s="32">
+        <v>1</v>
+      </c>
+      <c r="O108" s="32">
+        <v>1</v>
+      </c>
+      <c r="Q108" s="32">
+        <v>1</v>
+      </c>
+      <c r="R108" s="32">
+        <v>0</v>
+      </c>
+      <c r="S108" s="32">
+        <v>0</v>
+      </c>
+      <c r="T108" s="32">
+        <v>0</v>
+      </c>
+      <c r="U108" s="32">
+        <v>0</v>
+      </c>
+      <c r="V108" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="33" t="s">
+      <c r="A109" s="31" t="s">
         <v>968</v>
       </c>
-      <c r="B109" s="33" t="s">
+      <c r="B109" s="31" t="s">
         <v>969</v>
       </c>
-      <c r="C109" s="33" t="s">
+      <c r="C109" s="31" t="s">
         <v>970</v>
       </c>
-      <c r="D109" s="33" t="s">
+      <c r="D109" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E109" s="34">
-        <v>1</v>
-      </c>
-      <c r="F109" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G109" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H109" s="34">
-        <v>3</v>
-      </c>
-      <c r="J109" s="34">
-        <v>2</v>
-      </c>
-      <c r="K109" s="34">
-        <v>2</v>
-      </c>
-      <c r="L109" s="34">
-        <v>3</v>
-      </c>
-      <c r="M109" s="34">
-        <v>2</v>
-      </c>
-      <c r="N109" s="34">
+      <c r="E109" s="32">
+        <v>1</v>
+      </c>
+      <c r="F109" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G109" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="32">
+        <v>3</v>
+      </c>
+      <c r="J109" s="32">
+        <v>2</v>
+      </c>
+      <c r="K109" s="32">
+        <v>2</v>
+      </c>
+      <c r="L109" s="32">
+        <v>3</v>
+      </c>
+      <c r="M109" s="32">
+        <v>2</v>
+      </c>
+      <c r="N109" s="32">
         <v>4</v>
       </c>
-      <c r="O109" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q109" s="34">
-        <v>0</v>
-      </c>
-      <c r="R109" s="34">
-        <v>0</v>
-      </c>
-      <c r="S109" s="34">
-        <v>1</v>
-      </c>
-      <c r="T109" s="34">
-        <v>1</v>
-      </c>
-      <c r="U109" s="34">
-        <v>0</v>
-      </c>
-      <c r="V109" s="34">
+      <c r="O109" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q109" s="32">
+        <v>0</v>
+      </c>
+      <c r="R109" s="32">
+        <v>0</v>
+      </c>
+      <c r="S109" s="32">
+        <v>1</v>
+      </c>
+      <c r="T109" s="32">
+        <v>1</v>
+      </c>
+      <c r="U109" s="32">
+        <v>0</v>
+      </c>
+      <c r="V109" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="33" t="s">
+      <c r="A110" s="31" t="s">
         <v>971</v>
       </c>
-      <c r="B110" s="33" t="s">
+      <c r="B110" s="31" t="s">
         <v>972</v>
       </c>
-      <c r="C110" s="33" t="s">
+      <c r="C110" s="31" t="s">
         <v>973</v>
       </c>
-      <c r="D110" s="33" t="s">
+      <c r="D110" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E110" s="34">
-        <v>1</v>
-      </c>
-      <c r="F110" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G110" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" s="34">
+      <c r="E110" s="32">
+        <v>1</v>
+      </c>
+      <c r="F110" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G110" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="32">
         <v>5</v>
       </c>
-      <c r="J110" s="34">
-        <v>3</v>
-      </c>
-      <c r="K110" s="34">
-        <v>1</v>
-      </c>
-      <c r="L110" s="34">
-        <v>3</v>
-      </c>
-      <c r="M110" s="34">
-        <v>2</v>
-      </c>
-      <c r="N110" s="34">
-        <v>1</v>
-      </c>
-      <c r="O110" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q110" s="34">
-        <v>1</v>
-      </c>
-      <c r="R110" s="34">
-        <v>1</v>
-      </c>
-      <c r="S110" s="34">
-        <v>1</v>
-      </c>
-      <c r="T110" s="34">
-        <v>1</v>
-      </c>
-      <c r="U110" s="34">
-        <v>0</v>
-      </c>
-      <c r="V110" s="34">
+      <c r="J110" s="32">
+        <v>3</v>
+      </c>
+      <c r="K110" s="32">
+        <v>1</v>
+      </c>
+      <c r="L110" s="32">
+        <v>3</v>
+      </c>
+      <c r="M110" s="32">
+        <v>2</v>
+      </c>
+      <c r="N110" s="32">
+        <v>1</v>
+      </c>
+      <c r="O110" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q110" s="32">
+        <v>1</v>
+      </c>
+      <c r="R110" s="32">
+        <v>1</v>
+      </c>
+      <c r="S110" s="32">
+        <v>1</v>
+      </c>
+      <c r="T110" s="32">
+        <v>1</v>
+      </c>
+      <c r="U110" s="32">
+        <v>0</v>
+      </c>
+      <c r="V110" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="33" t="s">
+      <c r="A111" s="31" t="s">
         <v>974</v>
       </c>
-      <c r="B111" s="33" t="s">
+      <c r="B111" s="31" t="s">
         <v>975</v>
       </c>
-      <c r="C111" s="33" t="s">
+      <c r="C111" s="31" t="s">
         <v>976</v>
       </c>
-      <c r="D111" s="33" t="s">
+      <c r="D111" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E111" s="34">
-        <v>1</v>
-      </c>
-      <c r="F111" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G111" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" s="34">
+      <c r="E111" s="32">
+        <v>1</v>
+      </c>
+      <c r="F111" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G111" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="32">
         <v>4</v>
       </c>
-      <c r="J111" s="34">
-        <v>3</v>
-      </c>
-      <c r="K111" s="34">
-        <v>1</v>
-      </c>
-      <c r="L111" s="34">
-        <v>3</v>
-      </c>
-      <c r="M111" s="34">
-        <v>2</v>
-      </c>
-      <c r="N111" s="34">
+      <c r="J111" s="32">
+        <v>3</v>
+      </c>
+      <c r="K111" s="32">
+        <v>1</v>
+      </c>
+      <c r="L111" s="32">
+        <v>3</v>
+      </c>
+      <c r="M111" s="32">
+        <v>2</v>
+      </c>
+      <c r="N111" s="32">
         <v>4</v>
       </c>
-      <c r="O111" s="34">
-        <v>1</v>
-      </c>
-      <c r="Q111" s="34">
-        <v>1</v>
-      </c>
-      <c r="R111" s="34">
-        <v>1</v>
-      </c>
-      <c r="S111" s="34">
-        <v>1</v>
-      </c>
-      <c r="T111" s="34">
-        <v>1</v>
-      </c>
-      <c r="U111" s="34">
-        <v>0</v>
-      </c>
-      <c r="V111" s="34">
+      <c r="O111" s="32">
+        <v>1</v>
+      </c>
+      <c r="Q111" s="32">
+        <v>1</v>
+      </c>
+      <c r="R111" s="32">
+        <v>1</v>
+      </c>
+      <c r="S111" s="32">
+        <v>1</v>
+      </c>
+      <c r="T111" s="32">
+        <v>1</v>
+      </c>
+      <c r="U111" s="32">
+        <v>0</v>
+      </c>
+      <c r="V111" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="33" t="s">
+      <c r="A112" s="31" t="s">
         <v>977</v>
       </c>
-      <c r="B112" s="33" t="s">
+      <c r="B112" s="31" t="s">
         <v>978</v>
       </c>
-      <c r="C112" s="33" t="s">
+      <c r="C112" s="31" t="s">
         <v>979</v>
       </c>
-      <c r="D112" s="33" t="s">
+      <c r="D112" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E112" s="34">
-        <v>1</v>
-      </c>
-      <c r="F112" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G112" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H112" s="34">
+      <c r="E112" s="32">
+        <v>1</v>
+      </c>
+      <c r="F112" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G112" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="32">
         <v>6</v>
       </c>
-      <c r="J112" s="34">
-        <v>3</v>
-      </c>
-      <c r="K112" s="34">
-        <v>1</v>
-      </c>
-      <c r="L112" s="34">
-        <v>3</v>
-      </c>
-      <c r="M112" s="34">
-        <v>2</v>
-      </c>
-      <c r="N112" s="34">
-        <v>3</v>
-      </c>
-      <c r="O112" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q112" s="34">
-        <v>1</v>
-      </c>
-      <c r="R112" s="34">
-        <v>1</v>
-      </c>
-      <c r="S112" s="34">
-        <v>1</v>
-      </c>
-      <c r="T112" s="34">
-        <v>1</v>
-      </c>
-      <c r="U112" s="34">
-        <v>1</v>
-      </c>
-      <c r="V112" s="34">
+      <c r="J112" s="32">
+        <v>3</v>
+      </c>
+      <c r="K112" s="32">
+        <v>1</v>
+      </c>
+      <c r="L112" s="32">
+        <v>3</v>
+      </c>
+      <c r="M112" s="32">
+        <v>2</v>
+      </c>
+      <c r="N112" s="32">
+        <v>3</v>
+      </c>
+      <c r="O112" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q112" s="32">
+        <v>1</v>
+      </c>
+      <c r="R112" s="32">
+        <v>1</v>
+      </c>
+      <c r="S112" s="32">
+        <v>1</v>
+      </c>
+      <c r="T112" s="32">
+        <v>1</v>
+      </c>
+      <c r="U112" s="32">
+        <v>1</v>
+      </c>
+      <c r="V112" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="33" t="s">
+      <c r="A113" s="31" t="s">
         <v>980</v>
       </c>
-      <c r="B113" s="33" t="s">
+      <c r="B113" s="31" t="s">
         <v>981</v>
       </c>
-      <c r="C113" s="33" t="s">
+      <c r="C113" s="31" t="s">
         <v>982</v>
       </c>
-      <c r="D113" s="33" t="s">
+      <c r="D113" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E113" s="34">
-        <v>1</v>
-      </c>
-      <c r="F113" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G113" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="34">
+      <c r="E113" s="32">
+        <v>1</v>
+      </c>
+      <c r="F113" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G113" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="32">
         <v>4</v>
       </c>
-      <c r="J113" s="34">
-        <v>3</v>
-      </c>
-      <c r="K113" s="34">
+      <c r="J113" s="32">
+        <v>3</v>
+      </c>
+      <c r="K113" s="32">
         <v>4</v>
       </c>
-      <c r="L113" s="34">
-        <v>3</v>
-      </c>
-      <c r="M113" s="34">
-        <v>2</v>
-      </c>
-      <c r="N113" s="34">
-        <v>2</v>
-      </c>
-      <c r="O113" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q113" s="34">
-        <v>1</v>
-      </c>
-      <c r="R113" s="34">
-        <v>0</v>
-      </c>
-      <c r="S113" s="34">
-        <v>1</v>
-      </c>
-      <c r="T113" s="34">
-        <v>1</v>
-      </c>
-      <c r="U113" s="34">
-        <v>0</v>
-      </c>
-      <c r="V113" s="34">
+      <c r="L113" s="32">
+        <v>3</v>
+      </c>
+      <c r="M113" s="32">
+        <v>2</v>
+      </c>
+      <c r="N113" s="32">
+        <v>2</v>
+      </c>
+      <c r="O113" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q113" s="32">
+        <v>1</v>
+      </c>
+      <c r="R113" s="32">
+        <v>0</v>
+      </c>
+      <c r="S113" s="32">
+        <v>1</v>
+      </c>
+      <c r="T113" s="32">
+        <v>1</v>
+      </c>
+      <c r="U113" s="32">
+        <v>0</v>
+      </c>
+      <c r="V113" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="33" t="s">
+      <c r="A114" s="31" t="s">
         <v>983</v>
       </c>
-      <c r="B114" s="33" t="s">
+      <c r="B114" s="31" t="s">
         <v>949</v>
       </c>
-      <c r="C114" s="33" t="s">
+      <c r="C114" s="31" t="s">
         <v>984</v>
       </c>
-      <c r="D114" s="33" t="s">
+      <c r="D114" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E114" s="34">
-        <v>1</v>
-      </c>
-      <c r="F114" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G114" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="34">
+      <c r="E114" s="32">
+        <v>1</v>
+      </c>
+      <c r="F114" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G114" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="32">
         <v>4</v>
       </c>
-      <c r="J114" s="34">
-        <v>3</v>
-      </c>
-      <c r="K114" s="34">
-        <v>2</v>
-      </c>
-      <c r="L114" s="34">
-        <v>3</v>
-      </c>
-      <c r="M114" s="34">
-        <v>3</v>
-      </c>
-      <c r="N114" s="34">
-        <v>3</v>
-      </c>
-      <c r="O114" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q114" s="34">
-        <v>1</v>
-      </c>
-      <c r="R114" s="34">
-        <v>0</v>
-      </c>
-      <c r="S114" s="34">
-        <v>1</v>
-      </c>
-      <c r="T114" s="34">
-        <v>0</v>
-      </c>
-      <c r="U114" s="34">
-        <v>1</v>
-      </c>
-      <c r="V114" s="34">
+      <c r="J114" s="32">
+        <v>3</v>
+      </c>
+      <c r="K114" s="32">
+        <v>2</v>
+      </c>
+      <c r="L114" s="32">
+        <v>3</v>
+      </c>
+      <c r="M114" s="32">
+        <v>3</v>
+      </c>
+      <c r="N114" s="32">
+        <v>3</v>
+      </c>
+      <c r="O114" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q114" s="32">
+        <v>1</v>
+      </c>
+      <c r="R114" s="32">
+        <v>0</v>
+      </c>
+      <c r="S114" s="32">
+        <v>1</v>
+      </c>
+      <c r="T114" s="32">
+        <v>0</v>
+      </c>
+      <c r="U114" s="32">
+        <v>1</v>
+      </c>
+      <c r="V114" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="33" t="s">
+      <c r="A115" s="31" t="s">
         <v>985</v>
       </c>
-      <c r="B115" s="33" t="s">
+      <c r="B115" s="31" t="s">
         <v>986</v>
       </c>
-      <c r="C115" s="33" t="s">
+      <c r="C115" s="31" t="s">
         <v>987</v>
       </c>
-      <c r="D115" s="33" t="s">
+      <c r="D115" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E115" s="34">
-        <v>1</v>
-      </c>
-      <c r="F115" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G115" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="34">
-        <v>3</v>
-      </c>
-      <c r="J115" s="34">
-        <v>2</v>
-      </c>
-      <c r="K115" s="34">
-        <v>2</v>
-      </c>
-      <c r="L115" s="34">
-        <v>2</v>
-      </c>
-      <c r="M115" s="34">
-        <v>2</v>
-      </c>
-      <c r="N115" s="34">
-        <v>3</v>
-      </c>
-      <c r="O115" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q115" s="34">
-        <v>0</v>
-      </c>
-      <c r="R115" s="34">
-        <v>0</v>
-      </c>
-      <c r="S115" s="34">
-        <v>0</v>
-      </c>
-      <c r="T115" s="34">
-        <v>1</v>
-      </c>
-      <c r="U115" s="34">
-        <v>1</v>
-      </c>
-      <c r="V115" s="34">
+      <c r="E115" s="32">
+        <v>1</v>
+      </c>
+      <c r="F115" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G115" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="32">
+        <v>3</v>
+      </c>
+      <c r="J115" s="32">
+        <v>2</v>
+      </c>
+      <c r="K115" s="32">
+        <v>2</v>
+      </c>
+      <c r="L115" s="32">
+        <v>2</v>
+      </c>
+      <c r="M115" s="32">
+        <v>2</v>
+      </c>
+      <c r="N115" s="32">
+        <v>3</v>
+      </c>
+      <c r="O115" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q115" s="32">
+        <v>0</v>
+      </c>
+      <c r="R115" s="32">
+        <v>0</v>
+      </c>
+      <c r="S115" s="32">
+        <v>0</v>
+      </c>
+      <c r="T115" s="32">
+        <v>1</v>
+      </c>
+      <c r="U115" s="32">
+        <v>1</v>
+      </c>
+      <c r="V115" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="33" t="s">
+      <c r="A116" s="31" t="s">
         <v>988</v>
       </c>
-      <c r="B116" s="33" t="s">
+      <c r="B116" s="31" t="s">
         <v>989</v>
       </c>
-      <c r="C116" s="33" t="s">
+      <c r="C116" s="31" t="s">
         <v>990</v>
       </c>
-      <c r="D116" s="33" t="s">
+      <c r="D116" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E116" s="34">
-        <v>1</v>
-      </c>
-      <c r="F116" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G116" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="34">
+      <c r="E116" s="32">
+        <v>1</v>
+      </c>
+      <c r="F116" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G116" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="32">
         <v>6</v>
       </c>
-      <c r="J116" s="34">
-        <v>3</v>
-      </c>
-      <c r="K116" s="34">
-        <v>1</v>
-      </c>
-      <c r="L116" s="34">
-        <v>3</v>
-      </c>
-      <c r="M116" s="34">
-        <v>2</v>
-      </c>
-      <c r="N116" s="34">
-        <v>3</v>
-      </c>
-      <c r="O116" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q116" s="34">
-        <v>1</v>
-      </c>
-      <c r="R116" s="34">
-        <v>1</v>
-      </c>
-      <c r="S116" s="34">
-        <v>1</v>
-      </c>
-      <c r="T116" s="34">
-        <v>1</v>
-      </c>
-      <c r="U116" s="34">
-        <v>1</v>
-      </c>
-      <c r="V116" s="34">
+      <c r="J116" s="32">
+        <v>3</v>
+      </c>
+      <c r="K116" s="32">
+        <v>1</v>
+      </c>
+      <c r="L116" s="32">
+        <v>3</v>
+      </c>
+      <c r="M116" s="32">
+        <v>2</v>
+      </c>
+      <c r="N116" s="32">
+        <v>3</v>
+      </c>
+      <c r="O116" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q116" s="32">
+        <v>1</v>
+      </c>
+      <c r="R116" s="32">
+        <v>1</v>
+      </c>
+      <c r="S116" s="32">
+        <v>1</v>
+      </c>
+      <c r="T116" s="32">
+        <v>1</v>
+      </c>
+      <c r="U116" s="32">
+        <v>1</v>
+      </c>
+      <c r="V116" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="33" t="s">
+      <c r="A117" s="31" t="s">
         <v>991</v>
       </c>
-      <c r="B117" s="33" t="s">
+      <c r="B117" s="31" t="s">
         <v>992</v>
       </c>
-      <c r="C117" s="33" t="s">
+      <c r="C117" s="31" t="s">
         <v>993</v>
       </c>
-      <c r="D117" s="33" t="s">
+      <c r="D117" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E117" s="34">
-        <v>1</v>
-      </c>
-      <c r="F117" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G117" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="34">
+      <c r="E117" s="32">
+        <v>1</v>
+      </c>
+      <c r="F117" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G117" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="32">
         <v>4</v>
       </c>
-      <c r="J117" s="34">
-        <v>3</v>
-      </c>
-      <c r="K117" s="34">
-        <v>1</v>
-      </c>
-      <c r="L117" s="34">
-        <v>3</v>
-      </c>
-      <c r="M117" s="34">
+      <c r="J117" s="32">
+        <v>3</v>
+      </c>
+      <c r="K117" s="32">
+        <v>1</v>
+      </c>
+      <c r="L117" s="32">
+        <v>3</v>
+      </c>
+      <c r="M117" s="32">
         <v>4</v>
       </c>
-      <c r="N117" s="34">
-        <v>1</v>
-      </c>
-      <c r="O117" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q117" s="34">
-        <v>1</v>
-      </c>
-      <c r="R117" s="34">
-        <v>1</v>
-      </c>
-      <c r="S117" s="34">
-        <v>1</v>
-      </c>
-      <c r="T117" s="34">
-        <v>0</v>
-      </c>
-      <c r="U117" s="34">
-        <v>0</v>
-      </c>
-      <c r="V117" s="34">
+      <c r="N117" s="32">
+        <v>1</v>
+      </c>
+      <c r="O117" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q117" s="32">
+        <v>1</v>
+      </c>
+      <c r="R117" s="32">
+        <v>1</v>
+      </c>
+      <c r="S117" s="32">
+        <v>1</v>
+      </c>
+      <c r="T117" s="32">
+        <v>0</v>
+      </c>
+      <c r="U117" s="32">
+        <v>0</v>
+      </c>
+      <c r="V117" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A118" s="33" t="s">
+      <c r="A118" s="31" t="s">
         <v>994</v>
       </c>
-      <c r="B118" s="33" t="s">
+      <c r="B118" s="31" t="s">
         <v>995</v>
       </c>
-      <c r="C118" s="33" t="s">
+      <c r="C118" s="31" t="s">
         <v>996</v>
       </c>
-      <c r="D118" s="33" t="s">
+      <c r="D118" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E118" s="34">
-        <v>1</v>
-      </c>
-      <c r="F118" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G118" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H118" s="34">
+      <c r="E118" s="32">
+        <v>1</v>
+      </c>
+      <c r="F118" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G118" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="32">
         <v>4</v>
       </c>
-      <c r="J118" s="34">
-        <v>3</v>
-      </c>
-      <c r="K118" s="34">
-        <v>1</v>
-      </c>
-      <c r="L118" s="34">
-        <v>3</v>
-      </c>
-      <c r="M118" s="34">
-        <v>3</v>
-      </c>
-      <c r="N118" s="34">
-        <v>1</v>
-      </c>
-      <c r="O118" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q118" s="34">
-        <v>1</v>
-      </c>
-      <c r="R118" s="34">
-        <v>1</v>
-      </c>
-      <c r="S118" s="34">
-        <v>1</v>
-      </c>
-      <c r="T118" s="34">
-        <v>0</v>
-      </c>
-      <c r="U118" s="34">
-        <v>0</v>
-      </c>
-      <c r="V118" s="34">
+      <c r="J118" s="32">
+        <v>3</v>
+      </c>
+      <c r="K118" s="32">
+        <v>1</v>
+      </c>
+      <c r="L118" s="32">
+        <v>3</v>
+      </c>
+      <c r="M118" s="32">
+        <v>3</v>
+      </c>
+      <c r="N118" s="32">
+        <v>1</v>
+      </c>
+      <c r="O118" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q118" s="32">
+        <v>1</v>
+      </c>
+      <c r="R118" s="32">
+        <v>1</v>
+      </c>
+      <c r="S118" s="32">
+        <v>1</v>
+      </c>
+      <c r="T118" s="32">
+        <v>0</v>
+      </c>
+      <c r="U118" s="32">
+        <v>0</v>
+      </c>
+      <c r="V118" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A119" s="33" t="s">
+      <c r="A119" s="31" t="s">
         <v>997</v>
       </c>
-      <c r="B119" s="33" t="s">
+      <c r="B119" s="31" t="s">
         <v>998</v>
       </c>
-      <c r="C119" s="33" t="s">
+      <c r="C119" s="31" t="s">
         <v>999</v>
       </c>
-      <c r="D119" s="33" t="s">
+      <c r="D119" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E119" s="34">
-        <v>1</v>
-      </c>
-      <c r="F119" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G119" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H119" s="34">
+      <c r="E119" s="32">
+        <v>1</v>
+      </c>
+      <c r="F119" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G119" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="32">
         <v>4</v>
       </c>
-      <c r="J119" s="34">
-        <v>2</v>
-      </c>
-      <c r="K119" s="34">
-        <v>1</v>
-      </c>
-      <c r="L119" s="34">
-        <v>3</v>
-      </c>
-      <c r="M119" s="34">
-        <v>2</v>
-      </c>
-      <c r="N119" s="34">
-        <v>1</v>
-      </c>
-      <c r="O119" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q119" s="34">
-        <v>0</v>
-      </c>
-      <c r="R119" s="34">
-        <v>1</v>
-      </c>
-      <c r="S119" s="34">
-        <v>1</v>
-      </c>
-      <c r="T119" s="34">
-        <v>1</v>
-      </c>
-      <c r="U119" s="34">
-        <v>0</v>
-      </c>
-      <c r="V119" s="34">
+      <c r="J119" s="32">
+        <v>2</v>
+      </c>
+      <c r="K119" s="32">
+        <v>1</v>
+      </c>
+      <c r="L119" s="32">
+        <v>3</v>
+      </c>
+      <c r="M119" s="32">
+        <v>2</v>
+      </c>
+      <c r="N119" s="32">
+        <v>1</v>
+      </c>
+      <c r="O119" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q119" s="32">
+        <v>0</v>
+      </c>
+      <c r="R119" s="32">
+        <v>1</v>
+      </c>
+      <c r="S119" s="32">
+        <v>1</v>
+      </c>
+      <c r="T119" s="32">
+        <v>1</v>
+      </c>
+      <c r="U119" s="32">
+        <v>0</v>
+      </c>
+      <c r="V119" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A120" s="33" t="s">
+      <c r="A120" s="31" t="s">
         <v>1000</v>
       </c>
-      <c r="B120" s="33" t="s">
+      <c r="B120" s="31" t="s">
         <v>1001</v>
       </c>
-      <c r="C120" s="33" t="s">
+      <c r="C120" s="31" t="s">
         <v>1002</v>
       </c>
-      <c r="D120" s="33" t="s">
+      <c r="D120" s="31" t="s">
         <v>928</v>
       </c>
-      <c r="E120" s="34">
-        <v>1</v>
-      </c>
-      <c r="F120" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G120" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H120" s="34">
+      <c r="E120" s="32">
+        <v>1</v>
+      </c>
+      <c r="F120" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G120" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="32">
         <v>6</v>
       </c>
-      <c r="J120" s="34">
-        <v>3</v>
-      </c>
-      <c r="K120" s="34">
-        <v>1</v>
-      </c>
-      <c r="L120" s="34">
-        <v>3</v>
-      </c>
-      <c r="M120" s="34">
-        <v>2</v>
-      </c>
-      <c r="N120" s="34">
-        <v>3</v>
-      </c>
-      <c r="O120" s="34">
-        <v>2</v>
-      </c>
-      <c r="Q120" s="34">
-        <v>1</v>
-      </c>
-      <c r="R120" s="34">
-        <v>1</v>
-      </c>
-      <c r="S120" s="34">
-        <v>1</v>
-      </c>
-      <c r="T120" s="34">
-        <v>1</v>
-      </c>
-      <c r="U120" s="34">
-        <v>1</v>
-      </c>
-      <c r="V120" s="34">
+      <c r="J120" s="32">
+        <v>3</v>
+      </c>
+      <c r="K120" s="32">
+        <v>1</v>
+      </c>
+      <c r="L120" s="32">
+        <v>3</v>
+      </c>
+      <c r="M120" s="32">
+        <v>2</v>
+      </c>
+      <c r="N120" s="32">
+        <v>3</v>
+      </c>
+      <c r="O120" s="32">
+        <v>2</v>
+      </c>
+      <c r="Q120" s="32">
+        <v>1</v>
+      </c>
+      <c r="R120" s="32">
+        <v>1</v>
+      </c>
+      <c r="S120" s="32">
+        <v>1</v>
+      </c>
+      <c r="T120" s="32">
+        <v>1</v>
+      </c>
+      <c r="U120" s="32">
+        <v>1</v>
+      </c>
+      <c r="V120" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H121" s="41">
+      <c r="H121" s="39">
         <f>AVERAGE(Scores[MC])</f>
-        <v>3.672268907563025</v>
+        <v>3.7731092436974789</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:O120">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Q2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12570,7 +12554,7 @@
         <v>801</v>
       </c>
       <c r="E6" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>821</v>
@@ -12604,7 +12588,7 @@
       </c>
       <c r="P6" s="18">
         <f t="array" ref="P6">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A6,Scores[#Headers],0)))</f>
-        <v>0.26050420168067229</v>
+        <v>0.36134453781512604</v>
       </c>
       <c r="Q6" s="16"/>
     </row>
@@ -12693,7 +12677,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034BA313-8A5F-0646-A667-B76D8BE8D570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDF4E09-BA8B-6A46-A101-51047F14F5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="1010">
   <si>
     <t>Model</t>
   </si>
@@ -3048,13 +3048,34 @@
   </si>
   <si>
     <t>WILLIAMS</t>
+  </si>
+  <si>
+    <t>Qamar Galmen</t>
+  </si>
+  <si>
+    <t>NYAIRE WILLIS</t>
+  </si>
+  <si>
+    <t>QAMAR</t>
+  </si>
+  <si>
+    <t>QAMAR GALMEN</t>
+  </si>
+  <si>
+    <t>GALMEN</t>
+  </si>
+  <si>
+    <t>NYAIRE</t>
+  </si>
+  <si>
+    <t>WILLIS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3130,6 +3151,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3184,7 +3216,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3319,6 +3351,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3328,6 +3361,60 @@
     <cellStyle name="Percent 2" xfId="4" xr:uid="{E6DE421D-B06A-DB4D-BCE7-D696BB42B3F4}"/>
   </cellStyles>
   <dxfs count="76">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF3F4A58"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3348,6 +3435,216 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF3F4A58"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF3F4A58"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3489,270 +3786,6 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF3F4A58"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF3F4A58"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF3F4A58"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFF5F8FB"/>
@@ -3859,57 +3892,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V121" totalsRowCount="1" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V121" totalsRowCount="1" headerRowDxfId="48" dataDxfId="47" totalsRowDxfId="46">
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="68" totalsRowDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="66" totalsRowDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="64" totalsRowDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="45" totalsRowDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="44" totalsRowDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="43" totalsRowDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="42" totalsRowDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="41" totalsRowDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="5" totalsRowDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="4" totalsRowDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="40" totalsRowDxfId="20">
       <totalsRowFormula>AVERAGE(Scores[MC])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="36" totalsRowDxfId="35"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="39" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="38" totalsRowDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="37" totalsRowDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="36" totalsRowDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="35" totalsRowDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="34" totalsRowDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="33" totalsRowDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="32" totalsRowDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="31" totalsRowDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="30" totalsRowDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="29" totalsRowDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="28" totalsRowDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="27" totalsRowDxfId="7"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="26" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="58"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="57"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="55"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="54"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="53"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3919,7 +3952,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3930,7 +3963,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3942,7 +3975,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="49">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4173,7 +4206,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:V121"/>
+  <dimension ref="A1:X121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="22.6640625" style="30" customWidth="1"/>
@@ -4189,7 +4222,7 @@
     <col min="23" max="16384" width="12.6640625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="29" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:24" s="29" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="15" t="s">
         <v>9</v>
       </c>
@@ -4257,7 +4290,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>70</v>
       </c>
@@ -4329,8 +4362,11 @@
         <f>IF(O2=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X2" s="40" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>82</v>
       </c>
@@ -4402,8 +4438,11 @@
         <f>IF(O3=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X3" s="40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>112</v>
       </c>
@@ -4475,8 +4514,11 @@
         <f>IF(O4=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X4" s="40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>161</v>
       </c>
@@ -4548,8 +4590,11 @@
         <f>IF(O5=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X5" s="40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>245</v>
       </c>
@@ -4621,8 +4666,11 @@
         <f>IF(O6=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X6" s="40" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>314</v>
       </c>
@@ -4694,8 +4742,11 @@
         <f>IF(O7=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X7" s="40" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>367</v>
       </c>
@@ -4767,8 +4818,11 @@
         <f>IF(O8=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X8" s="40" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>432</v>
       </c>
@@ -4840,8 +4894,11 @@
         <f>IF(O9=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X9" s="40" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>473</v>
       </c>
@@ -4863,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="2"/>
@@ -4913,8 +4970,11 @@
         <f>IF(O10=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X10" s="40" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>523</v>
       </c>
@@ -4984,8 +5044,11 @@
         <f>IF(O11=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X11" s="40" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>575</v>
       </c>
@@ -5057,8 +5120,11 @@
         <f>IF(O12=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X12" s="40" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>614</v>
       </c>
@@ -5130,8 +5196,11 @@
         <f>IF(O13=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X13" s="40" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>678</v>
       </c>
@@ -5153,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="2"/>
@@ -5203,8 +5272,11 @@
         <f>IF(O14=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X14" s="40" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>719</v>
       </c>
@@ -5276,8 +5348,11 @@
         <f>IF(O15=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X15" s="40" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>720</v>
       </c>
@@ -5349,8 +5424,11 @@
         <f>IF(O16=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X16" s="40" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>721</v>
       </c>
@@ -5422,8 +5500,11 @@
         <f>IF(O17=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X17" s="40" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
         <v>722</v>
       </c>
@@ -5445,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="2"/>
@@ -5495,8 +5576,11 @@
         <f>IF(O18=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X18" s="40" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>723</v>
       </c>
@@ -5518,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="2"/>
@@ -5568,8 +5652,11 @@
         <f>IF(O19=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X19" s="40" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
         <v>724</v>
       </c>
@@ -5629,8 +5716,11 @@
         <f>IF(O20=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X20" s="40" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>725</v>
       </c>
@@ -5700,8 +5790,11 @@
         <f>IF(O21=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X21" s="40" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>726</v>
       </c>
@@ -5773,8 +5866,11 @@
         <f>IF(O22=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X22" s="40" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>727</v>
       </c>
@@ -5846,8 +5942,11 @@
         <f>IF(O23=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X23" s="40" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>728</v>
       </c>
@@ -5919,8 +6018,11 @@
         <f>IF(O24=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X24" s="40" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>729</v>
       </c>
@@ -5942,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="2"/>
@@ -5992,8 +6094,11 @@
         <f>IF(O25=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X25" s="40" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
         <v>730</v>
       </c>
@@ -6012,7 +6117,7 @@
         <v>8</v>
       </c>
       <c r="F26" s="22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="24" t="b">
         <v>0</v>
@@ -6065,8 +6170,11 @@
         <f>IF(O26=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X26" s="40" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>731</v>
       </c>
@@ -6088,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="2"/>
@@ -6138,8 +6246,11 @@
         <f>IF(O27=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X27" s="40" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
         <v>732</v>
       </c>
@@ -6211,8 +6322,11 @@
         <f>IF(O28=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X28" s="40" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>733</v>
       </c>
@@ -6284,8 +6398,11 @@
         <f>IF(O29=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X29" s="40" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
         <v>734</v>
       </c>
@@ -6355,8 +6472,11 @@
         <f>IF(O30=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X30" s="40" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
         <v>735</v>
       </c>
@@ -6375,7 +6495,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="24" t="b">
         <v>0</v>
@@ -6428,8 +6548,11 @@
         <f>IF(O31=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X31" s="40" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
         <v>736</v>
       </c>
@@ -6451,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="2"/>
@@ -6501,8 +6624,11 @@
         <f>IF(O32=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X32" s="40" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
         <v>737</v>
       </c>
@@ -6574,8 +6700,11 @@
         <f>IF(O33=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X33" s="40" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
         <v>738</v>
       </c>
@@ -6594,7 +6723,7 @@
         <v>3</v>
       </c>
       <c r="F34" s="22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="24" t="b">
         <v>0</v>
@@ -6647,8 +6776,11 @@
         <f>IF(O34=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X34" s="40" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>739</v>
       </c>
@@ -6720,8 +6852,11 @@
         <f>IF(O35=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X35" s="40" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
         <v>740</v>
       </c>
@@ -6793,8 +6928,11 @@
         <f>IF(O36=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X36" s="40" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
         <v>741</v>
       </c>
@@ -6866,8 +7004,11 @@
         <f>IF(O37=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X37" s="40" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>742</v>
       </c>
@@ -6939,8 +7080,11 @@
         <f>IF(O38=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X38" s="40" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>743</v>
       </c>
@@ -7012,8 +7156,11 @@
         <f>IF(O39=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X39" s="40" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
         <v>744</v>
       </c>
@@ -7085,8 +7232,11 @@
         <f>IF(O40=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X40" s="40" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
         <v>745</v>
       </c>
@@ -7158,8 +7308,11 @@
         <f>IF(O41=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X41" s="40" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
         <v>746</v>
       </c>
@@ -7231,8 +7384,11 @@
         <f>IF(O42=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X42" s="40" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
         <v>747</v>
       </c>
@@ -7304,8 +7460,11 @@
         <f>IF(O43=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X43" s="40" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
         <v>748</v>
       </c>
@@ -7377,8 +7536,11 @@
         <f>IF(O44=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X44" s="40" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
         <v>749</v>
       </c>
@@ -7400,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="2"/>
@@ -7442,8 +7604,11 @@
         <f>IF(O45=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X45" s="40" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
         <v>750</v>
       </c>
@@ -7515,16 +7680,19 @@
         <f>IF(O46=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X46" s="40" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
-        <v>838</v>
+        <v>1006</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>839</v>
+        <v>1005</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>840</v>
+        <v>1007</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>48</v>
@@ -7539,14 +7707,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="26"/>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="1">
         <v>3</v>
@@ -7554,35 +7722,50 @@
       <c r="M47" s="1">
         <v>2</v>
       </c>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
+      <c r="N47" s="1">
+        <v>2</v>
+      </c>
+      <c r="O47" s="1">
+        <v>1</v>
+      </c>
       <c r="P47" s="28"/>
       <c r="Q47" s="1">
+        <f>IF(J47=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="R47" s="1">
-        <v>0</v>
+        <f>IF(K47=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
       </c>
       <c r="S47" s="1">
+        <f>IF(L47=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T47" s="1">
+        <f>IF(M47=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U47" s="1">
+        <f>IF(N47=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="V47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C48" s="3" t="e">
-        <v>#VALUE!</v>
+        <f>IF(O47=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X47" s="40" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>840</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
@@ -7597,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" s="26"/>
       <c r="J48" s="1">
@@ -7607,17 +7790,13 @@
         <v>2</v>
       </c>
       <c r="L48" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M48" s="1">
         <v>2</v>
       </c>
-      <c r="N48" s="1">
-        <v>3</v>
-      </c>
-      <c r="O48" s="1">
-        <v>2</v>
-      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
       <c r="P48" s="28"/>
       <c r="Q48" s="1">
         <v>0</v>
@@ -7626,28 +7805,25 @@
         <v>0</v>
       </c>
       <c r="S48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="1">
         <v>1</v>
       </c>
       <c r="U48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>842</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X48" s="40" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
         <v>48</v>
       </c>
@@ -7661,56 +7837,57 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I49" s="26"/>
       <c r="J49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M49" s="1">
         <v>2</v>
       </c>
       <c r="N49" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O49" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P49" s="28"/>
       <c r="Q49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="1">
         <v>1</v>
       </c>
       <c r="U49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X49" s="40"/>
+    </row>
+    <row r="50" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>48</v>
@@ -7725,33 +7902,33 @@
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" s="26"/>
       <c r="J50" s="1">
+        <v>3</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>3</v>
+      </c>
+      <c r="M50" s="1">
+        <v>2</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1</v>
+      </c>
+      <c r="O50" s="1">
         <v>4</v>
-      </c>
-      <c r="K50" s="1">
-        <v>4</v>
-      </c>
-      <c r="L50" s="1">
-        <v>3</v>
-      </c>
-      <c r="M50" s="1">
-        <v>2</v>
-      </c>
-      <c r="N50" s="1">
-        <v>1</v>
-      </c>
-      <c r="O50" s="1">
-        <v>2</v>
       </c>
       <c r="P50" s="28"/>
       <c r="Q50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="1">
         <v>1</v>
@@ -7763,18 +7940,21 @@
         <v>0</v>
       </c>
       <c r="V50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X50" s="20" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>48</v>
@@ -7829,16 +8009,19 @@
       <c r="V51" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X51" s="40" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>48</v>
@@ -7853,17 +8036,17 @@
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" s="26"/>
       <c r="J52" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L52" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M52" s="1">
         <v>2</v>
@@ -7882,7 +8065,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" s="1">
         <v>1</v>
@@ -7893,16 +8076,19 @@
       <c r="V52" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X52" s="40" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>48</v>
@@ -7917,17 +8103,17 @@
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53" s="26"/>
       <c r="J53" s="1">
         <v>2</v>
       </c>
       <c r="K53" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M53" s="1">
         <v>2</v>
@@ -7943,10 +8129,10 @@
         <v>0</v>
       </c>
       <c r="R53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" s="1">
         <v>1</v>
@@ -7957,16 +8143,19 @@
       <c r="V53" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X53" s="40" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -7981,11 +8170,11 @@
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I54" s="26"/>
       <c r="J54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" s="1">
         <v>1</v>
@@ -8004,7 +8193,7 @@
       </c>
       <c r="P54" s="28"/>
       <c r="Q54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="1">
         <v>1</v>
@@ -8021,16 +8210,19 @@
       <c r="V54" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X54" s="40" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>48</v>
@@ -8061,7 +8253,7 @@
         <v>2</v>
       </c>
       <c r="N55" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O55" s="1">
         <v>2</v>
@@ -8085,16 +8277,19 @@
       <c r="V55" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X55" s="40" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>48</v>
@@ -8116,16 +8311,16 @@
         <v>3</v>
       </c>
       <c r="K56" s="1">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1">
+        <v>3</v>
+      </c>
+      <c r="M56" s="1">
+        <v>2</v>
+      </c>
+      <c r="N56" s="1">
         <v>4</v>
-      </c>
-      <c r="L56" s="1">
-        <v>3</v>
-      </c>
-      <c r="M56" s="1">
-        <v>2</v>
-      </c>
-      <c r="N56" s="1">
-        <v>3</v>
       </c>
       <c r="O56" s="1">
         <v>2</v>
@@ -8135,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="R56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="1">
         <v>1</v>
@@ -8144,21 +8339,24 @@
         <v>1</v>
       </c>
       <c r="U56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X56" s="40" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
@@ -8173,7 +8371,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I57" s="26"/>
       <c r="J57" s="1">
@@ -8189,7 +8387,7 @@
         <v>2</v>
       </c>
       <c r="N57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O57" s="1">
         <v>2</v>
@@ -8208,21 +8406,24 @@
         <v>1</v>
       </c>
       <c r="U57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X57" s="40" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>48</v>
@@ -8237,14 +8438,14 @@
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I58" s="26"/>
       <c r="J58" s="1">
         <v>3</v>
       </c>
       <c r="K58" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L58" s="1">
         <v>3</v>
@@ -8253,7 +8454,7 @@
         <v>2</v>
       </c>
       <c r="N58" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O58" s="1">
         <v>2</v>
@@ -8263,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="R58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" s="1">
         <v>1</v>
@@ -8277,16 +8478,19 @@
       <c r="V58" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X58" s="40" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>48</v>
@@ -8301,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59" s="26"/>
       <c r="J59" s="1">
@@ -8316,8 +8520,12 @@
       <c r="M59" s="1">
         <v>2</v>
       </c>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
+      <c r="N59" s="1">
+        <v>4</v>
+      </c>
+      <c r="O59" s="1">
+        <v>2</v>
+      </c>
       <c r="P59" s="28"/>
       <c r="Q59" s="1">
         <v>1</v>
@@ -8335,18 +8543,21 @@
         <v>0</v>
       </c>
       <c r="V59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X59" s="40" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
@@ -8361,14 +8572,14 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" s="26"/>
       <c r="J60" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K60" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L60" s="1">
         <v>3</v>
@@ -8376,18 +8587,14 @@
       <c r="M60" s="1">
         <v>2</v>
       </c>
-      <c r="N60" s="1">
-        <v>2</v>
-      </c>
-      <c r="O60" s="1">
-        <v>2</v>
-      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
       <c r="P60" s="28"/>
       <c r="Q60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="1">
         <v>1</v>
@@ -8399,18 +8606,21 @@
         <v>0</v>
       </c>
       <c r="V60" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X60" s="40" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>48</v>
@@ -8429,19 +8639,19 @@
       </c>
       <c r="I61" s="26"/>
       <c r="J61" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M61" s="1">
         <v>2</v>
       </c>
       <c r="N61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61" s="1">
         <v>2</v>
@@ -8451,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="R61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="1">
         <v>1</v>
@@ -8465,16 +8675,19 @@
       <c r="V61" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X61" s="40" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>48</v>
@@ -8489,17 +8702,17 @@
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I62" s="26"/>
       <c r="J62" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L62" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M62" s="1">
         <v>2</v>
@@ -8512,13 +8725,13 @@
       </c>
       <c r="P62" s="28"/>
       <c r="Q62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" s="1">
         <v>1</v>
@@ -8529,16 +8742,19 @@
       <c r="V62" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X62" s="40" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>48</v>
@@ -8553,14 +8769,14 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I63" s="26"/>
       <c r="J63" s="1">
         <v>3</v>
       </c>
       <c r="K63" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L63" s="1">
         <v>3</v>
@@ -8579,7 +8795,7 @@
         <v>1</v>
       </c>
       <c r="R63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" s="1">
         <v>1</v>
@@ -8593,16 +8809,19 @@
       <c r="V63" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X63" s="40" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>48</v>
@@ -8617,7 +8836,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I64" s="26"/>
       <c r="J64" s="1">
@@ -8627,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="L64" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M64" s="1">
         <v>2</v>
@@ -8636,7 +8855,7 @@
         <v>1</v>
       </c>
       <c r="O64" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P64" s="28"/>
       <c r="Q64" s="1">
@@ -8646,7 +8865,7 @@
         <v>1</v>
       </c>
       <c r="S64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="1">
         <v>1</v>
@@ -8655,18 +8874,21 @@
         <v>0</v>
       </c>
       <c r="V64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X64" s="40" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>48</v>
@@ -8681,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I65" s="26"/>
       <c r="J65" s="1">
@@ -8691,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="L65" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M65" s="1">
         <v>2</v>
@@ -8700,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="O65" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P65" s="28"/>
       <c r="Q65" s="1">
@@ -8710,7 +8932,7 @@
         <v>1</v>
       </c>
       <c r="S65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" s="1">
         <v>1</v>
@@ -8719,18 +8941,21 @@
         <v>0</v>
       </c>
       <c r="V65" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X65" s="40" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>48</v>
@@ -8761,7 +8986,7 @@
         <v>2</v>
       </c>
       <c r="N66" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O66" s="1">
         <v>2</v>
@@ -8785,20 +9010,25 @@
       <c r="V66" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C67" s="3" t="e">
-        <v>#VALUE!</v>
+      <c r="X66" s="40" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>875</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E67" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67" s="22" t="b">
         <v>0</v>
@@ -8823,7 +9053,7 @@
         <v>2</v>
       </c>
       <c r="N67" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O67" s="1">
         <v>2</v>
@@ -8847,18 +9077,21 @@
       <c r="V67" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="X67" s="40" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E68" s="1">
@@ -8871,14 +9104,14 @@
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I68" s="26"/>
       <c r="J68" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L68" s="1">
         <v>3</v>
@@ -8887,19 +9120,17 @@
         <v>2</v>
       </c>
       <c r="N68" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O68" s="1">
         <v>2</v>
       </c>
-      <c r="P68" s="28">
-        <v>3</v>
-      </c>
+      <c r="P68" s="28"/>
       <c r="Q68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" s="1">
         <v>1</v>
@@ -8913,16 +9144,19 @@
       <c r="V68" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X68" s="40" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>48</v>
@@ -8937,11 +9171,11 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I69" s="26"/>
       <c r="J69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" s="1">
         <v>4</v>
@@ -8953,16 +9187,16 @@
         <v>2</v>
       </c>
       <c r="N69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O69" s="1">
         <v>2</v>
       </c>
       <c r="P69" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="1">
         <v>0</v>
@@ -8974,21 +9208,24 @@
         <v>1</v>
       </c>
       <c r="U69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V69" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X69" s="40" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>48</v>
@@ -9003,14 +9240,14 @@
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I70" s="26"/>
       <c r="J70" s="1">
         <v>3</v>
       </c>
       <c r="K70" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L70" s="1">
         <v>3</v>
@@ -9025,13 +9262,13 @@
         <v>2</v>
       </c>
       <c r="P70" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="1">
         <v>1</v>
       </c>
       <c r="R70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" s="1">
         <v>1</v>
@@ -9045,16 +9282,19 @@
       <c r="V70" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X70" s="40" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>48</v>
@@ -9066,17 +9306,17 @@
         <v>0</v>
       </c>
       <c r="G71" s="24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I71" s="26"/>
       <c r="J71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="1">
         <v>3</v>
@@ -9084,16 +9324,20 @@
       <c r="M71" s="1">
         <v>2</v>
       </c>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
+      <c r="N71" s="1">
+        <v>3</v>
+      </c>
+      <c r="O71" s="1">
+        <v>2</v>
+      </c>
       <c r="P71" s="28">
         <v>3</v>
       </c>
       <c r="Q71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" s="1">
         <v>1</v>
@@ -9102,21 +9346,24 @@
         <v>1</v>
       </c>
       <c r="U71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X71" s="40" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>48</v>
@@ -9128,17 +9375,17 @@
         <v>0</v>
       </c>
       <c r="G72" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I72" s="26"/>
       <c r="J72" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K72" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L72" s="1">
         <v>3</v>
@@ -9146,17 +9393,13 @@
       <c r="M72" s="1">
         <v>2</v>
       </c>
-      <c r="N72" s="1">
-        <v>4</v>
-      </c>
-      <c r="O72" s="1">
-        <v>2</v>
-      </c>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
       <c r="P72" s="28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="1">
         <v>0</v>
@@ -9171,18 +9414,21 @@
         <v>0</v>
       </c>
       <c r="V72" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X72" s="40" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>48</v>
@@ -9194,17 +9440,17 @@
         <v>0</v>
       </c>
       <c r="G73" s="24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I73" s="26"/>
       <c r="J73" s="1">
         <v>3</v>
       </c>
       <c r="K73" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L73" s="1">
         <v>3</v>
@@ -9213,13 +9459,13 @@
         <v>2</v>
       </c>
       <c r="N73" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O73" s="1">
         <v>2</v>
       </c>
       <c r="P73" s="28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q73" s="1">
         <v>1</v>
@@ -9234,21 +9480,24 @@
         <v>1</v>
       </c>
       <c r="U73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X73" s="40" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>48</v>
@@ -9260,20 +9509,20 @@
         <v>0</v>
       </c>
       <c r="G74" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I74" s="26"/>
       <c r="J74" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K74" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" s="1">
         <v>2</v>
@@ -9285,16 +9534,16 @@
         <v>2</v>
       </c>
       <c r="P74" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="1">
         <v>0</v>
       </c>
       <c r="S74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="1">
         <v>1</v>
@@ -9305,16 +9554,19 @@
       <c r="V74" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X74" s="40" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>48</v>
@@ -9333,54 +9585,57 @@
       </c>
       <c r="I75" s="26"/>
       <c r="J75" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L75" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M75" s="1">
         <v>2</v>
       </c>
       <c r="N75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O75" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P75" s="28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="1">
         <v>0</v>
       </c>
       <c r="S75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" s="1">
         <v>1</v>
       </c>
       <c r="U75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X75" s="40" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>48</v>
@@ -9395,15 +9650,15 @@
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" s="26"/>
       <c r="J76" s="1">
+        <v>3</v>
+      </c>
+      <c r="K76" s="1">
         <v>4</v>
       </c>
-      <c r="K76" s="1">
-        <v>1</v>
-      </c>
       <c r="L76" s="1">
         <v>3</v>
       </c>
@@ -9411,19 +9666,19 @@
         <v>2</v>
       </c>
       <c r="N76" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P76" s="28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q76" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" s="1">
         <v>1</v>
@@ -9435,18 +9690,21 @@
         <v>0</v>
       </c>
       <c r="V76" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X76" s="40" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>48</v>
@@ -9461,11 +9719,11 @@
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I77" s="26"/>
       <c r="J77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77" s="1">
         <v>1</v>
@@ -9477,16 +9735,16 @@
         <v>2</v>
       </c>
       <c r="N77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O77" s="1">
         <v>2</v>
       </c>
       <c r="P77" s="28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" s="1">
         <v>1</v>
@@ -9498,21 +9756,24 @@
         <v>1</v>
       </c>
       <c r="U77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V77" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X77" s="40" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>48</v>
@@ -9569,16 +9830,19 @@
       <c r="V78" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X78" s="40" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>48</v>
@@ -9593,14 +9857,14 @@
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I79" s="26"/>
       <c r="J79" s="1">
         <v>3</v>
       </c>
       <c r="K79" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79" s="1">
         <v>3</v>
@@ -9615,13 +9879,13 @@
         <v>2</v>
       </c>
       <c r="P79" s="28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q79" s="1">
         <v>1</v>
       </c>
       <c r="R79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" s="1">
         <v>1</v>
@@ -9635,16 +9899,19 @@
       <c r="V79" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X79" s="40" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>48</v>
@@ -9659,14 +9926,14 @@
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I80" s="26"/>
       <c r="J80" s="1">
         <v>3</v>
       </c>
       <c r="K80" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L80" s="1">
         <v>3</v>
@@ -9675,7 +9942,7 @@
         <v>2</v>
       </c>
       <c r="N80" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O80" s="1">
         <v>2</v>
@@ -9696,21 +9963,24 @@
         <v>1</v>
       </c>
       <c r="U80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X80" s="40" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>48</v>
@@ -9722,61 +9992,64 @@
         <v>0</v>
       </c>
       <c r="G81" s="24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I81" s="26"/>
       <c r="J81" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K81" s="1">
         <v>4</v>
       </c>
       <c r="L81" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M81" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N81" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O81" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P81" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="1">
         <v>0</v>
       </c>
       <c r="S81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" s="1">
         <v>0</v>
       </c>
       <c r="V81" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X81" s="40" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>48</v>
@@ -9788,30 +10061,32 @@
         <v>0</v>
       </c>
       <c r="G82" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I82" s="26"/>
       <c r="J82" s="1">
         <v>4</v>
       </c>
-      <c r="K82" s="1"/>
+      <c r="K82" s="1">
+        <v>4</v>
+      </c>
       <c r="L82" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O82" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P82" s="28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="1">
         <v>0</v>
@@ -9820,27 +10095,30 @@
         <v>0</v>
       </c>
       <c r="S82" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U82" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X82" s="40" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>48</v>
@@ -9852,18 +10130,16 @@
         <v>0</v>
       </c>
       <c r="G83" s="24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I83" s="26"/>
       <c r="J83" s="1">
-        <v>2</v>
-      </c>
-      <c r="K83" s="1">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K83" s="1"/>
       <c r="L83" s="1">
         <v>3</v>
       </c>
@@ -9871,19 +10147,19 @@
         <v>2</v>
       </c>
       <c r="N83" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O83" s="1">
+        <v>2</v>
+      </c>
+      <c r="P83" s="28">
         <v>4</v>
       </c>
-      <c r="P83" s="28">
-        <v>3</v>
-      </c>
       <c r="Q83" s="1">
         <v>0</v>
       </c>
       <c r="R83" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" s="1">
         <v>1</v>
@@ -9892,21 +10168,24 @@
         <v>1</v>
       </c>
       <c r="U83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X83" s="40" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>48</v>
@@ -9918,14 +10197,14 @@
         <v>0</v>
       </c>
       <c r="G84" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I84" s="26"/>
       <c r="J84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K84" s="1">
         <v>1</v>
@@ -9937,16 +10216,16 @@
         <v>2</v>
       </c>
       <c r="N84" s="1">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1">
         <v>4</v>
       </c>
-      <c r="O84" s="1">
-        <v>2</v>
-      </c>
       <c r="P84" s="28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q84" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" s="1">
         <v>1</v>
@@ -9961,18 +10240,21 @@
         <v>0</v>
       </c>
       <c r="V84" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X84" s="40" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>48</v>
@@ -9987,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I85" s="26"/>
       <c r="J85" s="1">
@@ -10003,13 +10285,13 @@
         <v>2</v>
       </c>
       <c r="N85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O85" s="1">
         <v>2</v>
       </c>
       <c r="P85" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q85" s="1">
         <v>1</v>
@@ -10024,21 +10306,24 @@
         <v>1</v>
       </c>
       <c r="U85" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X85" s="40" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>48</v>
@@ -10053,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I86" s="26"/>
       <c r="J86" s="1">
@@ -10069,13 +10354,13 @@
         <v>2</v>
       </c>
       <c r="N86" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O86" s="1">
         <v>2</v>
       </c>
       <c r="P86" s="28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q86" s="1">
         <v>1</v>
@@ -10090,21 +10375,24 @@
         <v>1</v>
       </c>
       <c r="U86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V86" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X86" s="40" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>48</v>
@@ -10126,7 +10414,7 @@
         <v>3</v>
       </c>
       <c r="K87" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="1">
         <v>3</v>
@@ -10135,19 +10423,19 @@
         <v>2</v>
       </c>
       <c r="N87" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O87" s="1">
         <v>2</v>
       </c>
       <c r="P87" s="28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q87" s="1">
         <v>1</v>
       </c>
       <c r="R87" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" s="1">
         <v>1</v>
@@ -10156,21 +10444,24 @@
         <v>1</v>
       </c>
       <c r="U87" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V87" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X87" s="40" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>915</v>
+        <v>892</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>48</v>
@@ -10192,7 +10483,7 @@
         <v>3</v>
       </c>
       <c r="K88" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L88" s="1">
         <v>3</v>
@@ -10207,7 +10498,7 @@
         <v>2</v>
       </c>
       <c r="P88" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q88" s="1">
         <v>1</v>
@@ -10227,16 +10518,19 @@
       <c r="V88" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X88" s="40" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>849</v>
+        <v>915</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>48</v>
@@ -10248,61 +10542,64 @@
         <v>0</v>
       </c>
       <c r="G89" s="24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I89" s="26"/>
       <c r="J89" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L89" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M89" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N89" s="1">
         <v>3</v>
       </c>
       <c r="O89" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P89" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U89" s="1">
         <v>1</v>
       </c>
       <c r="V89" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X89" s="40" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>918</v>
+        <v>849</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>48</v>
@@ -10314,61 +10611,64 @@
         <v>0</v>
       </c>
       <c r="G90" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I90" s="26"/>
       <c r="J90" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K90" s="1">
         <v>1</v>
       </c>
       <c r="L90" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M90" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N90" s="1">
+        <v>3</v>
+      </c>
+      <c r="O90" s="1">
         <v>4</v>
       </c>
-      <c r="O90" s="1">
-        <v>2</v>
-      </c>
       <c r="P90" s="28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" s="1">
         <v>1</v>
       </c>
       <c r="S90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V90" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X90" s="40" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>920</v>
+        <v>791</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>48</v>
@@ -10393,13 +10693,13 @@
         <v>1</v>
       </c>
       <c r="L91" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M91" s="1">
         <v>2</v>
       </c>
       <c r="N91" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O91" s="1">
         <v>2</v>
@@ -10414,27 +10714,30 @@
         <v>1</v>
       </c>
       <c r="S91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" s="1">
         <v>1</v>
       </c>
       <c r="U91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X91" s="40" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>792</v>
+        <v>920</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>48</v>
@@ -10449,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I92" s="26"/>
       <c r="J92" s="1">
@@ -10459,7 +10762,7 @@
         <v>1</v>
       </c>
       <c r="L92" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M92" s="1">
         <v>2</v>
@@ -10480,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="S92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T92" s="1">
         <v>1</v>
@@ -10491,22 +10794,25 @@
       <c r="V92" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X92" s="40" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>925</v>
+        <v>792</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>928</v>
+        <v>48</v>
       </c>
       <c r="E93" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" s="22" t="b">
         <v>0</v>
@@ -10515,7 +10821,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I93" s="26"/>
       <c r="J93" s="1">
@@ -10531,12 +10837,14 @@
         <v>2</v>
       </c>
       <c r="N93" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O93" s="1">
         <v>2</v>
       </c>
-      <c r="P93" s="28"/>
+      <c r="P93" s="28">
+        <v>4</v>
+      </c>
       <c r="Q93" s="1">
         <v>1</v>
       </c>
@@ -10550,83 +10858,91 @@
         <v>1</v>
       </c>
       <c r="U93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V93" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="31" t="s">
+      <c r="X93" s="40" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="E94" s="1">
+        <v>2</v>
+      </c>
+      <c r="F94" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G94" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1">
+        <v>5</v>
+      </c>
+      <c r="I94" s="26"/>
+      <c r="J94" s="1">
+        <v>3</v>
+      </c>
+      <c r="K94" s="1">
+        <v>1</v>
+      </c>
+      <c r="L94" s="1">
+        <v>3</v>
+      </c>
+      <c r="M94" s="1">
+        <v>2</v>
+      </c>
+      <c r="N94" s="1">
+        <v>1</v>
+      </c>
+      <c r="O94" s="1">
+        <v>2</v>
+      </c>
+      <c r="P94" s="28"/>
+      <c r="Q94" s="1">
+        <v>1</v>
+      </c>
+      <c r="R94" s="1">
+        <v>1</v>
+      </c>
+      <c r="S94" s="1">
+        <v>1</v>
+      </c>
+      <c r="T94" s="1">
+        <v>1</v>
+      </c>
+      <c r="U94" s="1">
+        <v>0</v>
+      </c>
+      <c r="V94" s="1">
+        <v>1</v>
+      </c>
+      <c r="X94" s="40" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="31" t="s">
         <v>929</v>
       </c>
-      <c r="B94" s="31" t="s">
+      <c r="B95" s="31" t="s">
         <v>930</v>
       </c>
-      <c r="C94" s="31" t="s">
+      <c r="C95" s="31" t="s">
         <v>931</v>
-      </c>
-      <c r="D94" s="31" t="s">
-        <v>928</v>
-      </c>
-      <c r="E94" s="32">
-        <v>2</v>
-      </c>
-      <c r="F94" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G94" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="32">
-        <v>6</v>
-      </c>
-      <c r="J94" s="32">
-        <v>3</v>
-      </c>
-      <c r="K94" s="32">
-        <v>1</v>
-      </c>
-      <c r="L94" s="32">
-        <v>3</v>
-      </c>
-      <c r="M94" s="32">
-        <v>2</v>
-      </c>
-      <c r="N94" s="32">
-        <v>3</v>
-      </c>
-      <c r="O94" s="32">
-        <v>2</v>
-      </c>
-      <c r="Q94" s="32">
-        <v>1</v>
-      </c>
-      <c r="R94" s="32">
-        <v>1</v>
-      </c>
-      <c r="S94" s="32">
-        <v>1</v>
-      </c>
-      <c r="T94" s="32">
-        <v>1</v>
-      </c>
-      <c r="U94" s="32">
-        <v>1</v>
-      </c>
-      <c r="V94" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="31" t="s">
-        <v>932</v>
-      </c>
-      <c r="B95" s="31" t="s">
-        <v>933</v>
-      </c>
-      <c r="C95" s="31" t="s">
-        <v>934</v>
       </c>
       <c r="D95" s="31" t="s">
         <v>928</v>
@@ -10679,16 +10995,19 @@
       <c r="V95" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X95" s="40" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="31" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>851</v>
+        <v>933</v>
       </c>
       <c r="C96" s="31" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D96" s="31" t="s">
         <v>928</v>
@@ -10703,54 +11022,57 @@
         <v>0</v>
       </c>
       <c r="H96" s="32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J96" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K96" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="32">
         <v>3</v>
       </c>
       <c r="M96" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N96" s="32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O96" s="32">
         <v>2</v>
       </c>
       <c r="Q96" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" s="32">
         <v>1</v>
       </c>
       <c r="T96" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U96" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V96" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X96" s="40" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="31" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>938</v>
+        <v>851</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D97" s="31" t="s">
         <v>928</v>
@@ -10765,54 +11087,57 @@
         <v>0</v>
       </c>
       <c r="H97" s="32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J97" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" s="32">
         <v>3</v>
       </c>
       <c r="M97" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N97" s="32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O97" s="32">
         <v>2</v>
       </c>
       <c r="Q97" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" s="32">
         <v>1</v>
       </c>
       <c r="T97" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U97" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V97" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X97" s="40" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="31" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="D98" s="31" t="s">
         <v>928</v>
@@ -10827,7 +11152,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J98" s="32">
         <v>3</v>
@@ -10836,10 +11161,10 @@
         <v>1</v>
       </c>
       <c r="L98" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M98" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N98" s="32">
         <v>3</v>
@@ -10854,10 +11179,10 @@
         <v>1</v>
       </c>
       <c r="S98" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U98" s="32">
         <v>1</v>
@@ -10865,16 +11190,19 @@
       <c r="V98" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X98" s="40" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="31" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>903</v>
+        <v>942</v>
       </c>
       <c r="D99" s="31" t="s">
         <v>928</v>
@@ -10892,16 +11220,16 @@
         <v>4</v>
       </c>
       <c r="J99" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K99" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M99" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N99" s="32">
         <v>3</v>
@@ -10910,16 +11238,16 @@
         <v>2</v>
       </c>
       <c r="Q99" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T99" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U99" s="32">
         <v>1</v>
@@ -10927,16 +11255,19 @@
       <c r="V99" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X99" s="40" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="31" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>947</v>
+        <v>903</v>
       </c>
       <c r="D100" s="31" t="s">
         <v>928</v>
@@ -10951,25 +11282,25 @@
         <v>0</v>
       </c>
       <c r="H100" s="32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J100" s="32">
         <v>2</v>
       </c>
       <c r="K100" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L100" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M100" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N100" s="32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O100" s="32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q100" s="32">
         <v>0</v>
@@ -10978,27 +11309,30 @@
         <v>0</v>
       </c>
       <c r="S100" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U100" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V100" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="X100" s="40" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="31" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="C101" s="31" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D101" s="31" t="s">
         <v>928</v>
@@ -11013,46 +11347,49 @@
         <v>0</v>
       </c>
       <c r="H101" s="32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J101" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K101" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M101" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N101" s="32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O101" s="32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q101" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" s="32">
         <v>0</v>
       </c>
       <c r="S101" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U101" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V101" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="X101" s="40" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="31" t="s">
         <v>948</v>
       </c>
@@ -11113,8 +11450,11 @@
       <c r="V102" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X102" s="40" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="31" t="s">
         <v>951</v>
       </c>
@@ -11175,8 +11515,11 @@
       <c r="V103" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X103" s="40" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="31" t="s">
         <v>954</v>
       </c>
@@ -11237,8 +11580,11 @@
       <c r="V104" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X104" s="40" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="31" t="s">
         <v>957</v>
       </c>
@@ -11299,8 +11645,11 @@
       <c r="V105" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X105" s="40" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="31" t="s">
         <v>960</v>
       </c>
@@ -11361,8 +11710,11 @@
       <c r="V106" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X106" s="40" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="31" t="s">
         <v>963</v>
       </c>
@@ -11423,8 +11775,11 @@
       <c r="V107" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X107" s="40" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="31" t="s">
         <v>965</v>
       </c>
@@ -11485,8 +11840,11 @@
       <c r="V108" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X108" s="40" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="31" t="s">
         <v>968</v>
       </c>
@@ -11547,8 +11905,11 @@
       <c r="V109" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X109" s="40" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="31" t="s">
         <v>971</v>
       </c>
@@ -11609,8 +11970,11 @@
       <c r="V110" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X110" s="40" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="31" t="s">
         <v>974</v>
       </c>
@@ -11671,8 +12035,11 @@
       <c r="V111" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X111" s="40" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="31" t="s">
         <v>977</v>
       </c>
@@ -11733,8 +12100,11 @@
       <c r="V112" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X112" s="40" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="31" t="s">
         <v>980</v>
       </c>
@@ -11795,8 +12165,11 @@
       <c r="V113" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X113" s="40" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="31" t="s">
         <v>983</v>
       </c>
@@ -11857,8 +12230,11 @@
       <c r="V114" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X114" s="40" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="31" t="s">
         <v>985</v>
       </c>
@@ -11919,8 +12295,11 @@
       <c r="V115" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X115" s="40" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="31" t="s">
         <v>988</v>
       </c>
@@ -11981,8 +12360,11 @@
       <c r="V116" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X116" s="40" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="31" t="s">
         <v>991</v>
       </c>
@@ -12043,8 +12425,11 @@
       <c r="V117" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X117" s="40" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="31" t="s">
         <v>994</v>
       </c>
@@ -12105,8 +12490,11 @@
       <c r="V118" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X118" s="40" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="31" t="s">
         <v>997</v>
       </c>
@@ -12167,8 +12555,11 @@
       <c r="V119" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X119" s="40" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="31" t="s">
         <v>1000</v>
       </c>
@@ -12229,16 +12620,21 @@
       <c r="V120" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X120" s="40" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H121" s="39">
         <f>AVERAGE(Scores[MC])</f>
-        <v>3.7731092436974789</v>
-      </c>
+        <v>3.7563025210084033</v>
+      </c>
+      <c r="X121" s="40"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="J2:O120">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>Q2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12380,7 +12776,7 @@
       </c>
       <c r="P2" s="18">
         <f t="array" ref="P2">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A2,Scores[#Headers],0)))</f>
-        <v>0.58823529411764708</v>
+        <v>0.57983193277310929</v>
       </c>
       <c r="Q2" s="16"/>
     </row>
@@ -12432,7 +12828,7 @@
       </c>
       <c r="P3" s="18">
         <f t="array" ref="P3">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A3,Scores[#Headers],0)))</f>
-        <v>0.52941176470588236</v>
+        <v>0.53781512605042014</v>
       </c>
       <c r="Q3" s="16"/>
     </row>
@@ -12588,7 +12984,7 @@
       </c>
       <c r="P6" s="18">
         <f t="array" ref="P6">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A6,Scores[#Headers],0)))</f>
-        <v>0.36134453781512604</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="Q6" s="16"/>
     </row>
@@ -12640,7 +13036,7 @@
       </c>
       <c r="P7" s="18">
         <f t="array" ref="P7">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A7,Scores[#Headers],0)))</f>
-        <v>0.72268907563025209</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q7" s="16"/>
     </row>
@@ -12677,7 +13073,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDF4E09-BA8B-6A46-A101-51047F14F5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA37C0E-5382-C047-830C-CED48E380BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3362,114 +3362,6 @@
   </cellStyles>
   <dxfs count="76">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF3F4A58"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3534,6 +3426,60 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF3F4A58"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3549,102 +3495,25 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF3F4A58"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
+        <color rgb="FF9C0006"/>
       </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3786,6 +3655,137 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF3F4A58"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFF5F8FB"/>
@@ -3892,57 +3892,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V121" totalsRowCount="1" headerRowDxfId="48" dataDxfId="47" totalsRowDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:V121" totalsRowCount="1" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="45" totalsRowDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="44" totalsRowDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="43" totalsRowDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="42" totalsRowDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="41" totalsRowDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="5" totalsRowDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="4" totalsRowDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="40" totalsRowDxfId="20">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="68" totalsRowDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="67" totalsRowDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="66" totalsRowDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="65" totalsRowDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="64" totalsRowDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="63" totalsRowDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="62" totalsRowDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="14">
       <totalsRowFormula>AVERAGE(Scores[MC])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="39" totalsRowDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="38" totalsRowDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="37" totalsRowDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="36" totalsRowDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="35" totalsRowDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="34" totalsRowDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="33" totalsRowDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="32" totalsRowDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="31" totalsRowDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="30" totalsRowDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="29" totalsRowDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="28" totalsRowDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="27" totalsRowDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="26" totalsRowDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="60" totalsRowDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="59" totalsRowDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="58" totalsRowDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="57" totalsRowDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="56" totalsRowDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="55" totalsRowDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="54" totalsRowDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="53" totalsRowDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="52" totalsRowDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="51" totalsRowDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="50" totalsRowDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="49" totalsRowDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="48" totalsRowDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="47" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="46" dataDxfId="45" totalsRowDxfId="44">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="57"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="55"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="54"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="53"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3952,7 +3952,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3963,7 +3963,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3975,7 +3975,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="49">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="24">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4337,7 +4337,9 @@
       <c r="O2" s="1">
         <v>2</v>
       </c>
-      <c r="P2" s="28"/>
+      <c r="P2" s="28">
+        <v>3</v>
+      </c>
       <c r="Q2" s="1">
         <f>IF(J2=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -4413,7 +4415,9 @@
       <c r="O3" s="1">
         <v>3</v>
       </c>
-      <c r="P3" s="28"/>
+      <c r="P3" s="28">
+        <v>1</v>
+      </c>
       <c r="Q3" s="1">
         <f>IF(J3=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -4489,7 +4493,9 @@
       <c r="O4" s="1">
         <v>1</v>
       </c>
-      <c r="P4" s="28"/>
+      <c r="P4" s="28">
+        <v>2</v>
+      </c>
       <c r="Q4" s="1">
         <f>IF(J4=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -4565,7 +4571,9 @@
       <c r="O5" s="1">
         <v>2</v>
       </c>
-      <c r="P5" s="28"/>
+      <c r="P5" s="28">
+        <v>1</v>
+      </c>
       <c r="Q5" s="1">
         <f>IF(J5=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -4641,7 +4649,9 @@
       <c r="O6" s="1">
         <v>2</v>
       </c>
-      <c r="P6" s="28"/>
+      <c r="P6" s="28">
+        <v>1</v>
+      </c>
       <c r="Q6" s="1">
         <f>IF(J6=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -4717,7 +4727,9 @@
       <c r="O7" s="1">
         <v>3</v>
       </c>
-      <c r="P7" s="28"/>
+      <c r="P7" s="28">
+        <v>1</v>
+      </c>
       <c r="Q7" s="1">
         <f>IF(J7=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -4793,7 +4805,9 @@
       <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="P8" s="28"/>
+      <c r="P8" s="28">
+        <v>1</v>
+      </c>
       <c r="Q8" s="1">
         <f>IF(J8=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -4869,7 +4883,9 @@
       <c r="O9" s="1">
         <v>2</v>
       </c>
-      <c r="P9" s="28"/>
+      <c r="P9" s="28">
+        <v>1</v>
+      </c>
       <c r="Q9" s="1">
         <f>IF(J9=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -4945,7 +4961,9 @@
       <c r="O10" s="1">
         <v>2</v>
       </c>
-      <c r="P10" s="28"/>
+      <c r="P10" s="28">
+        <v>0</v>
+      </c>
       <c r="Q10" s="1">
         <f>IF(J10=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5019,7 +5037,9 @@
       <c r="O11" s="1">
         <v>3</v>
       </c>
-      <c r="P11" s="28"/>
+      <c r="P11" s="28">
+        <v>3</v>
+      </c>
       <c r="Q11" s="1">
         <f>IF(J11=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5095,7 +5115,9 @@
       <c r="O12" s="1">
         <v>1</v>
       </c>
-      <c r="P12" s="28"/>
+      <c r="P12" s="28">
+        <v>1</v>
+      </c>
       <c r="Q12" s="1">
         <f>IF(J12=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5171,7 +5193,9 @@
       <c r="O13" s="1">
         <v>2</v>
       </c>
-      <c r="P13" s="28"/>
+      <c r="P13" s="28">
+        <v>3</v>
+      </c>
       <c r="Q13" s="1">
         <f>IF(J13=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -5247,7 +5271,9 @@
       <c r="O14" s="1">
         <v>1</v>
       </c>
-      <c r="P14" s="28"/>
+      <c r="P14" s="28">
+        <v>0</v>
+      </c>
       <c r="Q14" s="1">
         <f>IF(J14=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5323,7 +5349,9 @@
       <c r="O15" s="1">
         <v>4</v>
       </c>
-      <c r="P15" s="28"/>
+      <c r="P15" s="28">
+        <v>1</v>
+      </c>
       <c r="Q15" s="1">
         <f>IF(J15=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5399,7 +5427,9 @@
       <c r="O16" s="1">
         <v>2</v>
       </c>
-      <c r="P16" s="28"/>
+      <c r="P16" s="28">
+        <v>2</v>
+      </c>
       <c r="Q16" s="1">
         <f>IF(J16=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -5475,7 +5505,9 @@
       <c r="O17" s="1">
         <v>2</v>
       </c>
-      <c r="P17" s="28"/>
+      <c r="P17" s="28">
+        <v>2</v>
+      </c>
       <c r="Q17" s="1">
         <f>IF(J17=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -5551,7 +5583,9 @@
       <c r="O18" s="1">
         <v>4</v>
       </c>
-      <c r="P18" s="28"/>
+      <c r="P18" s="28">
+        <v>3</v>
+      </c>
       <c r="Q18" s="1">
         <f>IF(J18=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5627,7 +5661,9 @@
       <c r="O19" s="1">
         <v>2</v>
       </c>
-      <c r="P19" s="28"/>
+      <c r="P19" s="28">
+        <v>1</v>
+      </c>
       <c r="Q19" s="1">
         <f>IF(J19=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5841,7 +5877,9 @@
       <c r="O22" s="1">
         <v>2</v>
       </c>
-      <c r="P22" s="28"/>
+      <c r="P22" s="28">
+        <v>2</v>
+      </c>
       <c r="Q22" s="1">
         <f>IF(J22=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5917,7 +5955,9 @@
       <c r="O23" s="1">
         <v>2</v>
       </c>
-      <c r="P23" s="28"/>
+      <c r="P23" s="28">
+        <v>1</v>
+      </c>
       <c r="Q23" s="1">
         <f>IF(J23=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -5993,7 +6033,9 @@
       <c r="O24" s="1">
         <v>2</v>
       </c>
-      <c r="P24" s="28"/>
+      <c r="P24" s="28">
+        <v>1</v>
+      </c>
       <c r="Q24" s="1">
         <f>IF(J24=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -6069,7 +6111,9 @@
       <c r="O25" s="1">
         <v>4</v>
       </c>
-      <c r="P25" s="28"/>
+      <c r="P25" s="28">
+        <v>1</v>
+      </c>
       <c r="Q25" s="1">
         <f>IF(J25=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -6145,7 +6189,9 @@
       <c r="O26" s="1">
         <v>4</v>
       </c>
-      <c r="P26" s="28"/>
+      <c r="P26" s="28">
+        <v>1</v>
+      </c>
       <c r="Q26" s="1">
         <f>IF(J26=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6221,7 +6267,9 @@
       <c r="O27" s="1">
         <v>1</v>
       </c>
-      <c r="P27" s="28"/>
+      <c r="P27" s="28">
+        <v>2</v>
+      </c>
       <c r="Q27" s="1">
         <f>IF(J27=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -6297,7 +6345,9 @@
       <c r="O28" s="1">
         <v>2</v>
       </c>
-      <c r="P28" s="28"/>
+      <c r="P28" s="28">
+        <v>3</v>
+      </c>
       <c r="Q28" s="1">
         <f>IF(J28=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -8057,7 +8107,9 @@
       <c r="O52" s="1">
         <v>2</v>
       </c>
-      <c r="P52" s="28"/>
+      <c r="P52" s="28">
+        <v>3</v>
+      </c>
       <c r="Q52" s="1">
         <v>0</v>
       </c>
@@ -8124,7 +8176,9 @@
       <c r="O53" s="1">
         <v>2</v>
       </c>
-      <c r="P53" s="28"/>
+      <c r="P53" s="28">
+        <v>1</v>
+      </c>
       <c r="Q53" s="1">
         <v>0</v>
       </c>
@@ -8258,7 +8312,9 @@
       <c r="O55" s="1">
         <v>2</v>
       </c>
-      <c r="P55" s="28"/>
+      <c r="P55" s="28">
+        <v>3</v>
+      </c>
       <c r="Q55" s="1">
         <v>1</v>
       </c>
@@ -8392,7 +8448,9 @@
       <c r="O57" s="1">
         <v>2</v>
       </c>
-      <c r="P57" s="28"/>
+      <c r="P57" s="28">
+        <v>4</v>
+      </c>
       <c r="Q57" s="1">
         <v>1</v>
       </c>
@@ -8459,7 +8517,9 @@
       <c r="O58" s="1">
         <v>2</v>
       </c>
-      <c r="P58" s="28"/>
+      <c r="P58" s="28">
+        <v>4</v>
+      </c>
       <c r="Q58" s="1">
         <v>1</v>
       </c>
@@ -8526,7 +8586,9 @@
       <c r="O59" s="1">
         <v>2</v>
       </c>
-      <c r="P59" s="28"/>
+      <c r="P59" s="28">
+        <v>4</v>
+      </c>
       <c r="Q59" s="1">
         <v>1</v>
       </c>
@@ -8656,7 +8718,9 @@
       <c r="O61" s="1">
         <v>2</v>
       </c>
-      <c r="P61" s="28"/>
+      <c r="P61" s="28">
+        <v>4</v>
+      </c>
       <c r="Q61" s="1">
         <v>0</v>
       </c>
@@ -8857,7 +8921,9 @@
       <c r="O64" s="1">
         <v>2</v>
       </c>
-      <c r="P64" s="28"/>
+      <c r="P64" s="28">
+        <v>4</v>
+      </c>
       <c r="Q64" s="1">
         <v>1</v>
       </c>
@@ -9058,7 +9124,9 @@
       <c r="O67" s="1">
         <v>2</v>
       </c>
-      <c r="P67" s="28"/>
+      <c r="P67" s="28">
+        <v>4</v>
+      </c>
       <c r="Q67" s="1">
         <v>1</v>
       </c>
@@ -9125,7 +9193,9 @@
       <c r="O68" s="1">
         <v>2</v>
       </c>
-      <c r="P68" s="28"/>
+      <c r="P68" s="28">
+        <v>3</v>
+      </c>
       <c r="Q68" s="1">
         <v>1</v>
       </c>
@@ -12634,7 +12704,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="J2:O120">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>Q2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13073,7 +13143,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BCB3DD-D386-CB45-9D79-6E9E13CF17BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146F52D6-DE9F-D44A-89FE-326FE8B2944C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3501,9 +3501,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -3763,6 +3760,9 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3908,51 +3908,51 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="68" totalsRowDxfId="20"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="67" totalsRowDxfId="19"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="66" totalsRowDxfId="18"/>
-    <tableColumn id="24" xr3:uid="{3D78B174-0EEB-C04D-AFAA-846CD92209B4}" name="Grade" dataDxfId="23" totalsRowDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="65" totalsRowDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="64" totalsRowDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="63" totalsRowDxfId="14">
+    <tableColumn id="24" xr3:uid="{3D78B174-0EEB-C04D-AFAA-846CD92209B4}" name="Grade" dataDxfId="65" totalsRowDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="64" totalsRowDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="63" totalsRowDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="62" totalsRowDxfId="14">
       <totalsRowFormula>AVERAGE(Scores[MC])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="62" totalsRowDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="61" totalsRowDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="60" totalsRowDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="59" totalsRowDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="58" totalsRowDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="57" totalsRowDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="56" totalsRowDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="55" totalsRowDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="54" totalsRowDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="53" totalsRowDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="52" totalsRowDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="51" totalsRowDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="50" totalsRowDxfId="1"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="49" totalsRowDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="61" totalsRowDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="60" totalsRowDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="59" totalsRowDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="58" totalsRowDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="57" totalsRowDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="56" totalsRowDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="55" totalsRowDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="54" totalsRowDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="53" totalsRowDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="52" totalsRowDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="51" totalsRowDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="50" totalsRowDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="49" totalsRowDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="48" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="48" dataDxfId="47" totalsRowDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="47" dataDxfId="46" totalsRowDxfId="45">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="32"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="31"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="30"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3962,7 +3962,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3973,7 +3973,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3985,7 +3985,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="26">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="25">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6520,7 +6520,9 @@
       <c r="P29" s="1">
         <v>2</v>
       </c>
-      <c r="Q29" s="28"/>
+      <c r="Q29" s="28">
+        <v>2</v>
+      </c>
       <c r="R29" s="1">
         <f>IF(K29=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6597,7 +6599,9 @@
         <v>1</v>
       </c>
       <c r="P30" s="1"/>
-      <c r="Q30" s="28"/>
+      <c r="Q30" s="28">
+        <v>2</v>
+      </c>
       <c r="R30" s="1">
         <f>IF(K30=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -6676,7 +6680,9 @@
       <c r="P31" s="1">
         <v>2</v>
       </c>
-      <c r="Q31" s="28"/>
+      <c r="Q31" s="28">
+        <v>0</v>
+      </c>
       <c r="R31" s="1">
         <f>IF(K31=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6834,7 +6840,9 @@
       <c r="P33" s="1">
         <v>3</v>
       </c>
-      <c r="Q33" s="28"/>
+      <c r="Q33" s="28">
+        <v>2</v>
+      </c>
       <c r="R33" s="1">
         <f>IF(K33=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -6913,7 +6921,9 @@
       <c r="P34" s="1">
         <v>1</v>
       </c>
-      <c r="Q34" s="28"/>
+      <c r="Q34" s="28">
+        <v>0</v>
+      </c>
       <c r="R34" s="1">
         <f>IF(K34=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6992,7 +7002,9 @@
       <c r="P35" s="1">
         <v>2</v>
       </c>
-      <c r="Q35" s="28"/>
+      <c r="Q35" s="28">
+        <v>0</v>
+      </c>
       <c r="R35" s="1">
         <f>IF(K35=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7071,7 +7083,9 @@
       <c r="P36" s="1">
         <v>2</v>
       </c>
-      <c r="Q36" s="28"/>
+      <c r="Q36" s="28">
+        <v>4</v>
+      </c>
       <c r="R36" s="1">
         <f>IF(K36=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -7229,7 +7243,9 @@
       <c r="P38" s="1">
         <v>2</v>
       </c>
-      <c r="Q38" s="28"/>
+      <c r="Q38" s="28">
+        <v>3</v>
+      </c>
       <c r="R38" s="1">
         <f>IF(K38=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -7308,7 +7324,9 @@
       <c r="P39" s="1">
         <v>2</v>
       </c>
-      <c r="Q39" s="28"/>
+      <c r="Q39" s="28">
+        <v>1</v>
+      </c>
       <c r="R39" s="1">
         <f>IF(K39=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -7387,7 +7405,9 @@
       <c r="P40" s="1">
         <v>1</v>
       </c>
-      <c r="Q40" s="28"/>
+      <c r="Q40" s="28">
+        <v>2</v>
+      </c>
       <c r="R40" s="1">
         <f>IF(K40=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -7466,7 +7486,9 @@
       <c r="P41" s="1">
         <v>2</v>
       </c>
-      <c r="Q41" s="28"/>
+      <c r="Q41" s="28">
+        <v>3</v>
+      </c>
       <c r="R41" s="1">
         <f>IF(K41=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -7545,7 +7567,9 @@
       <c r="P42" s="1">
         <v>2</v>
       </c>
-      <c r="Q42" s="28"/>
+      <c r="Q42" s="28">
+        <v>0</v>
+      </c>
       <c r="R42" s="1">
         <f>IF(K42=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7624,7 +7648,9 @@
       <c r="P43" s="1">
         <v>2</v>
       </c>
-      <c r="Q43" s="28"/>
+      <c r="Q43" s="28">
+        <v>2</v>
+      </c>
       <c r="R43" s="1">
         <f>IF(K43=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7703,7 +7729,9 @@
       <c r="P44" s="1">
         <v>4</v>
       </c>
-      <c r="Q44" s="28"/>
+      <c r="Q44" s="28">
+        <v>4</v>
+      </c>
       <c r="R44" s="1">
         <f>IF(K44=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -7853,7 +7881,9 @@
       <c r="P46" s="1">
         <v>2</v>
       </c>
-      <c r="Q46" s="28"/>
+      <c r="Q46" s="28">
+        <v>1</v>
+      </c>
       <c r="R46" s="1">
         <f>IF(K46=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -13074,7 +13104,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="K2:P120">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>R2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13513,7 +13543,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="24" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146F52D6-DE9F-D44A-89FE-326FE8B2944C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A85D8BF-7D80-524B-B5A1-BE29E9F1CAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="1060">
   <si>
     <t>Model</t>
   </si>
@@ -3050,9 +3050,6 @@
     <t>WILLIAMS</t>
   </si>
   <si>
-    <t>Qamar Galmen</t>
-  </si>
-  <si>
     <t>NYAIRE WILLIS</t>
   </si>
   <si>
@@ -3072,6 +3069,156 @@
   </si>
   <si>
     <t>Grade</t>
+  </si>
+  <si>
+    <t>JAISHON DAVY</t>
+  </si>
+  <si>
+    <t>JAISHON</t>
+  </si>
+  <si>
+    <t>DAVY</t>
+  </si>
+  <si>
+    <t>JEREMY FEMINELLO</t>
+  </si>
+  <si>
+    <t>JEREMY</t>
+  </si>
+  <si>
+    <t>FEMINELLO</t>
+  </si>
+  <si>
+    <t>ANTOINE GERMAIN-KENNER</t>
+  </si>
+  <si>
+    <t>ANTOINE</t>
+  </si>
+  <si>
+    <t>GERMAIN-KENNER</t>
+  </si>
+  <si>
+    <t>KAMYA GRANT</t>
+  </si>
+  <si>
+    <t>KAMYA</t>
+  </si>
+  <si>
+    <t>GRANT</t>
+  </si>
+  <si>
+    <t>DAMARCUS HALLEY</t>
+  </si>
+  <si>
+    <t>DAMARCUS</t>
+  </si>
+  <si>
+    <t>HALLEY</t>
+  </si>
+  <si>
+    <t>TAHSIN IFAZ</t>
+  </si>
+  <si>
+    <t>TAHSIN</t>
+  </si>
+  <si>
+    <t>IFAZ</t>
+  </si>
+  <si>
+    <t>SAIBAH ISHRAR</t>
+  </si>
+  <si>
+    <t>SAIBAH</t>
+  </si>
+  <si>
+    <t>ISHRAR</t>
+  </si>
+  <si>
+    <t>WITHMIT MAGLOIRE</t>
+  </si>
+  <si>
+    <t>WITHMIT</t>
+  </si>
+  <si>
+    <t>MAGLOIRE</t>
+  </si>
+  <si>
+    <t>ANGELYS MARRERO</t>
+  </si>
+  <si>
+    <t>ANGELYS</t>
+  </si>
+  <si>
+    <t>MARRERO</t>
+  </si>
+  <si>
+    <t>LUPITA MENDEZ</t>
+  </si>
+  <si>
+    <t>LUPITA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>JACOB MOORE</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>NATAN PALENCIA</t>
+  </si>
+  <si>
+    <t>NATAN</t>
+  </si>
+  <si>
+    <t>PALENCIA</t>
+  </si>
+  <si>
+    <t>TYLER ROSSER</t>
+  </si>
+  <si>
+    <t>TYLER</t>
+  </si>
+  <si>
+    <t>ROSSER</t>
+  </si>
+  <si>
+    <t>ISAIAH SCHNEIDER</t>
+  </si>
+  <si>
+    <t>ISAIAH</t>
+  </si>
+  <si>
+    <t>SCHNEIDER</t>
+  </si>
+  <si>
+    <t>ADDIS TELFER</t>
+  </si>
+  <si>
+    <t>ADDIS</t>
+  </si>
+  <si>
+    <t>TELFER</t>
+  </si>
+  <si>
+    <t>Miles Carty</t>
+  </si>
+  <si>
+    <t>Miles</t>
+  </si>
+  <si>
+    <t>Carty</t>
+  </si>
+  <si>
+    <t>marcuise Martin</t>
+  </si>
+  <si>
+    <t>marcuise</t>
+  </si>
+  <si>
+    <t>Martin</t>
   </si>
 </sst>
 </file>
@@ -3219,7 +3366,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3355,6 +3502,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3363,7 +3513,58 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{D605B4E0-7730-4D43-A011-6A0EF9292E1A}"/>
     <cellStyle name="Percent 2" xfId="4" xr:uid="{E6DE421D-B06A-DB4D-BCE7-D696BB42B3F4}"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="82">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3502,17 +3703,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3520,6 +3710,120 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF3F4A58"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF3F4A58"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3661,120 +3965,6 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF3F4A58"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF3F4A58"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3855,10 +4045,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Light and Airy" count="4" xr9:uid="{9857ACD9-B079-C44A-A030-69F7726DB419}">
-      <tableStyleElement type="wholeTable" dxfId="77"/>
-      <tableStyleElement type="headerRow" dxfId="76"/>
-      <tableStyleElement type="totalRow" dxfId="75"/>
-      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="wholeTable" dxfId="81"/>
+      <tableStyleElement type="headerRow" dxfId="80"/>
+      <tableStyleElement type="totalRow" dxfId="79"/>
+      <tableStyleElement type="firstRowStripe" dxfId="78"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3901,58 +4091,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:W121" totalsRowCount="1" headerRowDxfId="73" dataDxfId="72" totalsRowDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:W141" totalsRowCount="1" headerRowDxfId="77" dataDxfId="76" totalsRowDxfId="75">
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="70" totalsRowDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="69" totalsRowDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="68" totalsRowDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="67" totalsRowDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="66" totalsRowDxfId="18"/>
-    <tableColumn id="24" xr3:uid="{3D78B174-0EEB-C04D-AFAA-846CD92209B4}" name="Grade" dataDxfId="65" totalsRowDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="64" totalsRowDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="63" totalsRowDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="62" totalsRowDxfId="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Student" dataDxfId="51" totalsRowDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First" dataDxfId="50" totalsRowDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last" dataDxfId="49" totalsRowDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class" dataDxfId="48" totalsRowDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="47" totalsRowDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{3D78B174-0EEB-C04D-AFAA-846CD92209B4}" name="Grade" dataDxfId="46" totalsRowDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="45" totalsRowDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="44" totalsRowDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="19">
       <totalsRowFormula>AVERAGE(Scores[MC])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="61" totalsRowDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="60" totalsRowDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="59" totalsRowDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="58" totalsRowDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="57" totalsRowDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="56" totalsRowDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="55" totalsRowDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="54" totalsRowDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="53" totalsRowDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="52" totalsRowDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="51" totalsRowDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="50" totalsRowDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="49" totalsRowDxfId="1"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="48" totalsRowDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Final" dataDxfId="42" totalsRowDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1" dataDxfId="41" totalsRowDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="2" dataDxfId="40" totalsRowDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="3" dataDxfId="39" totalsRowDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="4" dataDxfId="38" totalsRowDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="5" dataDxfId="37" totalsRowDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="6" dataDxfId="36" totalsRowDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SEQ" dataDxfId="35" totalsRowDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Q1" dataDxfId="34" totalsRowDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Q2" dataDxfId="33" totalsRowDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Q3" dataDxfId="32" totalsRowDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Q4" dataDxfId="31" totalsRowDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Q5" dataDxfId="30" totalsRowDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Q6" dataDxfId="29" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="47" dataDxfId="46" totalsRowDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="74" dataDxfId="73" totalsRowDxfId="72">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="31"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="29"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="67"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="65"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="62"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="61"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="60"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="59"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="58"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="57"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="56"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3962,7 +4152,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3973,7 +4163,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3985,7 +4175,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="25">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="52">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4216,8 +4406,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:Y141"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="21" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="22.6640625" style="30" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" style="30" customWidth="1"/>
@@ -4232,7 +4422,7 @@
     <col min="24" max="16384" width="12.6640625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="29" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" s="29" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="15" t="s">
         <v>9</v>
       </c>
@@ -4249,7 +4439,7 @@
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G1" s="21" t="s">
         <v>32</v>
@@ -4303,7 +4493,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>70</v>
       </c>
@@ -4380,11 +4570,9 @@
         <f>IF(P2=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y2" s="40" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y2" s="40"/>
+    </row>
+    <row r="3" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>82</v>
       </c>
@@ -4461,11 +4649,9 @@
         <f>IF(P3=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y3" s="40" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y3" s="40"/>
+    </row>
+    <row r="4" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>112</v>
       </c>
@@ -4542,11 +4728,9 @@
         <f>IF(P4=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="40" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y4" s="40"/>
+    </row>
+    <row r="5" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>161</v>
       </c>
@@ -4623,11 +4807,9 @@
         <f>IF(P5=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y5" s="40" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y5" s="40"/>
+    </row>
+    <row r="6" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>245</v>
       </c>
@@ -4704,11 +4886,9 @@
         <f>IF(P6=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y6" s="40" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y6" s="40"/>
+    </row>
+    <row r="7" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>314</v>
       </c>
@@ -4785,11 +4965,9 @@
         <f>IF(P7=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="40" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y7" s="40"/>
+    </row>
+    <row r="8" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>367</v>
       </c>
@@ -4866,11 +5044,9 @@
         <f>IF(P8=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y8" s="40" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y8" s="40"/>
+    </row>
+    <row r="9" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>432</v>
       </c>
@@ -4947,11 +5123,9 @@
         <f>IF(P9=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y9" s="40" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y9" s="40"/>
+    </row>
+    <row r="10" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>473</v>
       </c>
@@ -5028,11 +5202,9 @@
         <f>IF(P10=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y10" s="40" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y10" s="40"/>
+    </row>
+    <row r="11" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>523</v>
       </c>
@@ -5107,11 +5279,9 @@
         <f>IF(P11=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="40" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y11" s="40"/>
+    </row>
+    <row r="12" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>575</v>
       </c>
@@ -5188,11 +5358,9 @@
         <f>IF(P12=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="40" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y12" s="40"/>
+    </row>
+    <row r="13" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>614</v>
       </c>
@@ -5269,11 +5437,9 @@
         <f>IF(P13=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y13" s="40" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y13" s="40"/>
+    </row>
+    <row r="14" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>678</v>
       </c>
@@ -5350,11 +5516,9 @@
         <f>IF(P14=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="40" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y14" s="40"/>
+    </row>
+    <row r="15" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>719</v>
       </c>
@@ -5431,11 +5595,9 @@
         <f>IF(P15=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y15" s="40" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y15" s="40"/>
+    </row>
+    <row r="16" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>720</v>
       </c>
@@ -5512,11 +5674,9 @@
         <f>IF(P16=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y16" s="40" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y16" s="40"/>
+    </row>
+    <row r="17" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>721</v>
       </c>
@@ -5593,11 +5753,9 @@
         <f>IF(P17=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y17" s="40" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y17" s="40"/>
+    </row>
+    <row r="18" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
         <v>722</v>
       </c>
@@ -5674,11 +5832,9 @@
         <f>IF(P18=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y18" s="40" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y18" s="40"/>
+    </row>
+    <row r="19" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>723</v>
       </c>
@@ -5755,11 +5911,9 @@
         <f>IF(P19=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y19" s="40" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y19" s="40"/>
+    </row>
+    <row r="20" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
         <v>724</v>
       </c>
@@ -5822,11 +5976,9 @@
         <f>IF(P20=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y20" s="40" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y20" s="40"/>
+    </row>
+    <row r="21" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>725</v>
       </c>
@@ -5899,11 +6051,9 @@
         <f>IF(P21=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y21" s="40" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y21" s="40"/>
+    </row>
+    <row r="22" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>726</v>
       </c>
@@ -5980,11 +6130,9 @@
         <f>IF(P22=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y22" s="40" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y22" s="40"/>
+    </row>
+    <row r="23" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>727</v>
       </c>
@@ -6061,11 +6209,9 @@
         <f>IF(P23=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y23" s="40" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y23" s="40"/>
+    </row>
+    <row r="24" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>728</v>
       </c>
@@ -6142,11 +6288,9 @@
         <f>IF(P24=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y24" s="40" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y24" s="40"/>
+    </row>
+    <row r="25" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>729</v>
       </c>
@@ -6223,11 +6367,9 @@
         <f>IF(P25=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y25" s="40" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y25" s="40"/>
+    </row>
+    <row r="26" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
         <v>730</v>
       </c>
@@ -6304,11 +6446,9 @@
         <f>IF(P26=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y26" s="40" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y26" s="40"/>
+    </row>
+    <row r="27" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>731</v>
       </c>
@@ -6385,11 +6525,9 @@
         <f>IF(P27=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y27" s="40" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y27" s="40"/>
+    </row>
+    <row r="28" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
         <v>732</v>
       </c>
@@ -6466,11 +6604,9 @@
         <f>IF(P28=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y28" s="40" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y28" s="40"/>
+    </row>
+    <row r="29" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>733</v>
       </c>
@@ -6547,11 +6683,9 @@
         <f>IF(P29=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y29" s="40" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y29" s="40"/>
+    </row>
+    <row r="30" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
         <v>734</v>
       </c>
@@ -6626,11 +6760,9 @@
         <f>IF(P30=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="40" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y30" s="40"/>
+    </row>
+    <row r="31" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
         <v>735</v>
       </c>
@@ -6707,11 +6839,9 @@
         <f>IF(P31=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y31" s="40" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y31" s="40"/>
+    </row>
+    <row r="32" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
         <v>736</v>
       </c>
@@ -6786,11 +6916,9 @@
         <f>IF(P32=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y32" s="40" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y32" s="40"/>
+    </row>
+    <row r="33" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
         <v>737</v>
       </c>
@@ -6867,11 +6995,9 @@
         <f>IF(P33=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y33" s="40" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y33" s="40"/>
+    </row>
+    <row r="34" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
         <v>738</v>
       </c>
@@ -6948,11 +7074,9 @@
         <f>IF(P34=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y34" s="40" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y34" s="40"/>
+    </row>
+    <row r="35" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>739</v>
       </c>
@@ -7029,11 +7153,9 @@
         <f>IF(P35=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y35" s="40" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y35" s="40"/>
+    </row>
+    <row r="36" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
         <v>740</v>
       </c>
@@ -7110,11 +7232,9 @@
         <f>IF(P36=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y36" s="40" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y36" s="40"/>
+    </row>
+    <row r="37" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
         <v>741</v>
       </c>
@@ -7189,11 +7309,9 @@
         <f>IF(P37=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y37" s="40" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y37" s="40"/>
+    </row>
+    <row r="38" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>742</v>
       </c>
@@ -7270,11 +7388,9 @@
         <f>IF(P38=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y38" s="40" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y38" s="40"/>
+    </row>
+    <row r="39" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>743</v>
       </c>
@@ -7351,11 +7467,9 @@
         <f>IF(P39=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y39" s="40" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y39" s="40"/>
+    </row>
+    <row r="40" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
         <v>744</v>
       </c>
@@ -7432,11 +7546,9 @@
         <f>IF(P40=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y40" s="40" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y40" s="40"/>
+    </row>
+    <row r="41" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
         <v>745</v>
       </c>
@@ -7513,11 +7625,9 @@
         <f>IF(P41=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y41" s="40" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y41" s="40"/>
+    </row>
+    <row r="42" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
         <v>746</v>
       </c>
@@ -7594,11 +7704,9 @@
         <f>IF(P42=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y42" s="40" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y42" s="40"/>
+    </row>
+    <row r="43" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
         <v>747</v>
       </c>
@@ -7675,11 +7783,9 @@
         <f>IF(P43=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y43" s="40" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y43" s="40"/>
+    </row>
+    <row r="44" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
         <v>748</v>
       </c>
@@ -7756,11 +7862,9 @@
         <f>IF(P44=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y44" s="40" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y44" s="40"/>
+    </row>
+    <row r="45" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
         <v>749</v>
       </c>
@@ -7827,11 +7931,9 @@
         <f>IF(P45=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y45" s="40" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y45" s="40"/>
+    </row>
+    <row r="46" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
         <v>750</v>
       </c>
@@ -7908,19 +8010,17 @@
         <f>IF(P46=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y46" s="40" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y46" s="40"/>
+    </row>
+    <row r="47" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>1006</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>1007</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>48</v>
@@ -7984,11 +8084,9 @@
         <f>IF(P47=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y47" s="40" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y47" s="40"/>
+    </row>
+    <row r="48" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
         <v>838</v>
       </c>
@@ -8033,28 +8131,32 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="28"/>
       <c r="R48" s="1">
+        <f>IF(K48=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S48" s="1">
+        <f>IF(L48=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T48" s="1">
+        <f>IF(M48=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U48" s="1">
+        <f>IF(N48=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V48" s="1">
+        <f>IF(O48=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W48" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="40" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P48=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="40"/>
+    </row>
+    <row r="49" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -8097,26 +8199,32 @@
       </c>
       <c r="Q49" s="28"/>
       <c r="R49" s="1">
+        <f>IF(K49=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S49" s="1">
+        <f>IF(L49=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T49" s="1">
+        <f>IF(M49=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U49" s="1">
+        <f>IF(N49=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V49" s="1">
+        <f>IF(O49=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W49" s="1">
+        <f>IF(P49=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="Y49" s="40"/>
     </row>
-    <row r="50" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
         <v>751</v>
       </c>
@@ -8165,28 +8273,32 @@
       </c>
       <c r="Q50" s="28"/>
       <c r="R50" s="1">
+        <f>IF(K50=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S50" s="1">
+        <f>IF(L50=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T50" s="1">
+        <f>IF(M50=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U50" s="1">
+        <f>IF(N50=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V50" s="1">
+        <f>IF(O50=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="20" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P50=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="20"/>
+    </row>
+    <row r="51" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
         <v>752</v>
       </c>
@@ -8235,28 +8347,32 @@
       </c>
       <c r="Q51" s="28"/>
       <c r="R51" s="1">
+        <f>IF(K51=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S51" s="1">
+        <f>IF(L51=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T51" s="1">
+        <f>IF(M51=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U51" s="1">
+        <f>IF(N51=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V51" s="1">
+        <f>IF(O51=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W51" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y51" s="40" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P51=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y51" s="40"/>
+    </row>
+    <row r="52" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
         <v>753</v>
       </c>
@@ -8307,28 +8423,32 @@
         <v>3</v>
       </c>
       <c r="R52" s="1">
+        <f>IF(K52=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S52" s="1">
+        <f>IF(L52=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T52" s="1">
+        <f>IF(M52=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U52" s="1">
+        <f>IF(N52=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V52" s="1">
+        <f>IF(O52=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W52" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y52" s="40" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P52=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y52" s="40"/>
+    </row>
+    <row r="53" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
         <v>754</v>
       </c>
@@ -8379,28 +8499,32 @@
         <v>1</v>
       </c>
       <c r="R53" s="1">
+        <f>IF(K53=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S53" s="1">
+        <f>IF(L53=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T53" s="1">
+        <f>IF(M53=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U53" s="1">
+        <f>IF(N53=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V53" s="1">
+        <f>IF(O53=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W53" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y53" s="40" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P53=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y53" s="40"/>
+    </row>
+    <row r="54" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
         <v>755</v>
       </c>
@@ -8449,28 +8573,32 @@
       </c>
       <c r="Q54" s="28"/>
       <c r="R54" s="1">
+        <f>IF(K54=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S54" s="1">
+        <f>IF(L54=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T54" s="1">
+        <f>IF(M54=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U54" s="1">
+        <f>IF(N54=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V54" s="1">
+        <f>IF(O54=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W54" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y54" s="40" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P54=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y54" s="40"/>
+    </row>
+    <row r="55" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
         <v>756</v>
       </c>
@@ -8521,28 +8649,32 @@
         <v>3</v>
       </c>
       <c r="R55" s="1">
+        <f>IF(K55=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S55" s="1">
+        <f>IF(L55=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T55" s="1">
+        <f>IF(M55=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U55" s="1">
+        <f>IF(N55=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V55" s="1">
+        <f>IF(O55=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W55" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y55" s="40" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P55=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y55" s="40"/>
+    </row>
+    <row r="56" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
         <v>757</v>
       </c>
@@ -8591,28 +8723,32 @@
       </c>
       <c r="Q56" s="28"/>
       <c r="R56" s="1">
+        <f>IF(K56=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S56" s="1">
+        <f>IF(L56=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T56" s="1">
+        <f>IF(M56=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U56" s="1">
+        <f>IF(N56=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V56" s="1">
+        <f>IF(O56=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W56" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="40" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P56=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y56" s="40"/>
+    </row>
+    <row r="57" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
         <v>758</v>
       </c>
@@ -8663,28 +8799,32 @@
         <v>4</v>
       </c>
       <c r="R57" s="1">
+        <f>IF(K57=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S57" s="1">
+        <f>IF(L57=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T57" s="1">
+        <f>IF(M57=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U57" s="1">
+        <f>IF(N57=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V57" s="1">
+        <f>IF(O57=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W57" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y57" s="40" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P57=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y57" s="40"/>
+    </row>
+    <row r="58" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
         <v>759</v>
       </c>
@@ -8735,28 +8875,32 @@
         <v>4</v>
       </c>
       <c r="R58" s="1">
+        <f>IF(K58=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S58" s="1">
+        <f>IF(L58=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T58" s="1">
+        <f>IF(M58=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U58" s="1">
+        <f>IF(N58=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V58" s="1">
+        <f>IF(O58=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W58" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y58" s="40" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P58=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y58" s="40"/>
+    </row>
+    <row r="59" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
         <v>760</v>
       </c>
@@ -8807,28 +8951,32 @@
         <v>4</v>
       </c>
       <c r="R59" s="1">
+        <f>IF(K59=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S59" s="1">
+        <f>IF(L59=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T59" s="1">
+        <f>IF(M59=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U59" s="1">
+        <f>IF(N59=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V59" s="1">
+        <f>IF(O59=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W59" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y59" s="40" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P59=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y59" s="40"/>
+    </row>
+    <row r="60" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
         <v>761</v>
       </c>
@@ -8873,28 +9021,32 @@
       <c r="P60" s="1"/>
       <c r="Q60" s="28"/>
       <c r="R60" s="1">
+        <f>IF(K60=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S60" s="1">
+        <f>IF(L60=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T60" s="1">
+        <f>IF(M60=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U60" s="1">
+        <f>IF(N60=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V60" s="1">
+        <f>IF(O60=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="40" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P60=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="40"/>
+    </row>
+    <row r="61" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
         <v>762</v>
       </c>
@@ -8945,28 +9097,32 @@
         <v>4</v>
       </c>
       <c r="R61" s="1">
+        <f>IF(K61=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S61" s="1">
+        <f>IF(L61=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T61" s="1">
+        <f>IF(M61=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U61" s="1">
+        <f>IF(N61=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V61" s="1">
+        <f>IF(O61=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W61" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y61" s="40" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P61=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y61" s="40"/>
+    </row>
+    <row r="62" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
         <v>763</v>
       </c>
@@ -9015,28 +9171,32 @@
       </c>
       <c r="Q62" s="28"/>
       <c r="R62" s="1">
+        <f>IF(K62=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S62" s="1">
+        <f>IF(L62=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T62" s="1">
+        <f>IF(M62=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U62" s="1">
+        <f>IF(N62=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V62" s="1">
+        <f>IF(O62=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W62" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y62" s="40" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P62=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y62" s="40"/>
+    </row>
+    <row r="63" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
         <v>764</v>
       </c>
@@ -9085,28 +9245,32 @@
       </c>
       <c r="Q63" s="28"/>
       <c r="R63" s="1">
+        <f>IF(K63=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S63" s="1">
+        <f>IF(L63=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T63" s="1">
+        <f>IF(M63=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U63" s="1">
+        <f>IF(N63=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V63" s="1">
+        <f>IF(O63=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W63" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y63" s="40" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P63=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y63" s="40"/>
+    </row>
+    <row r="64" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
         <v>765</v>
       </c>
@@ -9157,28 +9321,32 @@
         <v>4</v>
       </c>
       <c r="R64" s="1">
+        <f>IF(K64=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S64" s="1">
+        <f>IF(L64=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T64" s="1">
+        <f>IF(M64=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U64" s="1">
+        <f>IF(N64=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V64" s="1">
+        <f>IF(O64=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W64" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y64" s="40" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P64=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y64" s="40"/>
+    </row>
+    <row r="65" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
         <v>766</v>
       </c>
@@ -9227,28 +9395,32 @@
       </c>
       <c r="Q65" s="28"/>
       <c r="R65" s="1">
+        <f>IF(K65=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S65" s="1">
+        <f>IF(L65=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T65" s="1">
+        <f>IF(M65=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U65" s="1">
+        <f>IF(N65=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V65" s="1">
+        <f>IF(O65=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W65" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="40" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P65=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y65" s="40"/>
+    </row>
+    <row r="66" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
         <v>767</v>
       </c>
@@ -9297,28 +9469,32 @@
       </c>
       <c r="Q66" s="28"/>
       <c r="R66" s="1">
+        <f>IF(K66=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S66" s="1">
+        <f>IF(L66=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T66" s="1">
+        <f>IF(M66=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U66" s="1">
+        <f>IF(N66=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V66" s="1">
+        <f>IF(O66=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W66" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y66" s="40" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P66=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y66" s="40"/>
+    </row>
+    <row r="67" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
         <v>768</v>
       </c>
@@ -9369,36 +9545,40 @@
         <v>4</v>
       </c>
       <c r="R67" s="1">
+        <f>IF(K67=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S67" s="1">
+        <f>IF(L67=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T67" s="1">
+        <f>IF(M67=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U67" s="1">
+        <f>IF(N67=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V67" s="1">
+        <f>IF(O67=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W67" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y67" s="40" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <f>IF(P67=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y67" s="40"/>
+    </row>
+    <row r="68" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>48</v>
@@ -9441,26 +9621,30 @@
         <v>3</v>
       </c>
       <c r="R68" s="1">
+        <f>IF(K68=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S68" s="1">
+        <f>IF(L68=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T68" s="1">
+        <f>IF(M68=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U68" s="1">
+        <f>IF(N68=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V68" s="1">
+        <f>IF(O68=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W68" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y68" s="40" t="s">
-        <v>1004</v>
-      </c>
+        <f>IF(P68=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y68" s="40"/>
     </row>
     <row r="69" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
@@ -9513,26 +9697,30 @@
         <v>3</v>
       </c>
       <c r="R69" s="1">
+        <f>IF(K69=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S69" s="1">
+        <f>IF(L69=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T69" s="1">
+        <f>IF(M69=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U69" s="1">
+        <f>IF(N69=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V69" s="1">
+        <f>IF(O69=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W69" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y69" s="40" t="s">
-        <v>769</v>
-      </c>
+        <f>IF(P69=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y69" s="40"/>
     </row>
     <row r="70" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
@@ -9585,26 +9773,30 @@
         <v>2</v>
       </c>
       <c r="R70" s="1">
+        <f>IF(K70=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S70" s="1">
+        <f>IF(L70=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T70" s="1">
+        <f>IF(M70=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U70" s="1">
+        <f>IF(N70=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V70" s="1">
+        <f>IF(O70=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W70" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y70" s="40" t="s">
-        <v>770</v>
-      </c>
+        <f>IF(P70=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y70" s="40"/>
     </row>
     <row r="71" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
@@ -9657,26 +9849,30 @@
         <v>3</v>
       </c>
       <c r="R71" s="1">
+        <f>IF(K71=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S71" s="1">
+        <f>IF(L71=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T71" s="1">
+        <f>IF(M71=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U71" s="1">
+        <f>IF(N71=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V71" s="1">
+        <f>IF(O71=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W71" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y71" s="40" t="s">
-        <v>771</v>
-      </c>
+        <f>IF(P71=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y71" s="40"/>
     </row>
     <row r="72" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
@@ -9725,26 +9921,30 @@
         <v>3</v>
       </c>
       <c r="R72" s="1">
+        <f>IF(K72=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S72" s="1">
+        <f>IF(L72=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T72" s="1">
+        <f>IF(M72=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U72" s="1">
+        <f>IF(N72=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V72" s="1">
+        <f>IF(O72=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="40" t="s">
-        <v>772</v>
-      </c>
+        <f>IF(P72=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y72" s="40"/>
     </row>
     <row r="73" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
@@ -9797,26 +9997,30 @@
         <v>5</v>
       </c>
       <c r="R73" s="1">
+        <f>IF(K73=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S73" s="1">
+        <f>IF(L73=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T73" s="1">
+        <f>IF(M73=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U73" s="1">
+        <f>IF(N73=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V73" s="1">
+        <f>IF(O73=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W73" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y73" s="40" t="s">
-        <v>773</v>
-      </c>
+        <f>IF(P73=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y73" s="40"/>
     </row>
     <row r="74" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
@@ -9869,26 +10073,30 @@
         <v>3</v>
       </c>
       <c r="R74" s="1">
+        <f>IF(K74=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S74" s="1">
+        <f>IF(L74=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T74" s="1">
+        <f>IF(M74=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U74" s="1">
+        <f>IF(N74=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V74" s="1">
+        <f>IF(O74=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W74" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y74" s="40" t="s">
-        <v>774</v>
-      </c>
+        <f>IF(P74=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y74" s="40"/>
     </row>
     <row r="75" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
@@ -9941,26 +10149,30 @@
         <v>2</v>
       </c>
       <c r="R75" s="1">
+        <f>IF(K75=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S75" s="1">
+        <f>IF(L75=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T75" s="1">
+        <f>IF(M75=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U75" s="1">
+        <f>IF(N75=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V75" s="1">
+        <f>IF(O75=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W75" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y75" s="40" t="s">
-        <v>775</v>
-      </c>
+        <f>IF(P75=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y75" s="40"/>
     </row>
     <row r="76" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
@@ -10013,26 +10225,30 @@
         <v>5</v>
       </c>
       <c r="R76" s="1">
+        <f>IF(K76=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S76" s="1">
+        <f>IF(L76=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T76" s="1">
+        <f>IF(M76=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U76" s="1">
+        <f>IF(N76=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V76" s="1">
+        <f>IF(O76=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W76" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="40" t="s">
-        <v>776</v>
-      </c>
+        <f>IF(P76=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y76" s="40"/>
     </row>
     <row r="77" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
@@ -10085,26 +10301,30 @@
         <v>3</v>
       </c>
       <c r="R77" s="1">
+        <f>IF(K77=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S77" s="1">
+        <f>IF(L77=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T77" s="1">
+        <f>IF(M77=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U77" s="1">
+        <f>IF(N77=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V77" s="1">
+        <f>IF(O77=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W77" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y77" s="40" t="s">
-        <v>777</v>
-      </c>
+        <f>IF(P77=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y77" s="40"/>
     </row>
     <row r="78" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
@@ -10157,26 +10377,30 @@
         <v>5</v>
       </c>
       <c r="R78" s="1">
+        <f>IF(K78=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S78" s="1">
+        <f>IF(L78=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T78" s="1">
+        <f>IF(M78=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U78" s="1">
+        <f>IF(N78=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V78" s="1">
+        <f>IF(O78=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W78" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y78" s="40" t="s">
-        <v>778</v>
-      </c>
+        <f>IF(P78=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y78" s="40"/>
     </row>
     <row r="79" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
@@ -10229,26 +10453,30 @@
         <v>5</v>
       </c>
       <c r="R79" s="1">
+        <f>IF(K79=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S79" s="1">
+        <f>IF(L79=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T79" s="1">
+        <f>IF(M79=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U79" s="1">
+        <f>IF(N79=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V79" s="1">
+        <f>IF(O79=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W79" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y79" s="40" t="s">
-        <v>779</v>
-      </c>
+        <f>IF(P79=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y79" s="40"/>
     </row>
     <row r="80" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
@@ -10301,26 +10529,30 @@
         <v>3</v>
       </c>
       <c r="R80" s="1">
+        <f>IF(K80=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S80" s="1">
+        <f>IF(L80=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T80" s="1">
+        <f>IF(M80=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U80" s="1">
+        <f>IF(N80=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V80" s="1">
+        <f>IF(O80=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W80" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y80" s="40" t="s">
-        <v>780</v>
-      </c>
+        <f>IF(P80=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y80" s="40"/>
     </row>
     <row r="81" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
@@ -10373,26 +10605,30 @@
         <v>3</v>
       </c>
       <c r="R81" s="1">
+        <f>IF(K81=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S81" s="1">
+        <f>IF(L81=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T81" s="1">
+        <f>IF(M81=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U81" s="1">
+        <f>IF(N81=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V81" s="1">
+        <f>IF(O81=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W81" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y81" s="40" t="s">
-        <v>781</v>
-      </c>
+        <f>IF(P81=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y81" s="40"/>
     </row>
     <row r="82" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
@@ -10445,26 +10681,30 @@
         <v>1</v>
       </c>
       <c r="R82" s="1">
+        <f>IF(K82=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S82" s="1">
+        <f>IF(L82=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T82" s="1">
+        <f>IF(M82=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U82" s="1">
+        <f>IF(N82=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="V82" s="1">
+        <f>IF(O82=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W82" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="40" t="s">
-        <v>782</v>
-      </c>
+        <f>IF(P82=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y82" s="40"/>
     </row>
     <row r="83" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
@@ -10515,26 +10755,30 @@
         <v>4</v>
       </c>
       <c r="R83" s="1">
+        <f>IF(K83=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S83" s="1">
+        <f>IF(L83=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T83" s="1">
+        <f>IF(M83=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U83" s="1">
+        <f>IF(N83=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V83" s="1">
+        <f>IF(O83=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W83" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y83" s="40" t="s">
-        <v>783</v>
-      </c>
+        <f>IF(P83=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y83" s="40"/>
     </row>
     <row r="84" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
@@ -10587,26 +10831,30 @@
         <v>3</v>
       </c>
       <c r="R84" s="1">
+        <f>IF(K84=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S84" s="1">
+        <f>IF(L84=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T84" s="1">
+        <f>IF(M84=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U84" s="1">
+        <f>IF(N84=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V84" s="1">
+        <f>IF(O84=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W84" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="40" t="s">
-        <v>784</v>
-      </c>
+        <f>IF(P84=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="40"/>
     </row>
     <row r="85" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
@@ -10659,26 +10907,30 @@
         <v>4</v>
       </c>
       <c r="R85" s="1">
+        <f>IF(K85=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S85" s="1">
+        <f>IF(L85=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T85" s="1">
+        <f>IF(M85=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U85" s="1">
+        <f>IF(N85=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V85" s="1">
+        <f>IF(O85=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W85" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y85" s="40" t="s">
-        <v>785</v>
-      </c>
+        <f>IF(P85=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y85" s="40"/>
     </row>
     <row r="86" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
@@ -10731,26 +10983,30 @@
         <v>3</v>
       </c>
       <c r="R86" s="1">
+        <f>IF(K86=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S86" s="1">
+        <f>IF(L86=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T86" s="1">
+        <f>IF(M86=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U86" s="1">
+        <f>IF(N86=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V86" s="1">
+        <f>IF(O86=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W86" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y86" s="40" t="s">
-        <v>786</v>
-      </c>
+        <f>IF(P86=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y86" s="40"/>
     </row>
     <row r="87" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
@@ -10803,26 +11059,30 @@
         <v>4</v>
       </c>
       <c r="R87" s="1">
+        <f>IF(K87=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S87" s="1">
+        <f>IF(L87=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T87" s="1">
+        <f>IF(M87=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U87" s="1">
+        <f>IF(N87=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V87" s="1">
+        <f>IF(O87=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W87" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y87" s="40" t="s">
-        <v>787</v>
-      </c>
+        <f>IF(P87=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y87" s="40"/>
     </row>
     <row r="88" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
@@ -10875,26 +11135,30 @@
         <v>2</v>
       </c>
       <c r="R88" s="1">
+        <f>IF(K88=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S88" s="1">
+        <f>IF(L88=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T88" s="1">
+        <f>IF(M88=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U88" s="1">
+        <f>IF(N88=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V88" s="1">
+        <f>IF(O88=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W88" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y88" s="40" t="s">
-        <v>788</v>
-      </c>
+        <f>IF(P88=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y88" s="40"/>
     </row>
     <row r="89" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
@@ -10947,26 +11211,30 @@
         <v>3</v>
       </c>
       <c r="R89" s="1">
+        <f>IF(K89=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S89" s="1">
+        <f>IF(L89=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="T89" s="1">
+        <f>IF(M89=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U89" s="1">
+        <f>IF(N89=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V89" s="1">
+        <f>IF(O89=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W89" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y89" s="40" t="s">
-        <v>789</v>
-      </c>
+        <f>IF(P89=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y89" s="40"/>
     </row>
     <row r="90" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
@@ -11019,26 +11287,30 @@
         <v>2</v>
       </c>
       <c r="R90" s="1">
+        <f>IF(K90=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="S90" s="1">
+        <f>IF(L90=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T90" s="1">
+        <f>IF(M90=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U90" s="1">
+        <f>IF(N90=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="V90" s="1">
+        <f>IF(O90=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W90" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y90" s="40" t="s">
-        <v>790</v>
-      </c>
+        <f>IF(P90=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y90" s="40"/>
     </row>
     <row r="91" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
@@ -11091,26 +11363,30 @@
         <v>4</v>
       </c>
       <c r="R91" s="1">
+        <f>IF(K91=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S91" s="1">
+        <f>IF(L91=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T91" s="1">
+        <f>IF(M91=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U91" s="1">
+        <f>IF(N91=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V91" s="1">
+        <f>IF(O91=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W91" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y91" s="40" t="s">
-        <v>791</v>
-      </c>
+        <f>IF(P91=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y91" s="40"/>
     </row>
     <row r="92" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
@@ -11163,26 +11439,30 @@
         <v>4</v>
       </c>
       <c r="R92" s="1">
+        <f>IF(K92=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S92" s="1">
+        <f>IF(L92=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T92" s="1">
+        <f>IF(M92=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="U92" s="1">
+        <f>IF(N92=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V92" s="1">
+        <f>IF(O92=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W92" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y92" s="40" t="s">
-        <v>920</v>
-      </c>
+        <f>IF(P92=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y92" s="40"/>
     </row>
     <row r="93" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
@@ -11235,26 +11515,30 @@
         <v>4</v>
       </c>
       <c r="R93" s="1">
+        <f>IF(K93=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S93" s="1">
+        <f>IF(L93=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T93" s="1">
+        <f>IF(M93=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U93" s="1">
+        <f>IF(N93=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V93" s="1">
+        <f>IF(O93=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="W93" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y93" s="40" t="s">
-        <v>792</v>
-      </c>
+        <f>IF(P93=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y93" s="40"/>
     </row>
     <row r="94" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
@@ -11305,26 +11589,30 @@
       </c>
       <c r="Q94" s="28"/>
       <c r="R94" s="1">
+        <f>IF(K94=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="S94" s="1">
+        <f>IF(L94=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="T94" s="1">
+        <f>IF(M94=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="U94" s="1">
+        <f>IF(N94=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
       </c>
       <c r="V94" s="1">
+        <f>IF(O94=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
       <c r="W94" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y94" s="40" t="s">
-        <v>925</v>
-      </c>
+        <f>IF(P94=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y94" s="40"/>
     </row>
     <row r="95" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="31" t="s">
@@ -11372,27 +11660,31 @@
       <c r="P95" s="32">
         <v>2</v>
       </c>
-      <c r="R95" s="32">
-        <v>1</v>
-      </c>
-      <c r="S95" s="32">
-        <v>1</v>
-      </c>
-      <c r="T95" s="32">
-        <v>1</v>
-      </c>
-      <c r="U95" s="32">
-        <v>1</v>
-      </c>
-      <c r="V95" s="32">
-        <v>1</v>
-      </c>
-      <c r="W95" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y95" s="40" t="s">
-        <v>929</v>
-      </c>
+      <c r="R95" s="1">
+        <f>IF(K95=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S95" s="1">
+        <f>IF(L95=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T95" s="1">
+        <f>IF(M95=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U95" s="1">
+        <f>IF(N95=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V95" s="1">
+        <f>IF(O95=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W95" s="1">
+        <f>IF(P95=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y95" s="40"/>
     </row>
     <row r="96" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="31" t="s">
@@ -11440,27 +11732,31 @@
       <c r="P96" s="32">
         <v>2</v>
       </c>
-      <c r="R96" s="32">
-        <v>1</v>
-      </c>
-      <c r="S96" s="32">
-        <v>1</v>
-      </c>
-      <c r="T96" s="32">
-        <v>1</v>
-      </c>
-      <c r="U96" s="32">
-        <v>1</v>
-      </c>
-      <c r="V96" s="32">
-        <v>1</v>
-      </c>
-      <c r="W96" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y96" s="40" t="s">
-        <v>932</v>
-      </c>
+      <c r="R96" s="1">
+        <f>IF(K96=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S96" s="1">
+        <f>IF(L96=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T96" s="1">
+        <f>IF(M96=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U96" s="1">
+        <f>IF(N96=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V96" s="1">
+        <f>IF(O96=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W96" s="1">
+        <f>IF(P96=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y96" s="40"/>
     </row>
     <row r="97" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="31" t="s">
@@ -11508,27 +11804,31 @@
       <c r="P97" s="32">
         <v>2</v>
       </c>
-      <c r="R97" s="32">
-        <v>0</v>
-      </c>
-      <c r="S97" s="32">
-        <v>0</v>
-      </c>
-      <c r="T97" s="32">
-        <v>1</v>
-      </c>
-      <c r="U97" s="32">
-        <v>0</v>
-      </c>
-      <c r="V97" s="32">
-        <v>0</v>
-      </c>
-      <c r="W97" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y97" s="40" t="s">
-        <v>935</v>
-      </c>
+      <c r="R97" s="1">
+        <f>IF(K97=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S97" s="1">
+        <f>IF(L97=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T97" s="1">
+        <f>IF(M97=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U97" s="1">
+        <f>IF(N97=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V97" s="1">
+        <f>IF(O97=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W97" s="1">
+        <f>IF(P97=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y97" s="40"/>
     </row>
     <row r="98" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="31" t="s">
@@ -11576,27 +11876,31 @@
       <c r="P98" s="32">
         <v>2</v>
       </c>
-      <c r="R98" s="32">
-        <v>1</v>
-      </c>
-      <c r="S98" s="32">
-        <v>1</v>
-      </c>
-      <c r="T98" s="32">
-        <v>1</v>
-      </c>
-      <c r="U98" s="32">
-        <v>1</v>
-      </c>
-      <c r="V98" s="32">
-        <v>1</v>
-      </c>
-      <c r="W98" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y98" s="40" t="s">
-        <v>937</v>
-      </c>
+      <c r="R98" s="1">
+        <f>IF(K98=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S98" s="1">
+        <f>IF(L98=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T98" s="1">
+        <f>IF(M98=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U98" s="1">
+        <f>IF(N98=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V98" s="1">
+        <f>IF(O98=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W98" s="1">
+        <f>IF(P98=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y98" s="40"/>
     </row>
     <row r="99" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="31" t="s">
@@ -11644,27 +11948,31 @@
       <c r="P99" s="32">
         <v>2</v>
       </c>
-      <c r="R99" s="32">
-        <v>1</v>
-      </c>
-      <c r="S99" s="32">
-        <v>1</v>
-      </c>
-      <c r="T99" s="32">
-        <v>0</v>
-      </c>
-      <c r="U99" s="32">
-        <v>0</v>
-      </c>
-      <c r="V99" s="32">
-        <v>1</v>
-      </c>
-      <c r="W99" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y99" s="40" t="s">
-        <v>940</v>
-      </c>
+      <c r="R99" s="1">
+        <f>IF(K99=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S99" s="1">
+        <f>IF(L99=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T99" s="1">
+        <f>IF(M99=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U99" s="1">
+        <f>IF(N99=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V99" s="1">
+        <f>IF(O99=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W99" s="1">
+        <f>IF(P99=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y99" s="40"/>
     </row>
     <row r="100" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="31" t="s">
@@ -11712,27 +12020,31 @@
       <c r="P100" s="32">
         <v>2</v>
       </c>
-      <c r="R100" s="32">
-        <v>0</v>
-      </c>
-      <c r="S100" s="32">
-        <v>0</v>
-      </c>
-      <c r="T100" s="32">
-        <v>1</v>
-      </c>
-      <c r="U100" s="32">
-        <v>1</v>
-      </c>
-      <c r="V100" s="32">
-        <v>1</v>
-      </c>
-      <c r="W100" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y100" s="40" t="s">
-        <v>943</v>
-      </c>
+      <c r="R100" s="1">
+        <f>IF(K100=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S100" s="1">
+        <f>IF(L100=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T100" s="1">
+        <f>IF(M100=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U100" s="1">
+        <f>IF(N100=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V100" s="1">
+        <f>IF(O100=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W100" s="1">
+        <f>IF(P100=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y100" s="40"/>
     </row>
     <row r="101" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="31" t="s">
@@ -11780,27 +12092,31 @@
       <c r="P101" s="32">
         <v>4</v>
       </c>
-      <c r="R101" s="32">
-        <v>0</v>
-      </c>
-      <c r="S101" s="32">
-        <v>0</v>
-      </c>
-      <c r="T101" s="32">
-        <v>0</v>
-      </c>
-      <c r="U101" s="32">
-        <v>0</v>
-      </c>
-      <c r="V101" s="32">
-        <v>0</v>
-      </c>
-      <c r="W101" s="32">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="40" t="s">
-        <v>945</v>
-      </c>
+      <c r="R101" s="1">
+        <f>IF(K101=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S101" s="1">
+        <f>IF(L101=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T101" s="1">
+        <f>IF(M101=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U101" s="1">
+        <f>IF(N101=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V101" s="1">
+        <f>IF(O101=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W101" s="1">
+        <f>IF(P101=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y101" s="40"/>
     </row>
     <row r="102" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="31" t="s">
@@ -11848,27 +12164,31 @@
       <c r="P102" s="32">
         <v>2</v>
       </c>
-      <c r="R102" s="32">
-        <v>1</v>
-      </c>
-      <c r="S102" s="32">
-        <v>0</v>
-      </c>
-      <c r="T102" s="32">
-        <v>1</v>
-      </c>
-      <c r="U102" s="32">
-        <v>1</v>
-      </c>
-      <c r="V102" s="32">
-        <v>1</v>
-      </c>
-      <c r="W102" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y102" s="40" t="s">
-        <v>948</v>
-      </c>
+      <c r="R102" s="1">
+        <f>IF(K102=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S102" s="1">
+        <f>IF(L102=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T102" s="1">
+        <f>IF(M102=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U102" s="1">
+        <f>IF(N102=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V102" s="1">
+        <f>IF(O102=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W102" s="1">
+        <f>IF(P102=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y102" s="40"/>
     </row>
     <row r="103" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="31" t="s">
@@ -11916,27 +12236,31 @@
       <c r="P103" s="32">
         <v>2</v>
       </c>
-      <c r="R103" s="32">
-        <v>0</v>
-      </c>
-      <c r="S103" s="32">
-        <v>0</v>
-      </c>
-      <c r="T103" s="32">
-        <v>1</v>
-      </c>
-      <c r="U103" s="32">
-        <v>1</v>
-      </c>
-      <c r="V103" s="32">
-        <v>0</v>
-      </c>
-      <c r="W103" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y103" s="40" t="s">
-        <v>951</v>
-      </c>
+      <c r="R103" s="1">
+        <f>IF(K103=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S103" s="1">
+        <f>IF(L103=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T103" s="1">
+        <f>IF(M103=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U103" s="1">
+        <f>IF(N103=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V103" s="1">
+        <f>IF(O103=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W103" s="1">
+        <f>IF(P103=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y103" s="40"/>
     </row>
     <row r="104" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="31" t="s">
@@ -11984,27 +12308,31 @@
       <c r="P104" s="32">
         <v>2</v>
       </c>
-      <c r="R104" s="32">
-        <v>0</v>
-      </c>
-      <c r="S104" s="32">
-        <v>1</v>
-      </c>
-      <c r="T104" s="32">
-        <v>1</v>
-      </c>
-      <c r="U104" s="32">
-        <v>1</v>
-      </c>
-      <c r="V104" s="32">
-        <v>0</v>
-      </c>
-      <c r="W104" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y104" s="40" t="s">
-        <v>954</v>
-      </c>
+      <c r="R104" s="1">
+        <f>IF(K104=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S104" s="1">
+        <f>IF(L104=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T104" s="1">
+        <f>IF(M104=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U104" s="1">
+        <f>IF(N104=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V104" s="1">
+        <f>IF(O104=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W104" s="1">
+        <f>IF(P104=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y104" s="40"/>
     </row>
     <row r="105" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="31" t="s">
@@ -12052,27 +12380,31 @@
       <c r="P105" s="32">
         <v>3</v>
       </c>
-      <c r="R105" s="32">
-        <v>1</v>
-      </c>
-      <c r="S105" s="32">
-        <v>0</v>
-      </c>
-      <c r="T105" s="32">
-        <v>1</v>
-      </c>
-      <c r="U105" s="32">
-        <v>0</v>
-      </c>
-      <c r="V105" s="32">
-        <v>0</v>
-      </c>
-      <c r="W105" s="32">
-        <v>0</v>
-      </c>
-      <c r="Y105" s="40" t="s">
-        <v>957</v>
-      </c>
+      <c r="R105" s="1">
+        <f>IF(K105=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S105" s="1">
+        <f>IF(L105=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T105" s="1">
+        <f>IF(M105=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U105" s="1">
+        <f>IF(N105=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V105" s="1">
+        <f>IF(O105=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W105" s="1">
+        <f>IF(P105=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y105" s="40"/>
     </row>
     <row r="106" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="31" t="s">
@@ -12120,27 +12452,31 @@
       <c r="P106" s="32">
         <v>2</v>
       </c>
-      <c r="R106" s="32">
-        <v>0</v>
-      </c>
-      <c r="S106" s="32">
-        <v>0</v>
-      </c>
-      <c r="T106" s="32">
-        <v>1</v>
-      </c>
-      <c r="U106" s="32">
-        <v>0</v>
-      </c>
-      <c r="V106" s="32">
-        <v>1</v>
-      </c>
-      <c r="W106" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y106" s="40" t="s">
-        <v>960</v>
-      </c>
+      <c r="R106" s="1">
+        <f>IF(K106=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S106" s="1">
+        <f>IF(L106=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T106" s="1">
+        <f>IF(M106=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U106" s="1">
+        <f>IF(N106=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V106" s="1">
+        <f>IF(O106=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W106" s="1">
+        <f>IF(P106=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y106" s="40"/>
     </row>
     <row r="107" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="31" t="s">
@@ -12188,27 +12524,31 @@
       <c r="P107" s="32">
         <v>2</v>
       </c>
-      <c r="R107" s="32">
-        <v>0</v>
-      </c>
-      <c r="S107" s="32">
-        <v>0</v>
-      </c>
-      <c r="T107" s="32">
-        <v>1</v>
-      </c>
-      <c r="U107" s="32">
-        <v>1</v>
-      </c>
-      <c r="V107" s="32">
-        <v>0</v>
-      </c>
-      <c r="W107" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y107" s="40" t="s">
-        <v>963</v>
-      </c>
+      <c r="R107" s="1">
+        <f>IF(K107=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S107" s="1">
+        <f>IF(L107=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T107" s="1">
+        <f>IF(M107=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U107" s="1">
+        <f>IF(N107=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V107" s="1">
+        <f>IF(O107=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W107" s="1">
+        <f>IF(P107=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y107" s="40"/>
     </row>
     <row r="108" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="31" t="s">
@@ -12256,27 +12596,31 @@
       <c r="P108" s="32">
         <v>1</v>
       </c>
-      <c r="R108" s="32">
-        <v>1</v>
-      </c>
-      <c r="S108" s="32">
-        <v>0</v>
-      </c>
-      <c r="T108" s="32">
-        <v>0</v>
-      </c>
-      <c r="U108" s="32">
-        <v>0</v>
-      </c>
-      <c r="V108" s="32">
-        <v>0</v>
-      </c>
-      <c r="W108" s="32">
-        <v>0</v>
-      </c>
-      <c r="Y108" s="40" t="s">
-        <v>965</v>
-      </c>
+      <c r="R108" s="1">
+        <f>IF(K108=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S108" s="1">
+        <f>IF(L108=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T108" s="1">
+        <f>IF(M108=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U108" s="1">
+        <f>IF(N108=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V108" s="1">
+        <f>IF(O108=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W108" s="1">
+        <f>IF(P108=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y108" s="40"/>
     </row>
     <row r="109" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="31" t="s">
@@ -12324,27 +12668,31 @@
       <c r="P109" s="32">
         <v>2</v>
       </c>
-      <c r="R109" s="32">
-        <v>0</v>
-      </c>
-      <c r="S109" s="32">
-        <v>0</v>
-      </c>
-      <c r="T109" s="32">
-        <v>1</v>
-      </c>
-      <c r="U109" s="32">
-        <v>1</v>
-      </c>
-      <c r="V109" s="32">
-        <v>0</v>
-      </c>
-      <c r="W109" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y109" s="40" t="s">
-        <v>968</v>
-      </c>
+      <c r="R109" s="1">
+        <f>IF(K109=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S109" s="1">
+        <f>IF(L109=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T109" s="1">
+        <f>IF(M109=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U109" s="1">
+        <f>IF(N109=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V109" s="1">
+        <f>IF(O109=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W109" s="1">
+        <f>IF(P109=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y109" s="40"/>
     </row>
     <row r="110" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="31" t="s">
@@ -12392,27 +12740,31 @@
       <c r="P110" s="32">
         <v>2</v>
       </c>
-      <c r="R110" s="32">
-        <v>1</v>
-      </c>
-      <c r="S110" s="32">
-        <v>1</v>
-      </c>
-      <c r="T110" s="32">
-        <v>1</v>
-      </c>
-      <c r="U110" s="32">
-        <v>1</v>
-      </c>
-      <c r="V110" s="32">
-        <v>0</v>
-      </c>
-      <c r="W110" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y110" s="40" t="s">
-        <v>971</v>
-      </c>
+      <c r="R110" s="1">
+        <f>IF(K110=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S110" s="1">
+        <f>IF(L110=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T110" s="1">
+        <f>IF(M110=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U110" s="1">
+        <f>IF(N110=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V110" s="1">
+        <f>IF(O110=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W110" s="1">
+        <f>IF(P110=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y110" s="40"/>
     </row>
     <row r="111" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="31" t="s">
@@ -12460,27 +12812,31 @@
       <c r="P111" s="32">
         <v>1</v>
       </c>
-      <c r="R111" s="32">
-        <v>1</v>
-      </c>
-      <c r="S111" s="32">
-        <v>1</v>
-      </c>
-      <c r="T111" s="32">
-        <v>1</v>
-      </c>
-      <c r="U111" s="32">
-        <v>1</v>
-      </c>
-      <c r="V111" s="32">
-        <v>0</v>
-      </c>
-      <c r="W111" s="32">
-        <v>0</v>
-      </c>
-      <c r="Y111" s="40" t="s">
-        <v>974</v>
-      </c>
+      <c r="R111" s="1">
+        <f>IF(K111=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S111" s="1">
+        <f>IF(L111=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T111" s="1">
+        <f>IF(M111=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U111" s="1">
+        <f>IF(N111=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V111" s="1">
+        <f>IF(O111=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W111" s="1">
+        <f>IF(P111=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y111" s="40"/>
     </row>
     <row r="112" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="31" t="s">
@@ -12528,27 +12884,31 @@
       <c r="P112" s="32">
         <v>2</v>
       </c>
-      <c r="R112" s="32">
-        <v>1</v>
-      </c>
-      <c r="S112" s="32">
-        <v>1</v>
-      </c>
-      <c r="T112" s="32">
-        <v>1</v>
-      </c>
-      <c r="U112" s="32">
-        <v>1</v>
-      </c>
-      <c r="V112" s="32">
-        <v>1</v>
-      </c>
-      <c r="W112" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y112" s="40" t="s">
-        <v>977</v>
-      </c>
+      <c r="R112" s="1">
+        <f>IF(K112=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S112" s="1">
+        <f>IF(L112=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T112" s="1">
+        <f>IF(M112=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U112" s="1">
+        <f>IF(N112=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V112" s="1">
+        <f>IF(O112=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W112" s="1">
+        <f>IF(P112=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y112" s="40"/>
     </row>
     <row r="113" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="31" t="s">
@@ -12596,27 +12956,31 @@
       <c r="P113" s="32">
         <v>2</v>
       </c>
-      <c r="R113" s="32">
-        <v>1</v>
-      </c>
-      <c r="S113" s="32">
-        <v>0</v>
-      </c>
-      <c r="T113" s="32">
-        <v>1</v>
-      </c>
-      <c r="U113" s="32">
-        <v>1</v>
-      </c>
-      <c r="V113" s="32">
-        <v>0</v>
-      </c>
-      <c r="W113" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y113" s="40" t="s">
-        <v>980</v>
-      </c>
+      <c r="R113" s="1">
+        <f>IF(K113=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S113" s="1">
+        <f>IF(L113=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T113" s="1">
+        <f>IF(M113=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U113" s="1">
+        <f>IF(N113=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V113" s="1">
+        <f>IF(O113=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W113" s="1">
+        <f>IF(P113=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y113" s="40"/>
     </row>
     <row r="114" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="31" t="s">
@@ -12664,27 +13028,31 @@
       <c r="P114" s="32">
         <v>2</v>
       </c>
-      <c r="R114" s="32">
-        <v>1</v>
-      </c>
-      <c r="S114" s="32">
-        <v>0</v>
-      </c>
-      <c r="T114" s="32">
-        <v>1</v>
-      </c>
-      <c r="U114" s="32">
-        <v>0</v>
-      </c>
-      <c r="V114" s="32">
-        <v>1</v>
-      </c>
-      <c r="W114" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y114" s="40" t="s">
-        <v>983</v>
-      </c>
+      <c r="R114" s="1">
+        <f>IF(K114=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S114" s="1">
+        <f>IF(L114=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T114" s="1">
+        <f>IF(M114=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U114" s="1">
+        <f>IF(N114=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V114" s="1">
+        <f>IF(O114=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W114" s="1">
+        <f>IF(P114=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y114" s="40"/>
     </row>
     <row r="115" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="31" t="s">
@@ -12732,27 +13100,31 @@
       <c r="P115" s="32">
         <v>2</v>
       </c>
-      <c r="R115" s="32">
-        <v>0</v>
-      </c>
-      <c r="S115" s="32">
-        <v>0</v>
-      </c>
-      <c r="T115" s="32">
-        <v>0</v>
-      </c>
-      <c r="U115" s="32">
-        <v>1</v>
-      </c>
-      <c r="V115" s="32">
-        <v>1</v>
-      </c>
-      <c r="W115" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y115" s="40" t="s">
-        <v>985</v>
-      </c>
+      <c r="R115" s="1">
+        <f>IF(K115=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S115" s="1">
+        <f>IF(L115=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T115" s="1">
+        <f>IF(M115=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U115" s="1">
+        <f>IF(N115=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V115" s="1">
+        <f>IF(O115=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W115" s="1">
+        <f>IF(P115=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y115" s="40"/>
     </row>
     <row r="116" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="31" t="s">
@@ -12800,27 +13172,31 @@
       <c r="P116" s="32">
         <v>2</v>
       </c>
-      <c r="R116" s="32">
-        <v>1</v>
-      </c>
-      <c r="S116" s="32">
-        <v>1</v>
-      </c>
-      <c r="T116" s="32">
-        <v>1</v>
-      </c>
-      <c r="U116" s="32">
-        <v>1</v>
-      </c>
-      <c r="V116" s="32">
-        <v>1</v>
-      </c>
-      <c r="W116" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y116" s="40" t="s">
-        <v>988</v>
-      </c>
+      <c r="R116" s="1">
+        <f>IF(K116=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S116" s="1">
+        <f>IF(L116=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T116" s="1">
+        <f>IF(M116=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U116" s="1">
+        <f>IF(N116=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V116" s="1">
+        <f>IF(O116=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W116" s="1">
+        <f>IF(P116=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y116" s="40"/>
     </row>
     <row r="117" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="31" t="s">
@@ -12868,27 +13244,31 @@
       <c r="P117" s="32">
         <v>2</v>
       </c>
-      <c r="R117" s="32">
-        <v>1</v>
-      </c>
-      <c r="S117" s="32">
-        <v>1</v>
-      </c>
-      <c r="T117" s="32">
-        <v>1</v>
-      </c>
-      <c r="U117" s="32">
-        <v>0</v>
-      </c>
-      <c r="V117" s="32">
-        <v>0</v>
-      </c>
-      <c r="W117" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y117" s="40" t="s">
-        <v>991</v>
-      </c>
+      <c r="R117" s="1">
+        <f>IF(K117=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S117" s="1">
+        <f>IF(L117=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T117" s="1">
+        <f>IF(M117=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U117" s="1">
+        <f>IF(N117=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V117" s="1">
+        <f>IF(O117=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W117" s="1">
+        <f>IF(P117=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y117" s="40"/>
     </row>
     <row r="118" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="31" t="s">
@@ -12936,27 +13316,31 @@
       <c r="P118" s="32">
         <v>2</v>
       </c>
-      <c r="R118" s="32">
-        <v>1</v>
-      </c>
-      <c r="S118" s="32">
-        <v>1</v>
-      </c>
-      <c r="T118" s="32">
-        <v>1</v>
-      </c>
-      <c r="U118" s="32">
-        <v>0</v>
-      </c>
-      <c r="V118" s="32">
-        <v>0</v>
-      </c>
-      <c r="W118" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y118" s="40" t="s">
-        <v>994</v>
-      </c>
+      <c r="R118" s="1">
+        <f>IF(K118=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S118" s="1">
+        <f>IF(L118=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T118" s="1">
+        <f>IF(M118=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U118" s="1">
+        <f>IF(N118=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V118" s="1">
+        <f>IF(O118=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W118" s="1">
+        <f>IF(P118=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y118" s="40"/>
     </row>
     <row r="119" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="31" t="s">
@@ -13004,27 +13388,31 @@
       <c r="P119" s="32">
         <v>2</v>
       </c>
-      <c r="R119" s="32">
-        <v>0</v>
-      </c>
-      <c r="S119" s="32">
-        <v>1</v>
-      </c>
-      <c r="T119" s="32">
-        <v>1</v>
-      </c>
-      <c r="U119" s="32">
-        <v>1</v>
-      </c>
-      <c r="V119" s="32">
-        <v>0</v>
-      </c>
-      <c r="W119" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y119" s="40" t="s">
-        <v>997</v>
-      </c>
+      <c r="R119" s="1">
+        <f>IF(K119=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S119" s="1">
+        <f>IF(L119=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T119" s="1">
+        <f>IF(M119=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U119" s="1">
+        <f>IF(N119=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V119" s="1">
+        <f>IF(O119=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W119" s="1">
+        <f>IF(P119=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y119" s="40"/>
     </row>
     <row r="120" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="31" t="s">
@@ -13072,47 +13460,1407 @@
       <c r="P120" s="32">
         <v>2</v>
       </c>
-      <c r="R120" s="32">
-        <v>1</v>
-      </c>
-      <c r="S120" s="32">
-        <v>1</v>
-      </c>
-      <c r="T120" s="32">
-        <v>1</v>
-      </c>
-      <c r="U120" s="32">
-        <v>1</v>
-      </c>
-      <c r="V120" s="32">
-        <v>1</v>
-      </c>
-      <c r="W120" s="32">
-        <v>1</v>
-      </c>
-      <c r="Y120" s="40" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="121" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I121" s="39">
+      <c r="R120" s="1">
+        <f>IF(K120=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S120" s="1">
+        <f>IF(L120=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T120" s="1">
+        <f>IF(M120=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U120" s="1">
+        <f>IF(N120=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V120" s="1">
+        <f>IF(O120=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W120" s="1">
+        <f>IF(P120=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y120" s="40"/>
+    </row>
+    <row r="121" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D121" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E121" s="32">
+        <v>8</v>
+      </c>
+      <c r="F121" s="32">
+        <v>9</v>
+      </c>
+      <c r="G121" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I121" s="32">
+        <v>2</v>
+      </c>
+      <c r="J121" s="41"/>
+      <c r="K121" s="32">
+        <v>3</v>
+      </c>
+      <c r="L121" s="32">
+        <v>2</v>
+      </c>
+      <c r="M121" s="32">
+        <v>4</v>
+      </c>
+      <c r="N121" s="32">
+        <v>1</v>
+      </c>
+      <c r="O121" s="32">
+        <v>3</v>
+      </c>
+      <c r="P121" s="32">
+        <v>2</v>
+      </c>
+      <c r="R121" s="1">
+        <f>IF(K121=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S121" s="1">
+        <f>IF(L121=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T121" s="1">
+        <f>IF(M121=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U121" s="1">
+        <f>IF(N121=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V121" s="1">
+        <f>IF(O121=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W121" s="1">
+        <f>IF(P121=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y121" s="40"/>
+    </row>
+    <row r="122" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D122" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E122" s="32">
+        <v>8</v>
+      </c>
+      <c r="F122" s="32">
+        <v>9</v>
+      </c>
+      <c r="G122" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I122" s="32">
+        <v>2</v>
+      </c>
+      <c r="J122" s="41"/>
+      <c r="K122" s="32">
+        <v>4</v>
+      </c>
+      <c r="L122" s="32">
+        <v>2</v>
+      </c>
+      <c r="M122" s="32">
+        <v>3</v>
+      </c>
+      <c r="N122" s="32">
+        <v>2</v>
+      </c>
+      <c r="O122" s="32">
+        <v>3</v>
+      </c>
+      <c r="P122" s="32">
+        <v>1</v>
+      </c>
+      <c r="R122" s="1">
+        <f>IF(K122=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S122" s="1">
+        <f>IF(L122=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T122" s="1">
+        <f>IF(M122=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U122" s="1">
+        <f>IF(N122=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V122" s="1">
+        <f>IF(O122=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W122" s="1">
+        <f>IF(P122=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D123" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E123" s="32">
+        <v>8</v>
+      </c>
+      <c r="F123" s="32">
+        <v>9</v>
+      </c>
+      <c r="G123" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I123" s="32">
+        <v>3</v>
+      </c>
+      <c r="J123" s="41"/>
+      <c r="K123" s="32">
+        <v>3</v>
+      </c>
+      <c r="L123" s="32">
+        <v>4</v>
+      </c>
+      <c r="M123" s="32">
+        <v>3</v>
+      </c>
+      <c r="N123" s="32">
+        <v>2</v>
+      </c>
+      <c r="O123" s="32">
+        <v>1</v>
+      </c>
+      <c r="R123" s="1">
+        <f>IF(K123=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S123" s="1">
+        <f>IF(L123=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T123" s="1">
+        <f>IF(M123=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U123" s="1">
+        <f>IF(N123=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V123" s="1">
+        <f>IF(O123=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W123" s="1">
+        <f>IF(P123=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="30" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B124" s="30" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C124" s="30" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D124" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E124" s="32">
+        <v>8</v>
+      </c>
+      <c r="F124" s="32">
+        <v>9</v>
+      </c>
+      <c r="G124" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I124" s="32">
+        <v>3</v>
+      </c>
+      <c r="J124" s="41"/>
+      <c r="K124" s="32">
+        <v>4</v>
+      </c>
+      <c r="L124" s="32">
+        <v>2</v>
+      </c>
+      <c r="M124" s="32">
+        <v>3</v>
+      </c>
+      <c r="N124" s="32">
+        <v>2</v>
+      </c>
+      <c r="O124" s="32">
+        <v>4</v>
+      </c>
+      <c r="P124" s="32">
+        <v>2</v>
+      </c>
+      <c r="R124" s="1">
+        <f>IF(K124=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S124" s="1">
+        <f>IF(L124=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T124" s="1">
+        <f>IF(M124=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U124" s="1">
+        <f>IF(N124=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V124" s="1">
+        <f>IF(O124=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W124" s="1">
+        <f>IF(P124=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="30" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B125" s="30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C125" s="30" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D125" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E125" s="32">
+        <v>8</v>
+      </c>
+      <c r="F125" s="32">
+        <v>9</v>
+      </c>
+      <c r="G125" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I125" s="32">
+        <v>3</v>
+      </c>
+      <c r="J125" s="41"/>
+      <c r="K125" s="32">
+        <v>4</v>
+      </c>
+      <c r="L125" s="32">
+        <v>1</v>
+      </c>
+      <c r="M125" s="32">
+        <v>3</v>
+      </c>
+      <c r="N125" s="32">
+        <v>2</v>
+      </c>
+      <c r="O125" s="32">
+        <v>1</v>
+      </c>
+      <c r="P125" s="32">
+        <v>1</v>
+      </c>
+      <c r="R125" s="1">
+        <f>IF(K125=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S125" s="1">
+        <f>IF(L125=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T125" s="1">
+        <f>IF(M125=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U125" s="1">
+        <f>IF(N125=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V125" s="1">
+        <f>IF(O125=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W125" s="1">
+        <f>IF(P125=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="30" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B126" s="30" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C126" s="30" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D126" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126" s="32">
+        <v>8</v>
+      </c>
+      <c r="F126" s="32">
+        <v>9</v>
+      </c>
+      <c r="G126" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I126" s="32">
+        <v>0</v>
+      </c>
+      <c r="J126" s="41"/>
+      <c r="R126" s="1">
+        <f>IF(K126=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S126" s="1">
+        <f>IF(L126=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T126" s="1">
+        <f>IF(M126=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U126" s="1">
+        <f>IF(N126=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V126" s="1">
+        <f>IF(O126=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W126" s="1">
+        <f>IF(P126=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="30" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B127" s="30" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C127" s="30" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D127" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E127" s="32">
+        <v>8</v>
+      </c>
+      <c r="F127" s="32">
+        <v>9</v>
+      </c>
+      <c r="G127" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I127" s="32">
+        <v>2</v>
+      </c>
+      <c r="J127" s="41"/>
+      <c r="K127" s="32">
+        <v>1</v>
+      </c>
+      <c r="L127" s="32">
+        <v>2</v>
+      </c>
+      <c r="M127" s="32">
+        <v>3</v>
+      </c>
+      <c r="N127" s="32">
+        <v>3</v>
+      </c>
+      <c r="O127" s="32">
+        <v>2</v>
+      </c>
+      <c r="P127" s="32">
+        <v>2</v>
+      </c>
+      <c r="R127" s="1">
+        <f>IF(K127=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S127" s="1">
+        <f>IF(L127=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T127" s="1">
+        <f>IF(M127=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U127" s="1">
+        <f>IF(N127=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V127" s="1">
+        <f>IF(O127=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W127" s="1">
+        <f>IF(P127=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A128" s="30" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B128" s="30" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C128" s="30" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D128" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E128" s="32">
+        <v>8</v>
+      </c>
+      <c r="F128" s="32">
+        <v>9</v>
+      </c>
+      <c r="G128" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I128" s="32">
+        <v>4</v>
+      </c>
+      <c r="J128" s="41"/>
+      <c r="K128" s="32">
+        <v>4</v>
+      </c>
+      <c r="L128" s="32">
+        <v>1</v>
+      </c>
+      <c r="M128" s="32">
+        <v>3</v>
+      </c>
+      <c r="N128" s="32">
+        <v>2</v>
+      </c>
+      <c r="O128" s="32">
+        <v>1</v>
+      </c>
+      <c r="P128" s="32">
+        <v>2</v>
+      </c>
+      <c r="R128" s="1">
+        <f>IF(K128=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S128" s="1">
+        <f>IF(L128=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T128" s="1">
+        <f>IF(M128=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U128" s="1">
+        <f>IF(N128=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V128" s="1">
+        <f>IF(O128=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W128" s="1">
+        <f>IF(P128=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="30" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B129" s="30" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D129" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E129" s="32">
+        <v>8</v>
+      </c>
+      <c r="F129" s="32">
+        <v>9</v>
+      </c>
+      <c r="G129" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I129" s="32">
+        <v>5</v>
+      </c>
+      <c r="J129" s="41"/>
+      <c r="K129" s="32">
+        <v>3</v>
+      </c>
+      <c r="L129" s="32">
+        <v>1</v>
+      </c>
+      <c r="M129" s="32">
+        <v>3</v>
+      </c>
+      <c r="N129" s="32">
+        <v>2</v>
+      </c>
+      <c r="O129" s="32">
+        <v>3</v>
+      </c>
+      <c r="P129" s="32">
+        <v>2</v>
+      </c>
+      <c r="R129" s="1">
+        <f>IF(K129=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S129" s="1">
+        <f>IF(L129=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T129" s="1">
+        <f>IF(M129=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U129" s="1">
+        <f>IF(N129=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V129" s="1">
+        <f>IF(O129=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W129" s="1">
+        <f>IF(P129=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="30" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B130" s="30" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C130" s="30" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D130" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E130" s="32">
+        <v>8</v>
+      </c>
+      <c r="F130" s="32">
+        <v>9</v>
+      </c>
+      <c r="G130" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I130" s="32">
+        <v>2</v>
+      </c>
+      <c r="J130" s="41"/>
+      <c r="K130" s="32">
+        <v>2</v>
+      </c>
+      <c r="L130" s="32">
+        <v>3</v>
+      </c>
+      <c r="M130" s="32">
+        <v>3</v>
+      </c>
+      <c r="N130" s="32">
+        <v>2</v>
+      </c>
+      <c r="O130" s="32">
+        <v>1</v>
+      </c>
+      <c r="P130" s="32">
+        <v>3</v>
+      </c>
+      <c r="R130" s="1">
+        <f>IF(K130=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S130" s="1">
+        <f>IF(L130=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T130" s="1">
+        <f>IF(M130=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U130" s="1">
+        <f>IF(N130=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V130" s="1">
+        <f>IF(O130=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W130" s="1">
+        <f>IF(P130=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="30" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B131" s="30" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C131" s="30" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D131" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E131" s="32">
+        <v>8</v>
+      </c>
+      <c r="F131" s="32">
+        <v>9</v>
+      </c>
+      <c r="G131" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I131" s="32">
+        <v>1</v>
+      </c>
+      <c r="J131" s="41"/>
+      <c r="K131" s="32">
+        <v>2</v>
+      </c>
+      <c r="L131" s="32">
+        <v>4</v>
+      </c>
+      <c r="M131" s="32">
+        <v>2</v>
+      </c>
+      <c r="N131" s="32">
+        <v>1</v>
+      </c>
+      <c r="O131" s="32">
+        <v>3</v>
+      </c>
+      <c r="P131" s="32">
+        <v>2</v>
+      </c>
+      <c r="R131" s="1">
+        <f>IF(K131=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S131" s="1">
+        <f>IF(L131=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T131" s="1">
+        <f>IF(M131=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U131" s="1">
+        <f>IF(N131=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V131" s="1">
+        <f>IF(O131=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W131" s="1">
+        <f>IF(P131=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="30" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B132" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C132" s="30" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D132" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E132" s="32">
+        <v>8</v>
+      </c>
+      <c r="F132" s="32">
+        <v>9</v>
+      </c>
+      <c r="G132" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I132" s="32">
+        <v>2</v>
+      </c>
+      <c r="J132" s="41"/>
+      <c r="K132" s="32">
+        <v>2</v>
+      </c>
+      <c r="L132" s="32">
+        <v>2</v>
+      </c>
+      <c r="M132" s="32">
+        <v>1</v>
+      </c>
+      <c r="N132" s="32">
+        <v>2</v>
+      </c>
+      <c r="O132" s="32">
+        <v>3</v>
+      </c>
+      <c r="P132" s="32">
+        <v>2</v>
+      </c>
+      <c r="R132" s="1">
+        <f>IF(K132=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S132" s="1">
+        <f>IF(L132=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T132" s="1">
+        <f>IF(M132=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U132" s="1">
+        <f>IF(N132=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V132" s="1">
+        <f>IF(O132=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W132" s="1">
+        <f>IF(P132=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A133" s="30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B133" s="30" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C133" s="30" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D133" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E133" s="32">
+        <v>8</v>
+      </c>
+      <c r="F133" s="32">
+        <v>9</v>
+      </c>
+      <c r="G133" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I133" s="32">
+        <v>2</v>
+      </c>
+      <c r="J133" s="41"/>
+      <c r="K133" s="32">
+        <v>2</v>
+      </c>
+      <c r="L133" s="32">
+        <v>1</v>
+      </c>
+      <c r="M133" s="32">
+        <v>3</v>
+      </c>
+      <c r="N133" s="32">
+        <v>4</v>
+      </c>
+      <c r="O133" s="32">
+        <v>1</v>
+      </c>
+      <c r="P133" s="32">
+        <v>3</v>
+      </c>
+      <c r="R133" s="1">
+        <f>IF(K133=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S133" s="1">
+        <f>IF(L133=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T133" s="1">
+        <f>IF(M133=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U133" s="1">
+        <f>IF(N133=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V133" s="1">
+        <f>IF(O133=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W133" s="1">
+        <f>IF(P133=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="30" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B134" s="30" t="s">
+        <v>981</v>
+      </c>
+      <c r="C134" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D134" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E134" s="32">
+        <v>8</v>
+      </c>
+      <c r="F134" s="32">
+        <v>9</v>
+      </c>
+      <c r="G134" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H134" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I134" s="32">
+        <v>3</v>
+      </c>
+      <c r="J134" s="41"/>
+      <c r="K134" s="32">
+        <v>3</v>
+      </c>
+      <c r="L134" s="32">
+        <v>4</v>
+      </c>
+      <c r="M134" s="32">
+        <v>3</v>
+      </c>
+      <c r="N134" s="32">
+        <v>2</v>
+      </c>
+      <c r="O134" s="32">
+        <v>4</v>
+      </c>
+      <c r="P134" s="32">
+        <v>1</v>
+      </c>
+      <c r="R134" s="1">
+        <f>IF(K134=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S134" s="1">
+        <f>IF(L134=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T134" s="1">
+        <f>IF(M134=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U134" s="1">
+        <f>IF(N134=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V134" s="1">
+        <f>IF(O134=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W134" s="1">
+        <f>IF(P134=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A135" s="30" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B135" s="30" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C135" s="30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D135" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E135" s="32">
+        <v>8</v>
+      </c>
+      <c r="F135" s="32">
+        <v>9</v>
+      </c>
+      <c r="G135" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H135" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I135" s="32">
+        <v>2</v>
+      </c>
+      <c r="J135" s="41"/>
+      <c r="K135" s="32">
+        <v>1</v>
+      </c>
+      <c r="L135" s="32">
+        <v>2</v>
+      </c>
+      <c r="M135" s="32">
+        <v>3</v>
+      </c>
+      <c r="N135" s="32">
+        <v>1</v>
+      </c>
+      <c r="O135" s="32">
+        <v>4</v>
+      </c>
+      <c r="P135" s="32">
+        <v>2</v>
+      </c>
+      <c r="R135" s="1">
+        <f>IF(K135=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S135" s="1">
+        <f>IF(L135=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T135" s="1">
+        <f>IF(M135=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U135" s="1">
+        <f>IF(N135=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V135" s="1">
+        <f>IF(O135=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W135" s="1">
+        <f>IF(P135=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A136" s="30" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B136" s="30" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C136" s="30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D136" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E136" s="32">
+        <v>8</v>
+      </c>
+      <c r="F136" s="32">
+        <v>9</v>
+      </c>
+      <c r="G136" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H136" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I136" s="32">
+        <v>2</v>
+      </c>
+      <c r="J136" s="41"/>
+      <c r="K136" s="32">
+        <v>2</v>
+      </c>
+      <c r="L136" s="32">
+        <v>4</v>
+      </c>
+      <c r="M136" s="32">
+        <v>3</v>
+      </c>
+      <c r="N136" s="32">
+        <v>2</v>
+      </c>
+      <c r="O136" s="32">
+        <v>1</v>
+      </c>
+      <c r="P136" s="32">
+        <v>3</v>
+      </c>
+      <c r="R136" s="1">
+        <f>IF(K136=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S136" s="1">
+        <f>IF(L136=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T136" s="1">
+        <f>IF(M136=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U136" s="1">
+        <f>IF(N136=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V136" s="1">
+        <f>IF(O136=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W136" s="1">
+        <f>IF(P136=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A137" s="30" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B137" s="30" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C137" s="30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D137" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E137" s="32">
+        <v>8</v>
+      </c>
+      <c r="F137" s="32">
+        <v>9</v>
+      </c>
+      <c r="G137" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H137" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I137" s="32">
+        <v>0</v>
+      </c>
+      <c r="J137" s="41"/>
+      <c r="R137" s="1">
+        <f>IF(K137=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S137" s="1">
+        <f>IF(L137=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T137" s="1">
+        <f>IF(M137=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U137" s="1">
+        <f>IF(N137=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V137" s="1">
+        <f>IF(O137=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W137" s="1">
+        <f>IF(P137=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B138" s="30" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C138" s="30" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D138" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E138" s="32">
+        <v>8</v>
+      </c>
+      <c r="F138" s="32">
+        <v>9</v>
+      </c>
+      <c r="G138" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H138" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I138" s="32">
+        <v>0</v>
+      </c>
+      <c r="J138" s="41"/>
+      <c r="R138" s="1">
+        <f>IF(K138=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S138" s="1">
+        <f>IF(L138=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T138" s="1">
+        <f>IF(M138=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U138" s="1">
+        <f>IF(N138=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V138" s="1">
+        <f>IF(O138=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W138" s="1">
+        <f>IF(P138=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="30" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B139" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C139" s="30" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D139" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E139" s="32">
+        <v>8</v>
+      </c>
+      <c r="F139" s="32">
+        <v>9</v>
+      </c>
+      <c r="G139" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H139" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I139" s="32">
+        <v>2</v>
+      </c>
+      <c r="J139" s="41"/>
+      <c r="K139" s="32">
+        <v>1</v>
+      </c>
+      <c r="L139" s="32">
+        <v>4</v>
+      </c>
+      <c r="M139" s="32">
+        <v>3</v>
+      </c>
+      <c r="N139" s="32">
+        <v>2</v>
+      </c>
+      <c r="O139" s="32">
+        <v>4</v>
+      </c>
+      <c r="P139" s="32">
+        <v>1</v>
+      </c>
+      <c r="R139" s="1">
+        <f>IF(K139=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S139" s="1">
+        <f>IF(L139=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T139" s="1">
+        <f>IF(M139=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U139" s="1">
+        <f>IF(N139=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V139" s="1">
+        <f>IF(O139=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W139" s="1">
+        <f>IF(P139=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A140" s="30" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B140" s="30" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C140" s="30" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D140" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E140" s="32">
+        <v>8</v>
+      </c>
+      <c r="F140" s="32">
+        <v>9</v>
+      </c>
+      <c r="G140" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H140" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I140" s="32">
+        <v>4</v>
+      </c>
+      <c r="J140" s="41"/>
+      <c r="K140" s="32">
+        <v>4</v>
+      </c>
+      <c r="L140" s="32">
+        <v>1</v>
+      </c>
+      <c r="M140" s="32">
+        <v>3</v>
+      </c>
+      <c r="N140" s="32">
+        <v>2</v>
+      </c>
+      <c r="O140" s="32">
+        <v>3</v>
+      </c>
+      <c r="P140" s="32">
+        <v>2</v>
+      </c>
+      <c r="R140" s="1">
+        <f>IF(K140=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S140" s="1">
+        <f>IF(L140=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T140" s="1">
+        <f>IF(M140=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U140" s="1">
+        <f>IF(N140=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V140" s="1">
+        <f>IF(O140=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W140" s="1">
+        <f>IF(P140=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I141" s="39">
         <f>AVERAGE(Scores[MC])</f>
-        <v>3.7563025210084033</v>
-      </c>
-      <c r="Y121" s="40"/>
+        <v>3.5323741007194243</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
-  <conditionalFormatting sqref="K2:P120">
-    <cfRule type="expression" dxfId="24" priority="1">
+  <conditionalFormatting sqref="K2:P140">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>R2=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D120" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D140" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Bermejo,Dushin,Klein / Cooper,Kovelsky"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="J2:J120" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="J2:J140" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>AND(ISNUMBER(J2),(NOT(OR(NOT(ISERROR(DATEVALUE(J2))), AND(ISNUMBER(J2), LEFT(CELL("format", J2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -13246,7 +14994,7 @@
       </c>
       <c r="P2" s="18">
         <f t="array" ref="P2">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A2,Scores[#Headers],0)))</f>
-        <v>0.57983193277310929</v>
+        <v>0.52517985611510787</v>
       </c>
       <c r="Q2" s="16"/>
     </row>
@@ -13298,7 +15046,7 @@
       </c>
       <c r="P3" s="18">
         <f t="array" ref="P3">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A3,Scores[#Headers],0)))</f>
-        <v>0.53781512605042014</v>
+        <v>0.49640287769784175</v>
       </c>
       <c r="Q3" s="16"/>
     </row>
@@ -13350,7 +15098,7 @@
       </c>
       <c r="P4" s="18">
         <f t="array" ref="P4">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A4,Scores[#Headers],0)))</f>
-        <v>0.81512605042016806</v>
+        <v>0.79856115107913672</v>
       </c>
       <c r="Q4" s="16"/>
     </row>
@@ -13402,7 +15150,7 @@
       </c>
       <c r="P5" s="18">
         <f t="array" ref="P5">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A5,Scores[#Headers],0)))</f>
-        <v>0.75630252100840334</v>
+        <v>0.73381294964028776</v>
       </c>
       <c r="Q5" s="16"/>
     </row>
@@ -13454,7 +15202,7 @@
       </c>
       <c r="P6" s="18">
         <f t="array" ref="P6">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A6,Scores[#Headers],0)))</f>
-        <v>0.35294117647058826</v>
+        <v>0.34532374100719426</v>
       </c>
       <c r="Q6" s="16"/>
     </row>
@@ -13506,7 +15254,7 @@
       </c>
       <c r="P7" s="18">
         <f t="array" ref="P7">AVERAGE(INDEX(Scores[],0,MATCH("Q"&amp;$A7,Scores[#Headers],0)))</f>
-        <v>0.7142857142857143</v>
+        <v>0.67625899280575541</v>
       </c>
       <c r="Q7" s="16"/>
     </row>
@@ -13543,7 +15291,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3052F8A2-9498-D34B-9544-2464D3270C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1809095C-331E-FA4C-B427-575B19AFBA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="889">
   <si>
     <t>Model</t>
   </si>
@@ -2289,6 +2289,423 @@
   </si>
   <si>
     <t>Grade</t>
+  </si>
+  <si>
+    <t>BCE87468</t>
+  </si>
+  <si>
+    <t>PYD85821</t>
+  </si>
+  <si>
+    <t>SPL19463</t>
+  </si>
+  <si>
+    <t>TFT96599</t>
+  </si>
+  <si>
+    <t>AEA52429</t>
+  </si>
+  <si>
+    <t>ONK63527</t>
+  </si>
+  <si>
+    <t>MPA54097</t>
+  </si>
+  <si>
+    <t>PUZ92475</t>
+  </si>
+  <si>
+    <t>BFA12371</t>
+  </si>
+  <si>
+    <t>BWX22237</t>
+  </si>
+  <si>
+    <t>MRQ47886</t>
+  </si>
+  <si>
+    <t>DTY88033</t>
+  </si>
+  <si>
+    <t>EBH29779</t>
+  </si>
+  <si>
+    <t>BJO21212</t>
+  </si>
+  <si>
+    <t>JLX21297</t>
+  </si>
+  <si>
+    <t>VHW73020</t>
+  </si>
+  <si>
+    <t>TXB14318</t>
+  </si>
+  <si>
+    <t>ZMS92794</t>
+  </si>
+  <si>
+    <t>RQY44411</t>
+  </si>
+  <si>
+    <t>OTM13405</t>
+  </si>
+  <si>
+    <t>HOT90521</t>
+  </si>
+  <si>
+    <t>RTH79332</t>
+  </si>
+  <si>
+    <t>XXD85883</t>
+  </si>
+  <si>
+    <t>LFK75199</t>
+  </si>
+  <si>
+    <t>AZH29276</t>
+  </si>
+  <si>
+    <t>JSN75135</t>
+  </si>
+  <si>
+    <t>MDS28198</t>
+  </si>
+  <si>
+    <t>BBW35809</t>
+  </si>
+  <si>
+    <t>QJC38094</t>
+  </si>
+  <si>
+    <t>EXL78479</t>
+  </si>
+  <si>
+    <t>QMV74206</t>
+  </si>
+  <si>
+    <t>CIT87934</t>
+  </si>
+  <si>
+    <t>CLQ75171</t>
+  </si>
+  <si>
+    <t>FXD68642</t>
+  </si>
+  <si>
+    <t>AEU59958</t>
+  </si>
+  <si>
+    <t>JXA20997</t>
+  </si>
+  <si>
+    <t>LOB72239</t>
+  </si>
+  <si>
+    <t>MND12981</t>
+  </si>
+  <si>
+    <t>DTP58821</t>
+  </si>
+  <si>
+    <t>NFR65117</t>
+  </si>
+  <si>
+    <t>TOB31201</t>
+  </si>
+  <si>
+    <t>OTB29052</t>
+  </si>
+  <si>
+    <t>SBP71888</t>
+  </si>
+  <si>
+    <t>ZJU22624</t>
+  </si>
+  <si>
+    <t>DWK39559</t>
+  </si>
+  <si>
+    <t>TAJ26766</t>
+  </si>
+  <si>
+    <t>NBR19673</t>
+  </si>
+  <si>
+    <t>FYI62103</t>
+  </si>
+  <si>
+    <t>SES69634</t>
+  </si>
+  <si>
+    <t>DHC45581</t>
+  </si>
+  <si>
+    <t>QAI80102</t>
+  </si>
+  <si>
+    <t>VBX69991</t>
+  </si>
+  <si>
+    <t>VEI56568</t>
+  </si>
+  <si>
+    <t>DLA71738</t>
+  </si>
+  <si>
+    <t>UOK67779</t>
+  </si>
+  <si>
+    <t>SSH34700</t>
+  </si>
+  <si>
+    <t>FGQ30121</t>
+  </si>
+  <si>
+    <t>YIN10536</t>
+  </si>
+  <si>
+    <t>GIS59561</t>
+  </si>
+  <si>
+    <t>YCB68290</t>
+  </si>
+  <si>
+    <t>FZG75254</t>
+  </si>
+  <si>
+    <t>LFA38642</t>
+  </si>
+  <si>
+    <t>XJB61404</t>
+  </si>
+  <si>
+    <t>UYT20669</t>
+  </si>
+  <si>
+    <t>CRI76501</t>
+  </si>
+  <si>
+    <t>EAH31443</t>
+  </si>
+  <si>
+    <t>OYR21509</t>
+  </si>
+  <si>
+    <t>NBI81346</t>
+  </si>
+  <si>
+    <t>NPQ11133</t>
+  </si>
+  <si>
+    <t>KQW90435</t>
+  </si>
+  <si>
+    <t>VGQ54749</t>
+  </si>
+  <si>
+    <t>KNB73713</t>
+  </si>
+  <si>
+    <t>VJX26106</t>
+  </si>
+  <si>
+    <t>NPR55657</t>
+  </si>
+  <si>
+    <t>ATP23397</t>
+  </si>
+  <si>
+    <t>DPT96866</t>
+  </si>
+  <si>
+    <t>VDA73806</t>
+  </si>
+  <si>
+    <t>SBA28155</t>
+  </si>
+  <si>
+    <t>UCD49129</t>
+  </si>
+  <si>
+    <t>CLK39974</t>
+  </si>
+  <si>
+    <t>ZPI51571</t>
+  </si>
+  <si>
+    <t>MRC57489</t>
+  </si>
+  <si>
+    <t>JTO21324</t>
+  </si>
+  <si>
+    <t>HXE84177</t>
+  </si>
+  <si>
+    <t>OCS40016</t>
+  </si>
+  <si>
+    <t>WVH29287</t>
+  </si>
+  <si>
+    <t>AGB36654</t>
+  </si>
+  <si>
+    <t>SNV77028</t>
+  </si>
+  <si>
+    <t>XMZ55136</t>
+  </si>
+  <si>
+    <t>GKB67820</t>
+  </si>
+  <si>
+    <t>BBY14959</t>
+  </si>
+  <si>
+    <t>DWK74474</t>
+  </si>
+  <si>
+    <t>MZB79205</t>
+  </si>
+  <si>
+    <t>XCN58637</t>
+  </si>
+  <si>
+    <t>PLD66414</t>
+  </si>
+  <si>
+    <t>FIM25375</t>
+  </si>
+  <si>
+    <t>OWI55457</t>
+  </si>
+  <si>
+    <t>JGN46222</t>
+  </si>
+  <si>
+    <t>KIF34983</t>
+  </si>
+  <si>
+    <t>LYP83564</t>
+  </si>
+  <si>
+    <t>JER71568</t>
+  </si>
+  <si>
+    <t>IHK21700</t>
+  </si>
+  <si>
+    <t>JOE63160</t>
+  </si>
+  <si>
+    <t>WRF62439</t>
+  </si>
+  <si>
+    <t>VHB56911</t>
+  </si>
+  <si>
+    <t>HPM45577</t>
+  </si>
+  <si>
+    <t>TFC63010</t>
+  </si>
+  <si>
+    <t>AVW57108</t>
+  </si>
+  <si>
+    <t>SHL28614</t>
+  </si>
+  <si>
+    <t>TCZ30524</t>
+  </si>
+  <si>
+    <t>MEK28482</t>
+  </si>
+  <si>
+    <t>OYA29056</t>
+  </si>
+  <si>
+    <t>TMI31401</t>
+  </si>
+  <si>
+    <t>MBT39196</t>
+  </si>
+  <si>
+    <t>ZOY64027</t>
+  </si>
+  <si>
+    <t>BXA18368</t>
+  </si>
+  <si>
+    <t>WMW86220</t>
+  </si>
+  <si>
+    <t>AVO62088</t>
+  </si>
+  <si>
+    <t>ASV84493</t>
+  </si>
+  <si>
+    <t>MBL38474</t>
+  </si>
+  <si>
+    <t>JRG12665</t>
+  </si>
+  <si>
+    <t>ISA40439</t>
+  </si>
+  <si>
+    <t>FDC41321</t>
+  </si>
+  <si>
+    <t>YGY58448</t>
+  </si>
+  <si>
+    <t>FDV70186</t>
+  </si>
+  <si>
+    <t>NUB89163</t>
+  </si>
+  <si>
+    <t>QQA90014</t>
+  </si>
+  <si>
+    <t>ZJL27840</t>
+  </si>
+  <si>
+    <t>MSR33082</t>
+  </si>
+  <si>
+    <t>BUE64832</t>
+  </si>
+  <si>
+    <t>VLC23912</t>
+  </si>
+  <si>
+    <t>GVR79043</t>
+  </si>
+  <si>
+    <t>WWL74295</t>
+  </si>
+  <si>
+    <t>WZE53686</t>
+  </si>
+  <si>
+    <t>XXA89248</t>
+  </si>
+  <si>
+    <t>SYE52204</t>
+  </si>
+  <si>
+    <t>AUG82979</t>
+  </si>
+  <si>
+    <t>VIT24690</t>
+  </si>
+  <si>
+    <t>OYI76487</t>
   </si>
 </sst>
 </file>
@@ -2837,9 +3254,6 @@
   </cellStyles>
   <dxfs count="32">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -2859,38 +3273,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE8EEF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="hair">
-          <color rgb="FFD8E0E8"/>
-        </right>
-      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3032,6 +3414,41 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="hair">
+          <color rgb="FFD8E0E8"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8EEF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFF5F8FB"/>
@@ -3133,10 +3550,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C04EAAE0-8575-4C4D-8F7C-680B0F8FE844}" name="Table4" displayName="Table4" ref="A1:U141" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C04EAAE0-8575-4C4D-8F7C-680B0F8FE844}" name="Table4" displayName="Table4" ref="A1:U141" totalsRowShown="0" headerRowDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="A1:U141" xr:uid="{C04EAAE0-8575-4C4D-8F7C-680B0F8FE844}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C8800E54-CA52-2044-A16A-FF3249E700E8}" name="Key" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C8800E54-CA52-2044-A16A-FF3249E700E8}" name="Key" dataDxfId="25"/>
     <tableColumn id="5" xr3:uid="{1508E423-CBEF-6F4B-9DCF-7D205ACAAA4A}" name="Class"/>
     <tableColumn id="6" xr3:uid="{AACC7F38-4163-B84F-88F9-448EEF83552D}" name="Period"/>
     <tableColumn id="7" xr3:uid="{1050C21B-C0F8-E841-8048-E0D87CBF2D06}" name="Grade"/>
@@ -3163,25 +3580,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3191,7 +3608,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3202,7 +3619,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3214,7 +3631,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3448,7 +3865,7 @@
   <dimension ref="A1:W141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="21" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" style="19" customWidth="1"/>
     <col min="3" max="4" width="10.1640625" style="20" customWidth="1"/>
     <col min="5" max="5" width="10.1640625" style="23" customWidth="1"/>
@@ -3527,8 +3944,8 @@
       </c>
     </row>
     <row r="2" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1">
-        <v>1</v>
+      <c r="A2" s="1" t="s">
+        <v>750</v>
       </c>
       <c r="B2" s="30" t="s">
         <v>28</v>
@@ -3598,8 +4015,8 @@
       <c r="W2" s="25"/>
     </row>
     <row r="3" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
-        <v>2</v>
+      <c r="A3" s="1" t="s">
+        <v>751</v>
       </c>
       <c r="B3" s="36" t="s">
         <v>28</v>
@@ -3669,8 +4086,8 @@
       <c r="W3" s="25"/>
     </row>
     <row r="4" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1">
-        <v>3</v>
+      <c r="A4" s="1" t="s">
+        <v>752</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>28</v>
@@ -3740,8 +4157,8 @@
       <c r="W4" s="25"/>
     </row>
     <row r="5" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>4</v>
+      <c r="A5" s="1" t="s">
+        <v>753</v>
       </c>
       <c r="B5" s="36" t="s">
         <v>28</v>
@@ -3811,8 +4228,8 @@
       <c r="W5" s="25"/>
     </row>
     <row r="6" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
-        <v>5</v>
+      <c r="A6" s="1" t="s">
+        <v>754</v>
       </c>
       <c r="B6" s="42" t="s">
         <v>28</v>
@@ -3882,8 +4299,8 @@
       <c r="W6" s="25"/>
     </row>
     <row r="7" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
-        <v>6</v>
+      <c r="A7" s="1" t="s">
+        <v>755</v>
       </c>
       <c r="B7" s="36" t="s">
         <v>28</v>
@@ -3953,8 +4370,8 @@
       <c r="W7" s="25"/>
     </row>
     <row r="8" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
-        <v>7</v>
+      <c r="A8" s="1" t="s">
+        <v>756</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>28</v>
@@ -4024,8 +4441,8 @@
       <c r="W8" s="25"/>
     </row>
     <row r="9" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
-        <v>8</v>
+      <c r="A9" s="1" t="s">
+        <v>757</v>
       </c>
       <c r="B9" s="36" t="s">
         <v>28</v>
@@ -4095,8 +4512,8 @@
       <c r="W9" s="25"/>
     </row>
     <row r="10" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
-        <v>9</v>
+      <c r="A10" s="1" t="s">
+        <v>758</v>
       </c>
       <c r="B10" s="42" t="s">
         <v>28</v>
@@ -4166,8 +4583,8 @@
       <c r="W10" s="25"/>
     </row>
     <row r="11" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
-        <v>10</v>
+      <c r="A11" s="1" t="s">
+        <v>759</v>
       </c>
       <c r="B11" s="36" t="s">
         <v>28</v>
@@ -4235,8 +4652,8 @@
       <c r="W11" s="25"/>
     </row>
     <row r="12" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
-        <v>11</v>
+      <c r="A12" s="1" t="s">
+        <v>760</v>
       </c>
       <c r="B12" s="42" t="s">
         <v>28</v>
@@ -4306,8 +4723,8 @@
       <c r="W12" s="25"/>
     </row>
     <row r="13" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
-        <v>12</v>
+      <c r="A13" s="1" t="s">
+        <v>761</v>
       </c>
       <c r="B13" s="36" t="s">
         <v>28</v>
@@ -4377,8 +4794,8 @@
       <c r="W13" s="25"/>
     </row>
     <row r="14" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="1">
-        <v>13</v>
+      <c r="A14" s="1" t="s">
+        <v>762</v>
       </c>
       <c r="B14" s="42" t="s">
         <v>28</v>
@@ -4448,8 +4865,8 @@
       <c r="W14" s="25"/>
     </row>
     <row r="15" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
-        <v>14</v>
+      <c r="A15" s="1" t="s">
+        <v>763</v>
       </c>
       <c r="B15" s="36" t="s">
         <v>28</v>
@@ -4519,8 +4936,8 @@
       <c r="W15" s="25"/>
     </row>
     <row r="16" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
-        <v>15</v>
+      <c r="A16" s="1" t="s">
+        <v>764</v>
       </c>
       <c r="B16" s="42" t="s">
         <v>28</v>
@@ -4590,8 +5007,8 @@
       <c r="W16" s="25"/>
     </row>
     <row r="17" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
-        <v>16</v>
+      <c r="A17" s="1" t="s">
+        <v>765</v>
       </c>
       <c r="B17" s="36" t="s">
         <v>28</v>
@@ -4661,8 +5078,8 @@
       <c r="W17" s="25"/>
     </row>
     <row r="18" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="1">
-        <v>17</v>
+      <c r="A18" s="1" t="s">
+        <v>766</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>28</v>
@@ -4732,8 +5149,8 @@
       <c r="W18" s="25"/>
     </row>
     <row r="19" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="1">
-        <v>18</v>
+      <c r="A19" s="1" t="s">
+        <v>767</v>
       </c>
       <c r="B19" s="36" t="s">
         <v>28</v>
@@ -4803,8 +5220,8 @@
       <c r="W19" s="25"/>
     </row>
     <row r="20" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1">
-        <v>19</v>
+      <c r="A20" s="1" t="s">
+        <v>768</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>28</v>
@@ -4860,8 +5277,8 @@
       <c r="W20" s="25"/>
     </row>
     <row r="21" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="1">
-        <v>20</v>
+      <c r="A21" s="1" t="s">
+        <v>769</v>
       </c>
       <c r="B21" s="36" t="s">
         <v>28</v>
@@ -4927,8 +5344,8 @@
       <c r="W21" s="25"/>
     </row>
     <row r="22" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="1">
-        <v>21</v>
+      <c r="A22" s="1" t="s">
+        <v>770</v>
       </c>
       <c r="B22" s="42" t="s">
         <v>28</v>
@@ -4998,8 +5415,8 @@
       <c r="W22" s="25"/>
     </row>
     <row r="23" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
-        <v>22</v>
+      <c r="A23" s="1" t="s">
+        <v>771</v>
       </c>
       <c r="B23" s="36" t="s">
         <v>28</v>
@@ -5069,8 +5486,8 @@
       <c r="W23" s="25"/>
     </row>
     <row r="24" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="1">
-        <v>23</v>
+      <c r="A24" s="1" t="s">
+        <v>772</v>
       </c>
       <c r="B24" s="42" t="s">
         <v>28</v>
@@ -5140,8 +5557,8 @@
       <c r="W24" s="25"/>
     </row>
     <row r="25" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="1">
-        <v>24</v>
+      <c r="A25" s="1" t="s">
+        <v>773</v>
       </c>
       <c r="B25" s="36" t="s">
         <v>28</v>
@@ -5211,8 +5628,8 @@
       <c r="W25" s="25"/>
     </row>
     <row r="26" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="1">
-        <v>25</v>
+      <c r="A26" s="1" t="s">
+        <v>774</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>28</v>
@@ -5282,8 +5699,8 @@
       <c r="W26" s="25"/>
     </row>
     <row r="27" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1">
-        <v>26</v>
+      <c r="A27" s="1" t="s">
+        <v>775</v>
       </c>
       <c r="B27" s="36" t="s">
         <v>28</v>
@@ -5353,8 +5770,8 @@
       <c r="W27" s="25"/>
     </row>
     <row r="28" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="1">
-        <v>27</v>
+      <c r="A28" s="1" t="s">
+        <v>776</v>
       </c>
       <c r="B28" s="42" t="s">
         <v>28</v>
@@ -5424,8 +5841,8 @@
       <c r="W28" s="25"/>
     </row>
     <row r="29" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="1">
-        <v>28</v>
+      <c r="A29" s="1" t="s">
+        <v>777</v>
       </c>
       <c r="B29" s="36" t="s">
         <v>42</v>
@@ -5495,8 +5912,8 @@
       <c r="W29" s="25"/>
     </row>
     <row r="30" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="1">
-        <v>29</v>
+      <c r="A30" s="1" t="s">
+        <v>778</v>
       </c>
       <c r="B30" s="42" t="s">
         <v>42</v>
@@ -5564,8 +5981,8 @@
       <c r="W30" s="25"/>
     </row>
     <row r="31" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="1">
-        <v>30</v>
+      <c r="A31" s="1" t="s">
+        <v>779</v>
       </c>
       <c r="B31" s="36" t="s">
         <v>42</v>
@@ -5635,8 +6052,8 @@
       <c r="W31" s="25"/>
     </row>
     <row r="32" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="1">
-        <v>31</v>
+      <c r="A32" s="1" t="s">
+        <v>780</v>
       </c>
       <c r="B32" s="42" t="s">
         <v>42</v>
@@ -5704,8 +6121,8 @@
       <c r="W32" s="25"/>
     </row>
     <row r="33" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="1">
-        <v>32</v>
+      <c r="A33" s="1" t="s">
+        <v>781</v>
       </c>
       <c r="B33" s="36" t="s">
         <v>42</v>
@@ -5775,8 +6192,8 @@
       <c r="W33" s="25"/>
     </row>
     <row r="34" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="1">
-        <v>33</v>
+      <c r="A34" s="1" t="s">
+        <v>782</v>
       </c>
       <c r="B34" s="42" t="s">
         <v>42</v>
@@ -5846,8 +6263,8 @@
       <c r="W34" s="25"/>
     </row>
     <row r="35" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="1">
-        <v>34</v>
+      <c r="A35" s="1" t="s">
+        <v>783</v>
       </c>
       <c r="B35" s="36" t="s">
         <v>42</v>
@@ -5917,8 +6334,8 @@
       <c r="W35" s="25"/>
     </row>
     <row r="36" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="1">
-        <v>35</v>
+      <c r="A36" s="1" t="s">
+        <v>784</v>
       </c>
       <c r="B36" s="42" t="s">
         <v>42</v>
@@ -5988,8 +6405,8 @@
       <c r="W36" s="25"/>
     </row>
     <row r="37" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="1">
-        <v>36</v>
+      <c r="A37" s="1" t="s">
+        <v>785</v>
       </c>
       <c r="B37" s="36" t="s">
         <v>42</v>
@@ -6057,8 +6474,8 @@
       <c r="W37" s="25"/>
     </row>
     <row r="38" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="1">
-        <v>37</v>
+      <c r="A38" s="1" t="s">
+        <v>786</v>
       </c>
       <c r="B38" s="42" t="s">
         <v>42</v>
@@ -6128,8 +6545,8 @@
       <c r="W38" s="25"/>
     </row>
     <row r="39" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="1">
-        <v>38</v>
+      <c r="A39" s="1" t="s">
+        <v>787</v>
       </c>
       <c r="B39" s="36" t="s">
         <v>42</v>
@@ -6199,8 +6616,8 @@
       <c r="W39" s="25"/>
     </row>
     <row r="40" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="1">
-        <v>39</v>
+      <c r="A40" s="1" t="s">
+        <v>788</v>
       </c>
       <c r="B40" s="42" t="s">
         <v>42</v>
@@ -6270,8 +6687,8 @@
       <c r="W40" s="25"/>
     </row>
     <row r="41" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="1">
-        <v>40</v>
+      <c r="A41" s="1" t="s">
+        <v>789</v>
       </c>
       <c r="B41" s="36" t="s">
         <v>42</v>
@@ -6341,8 +6758,8 @@
       <c r="W41" s="25"/>
     </row>
     <row r="42" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="1">
-        <v>41</v>
+      <c r="A42" s="1" t="s">
+        <v>790</v>
       </c>
       <c r="B42" s="42" t="s">
         <v>42</v>
@@ -6412,8 +6829,8 @@
       <c r="W42" s="25"/>
     </row>
     <row r="43" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="1">
-        <v>42</v>
+      <c r="A43" s="1" t="s">
+        <v>791</v>
       </c>
       <c r="B43" s="36" t="s">
         <v>42</v>
@@ -6483,8 +6900,8 @@
       <c r="W43" s="25"/>
     </row>
     <row r="44" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="1">
-        <v>43</v>
+      <c r="A44" s="1" t="s">
+        <v>792</v>
       </c>
       <c r="B44" s="42" t="s">
         <v>42</v>
@@ -6554,8 +6971,8 @@
       <c r="W44" s="25"/>
     </row>
     <row r="45" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="1">
-        <v>44</v>
+      <c r="A45" s="1" t="s">
+        <v>793</v>
       </c>
       <c r="B45" s="36" t="s">
         <v>42</v>
@@ -6615,8 +7032,8 @@
       <c r="W45" s="25"/>
     </row>
     <row r="46" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="1">
-        <v>45</v>
+      <c r="A46" s="1" t="s">
+        <v>794</v>
       </c>
       <c r="B46" s="42" t="s">
         <v>42</v>
@@ -6686,8 +7103,8 @@
       <c r="W46" s="25"/>
     </row>
     <row r="47" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="1">
-        <v>46</v>
+      <c r="A47" s="1" t="s">
+        <v>795</v>
       </c>
       <c r="B47" s="36" t="s">
         <v>45</v>
@@ -6754,8 +7171,8 @@
       <c r="W47" s="25"/>
     </row>
     <row r="48" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="1">
-        <v>47</v>
+      <c r="A48" s="1" t="s">
+        <v>796</v>
       </c>
       <c r="B48" s="42" t="s">
         <v>45</v>
@@ -6818,8 +7235,8 @@
       <c r="W48" s="25"/>
     </row>
     <row r="49" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="1">
-        <v>48</v>
+      <c r="A49" s="1" t="s">
+        <v>797</v>
       </c>
       <c r="B49" s="36" t="s">
         <v>45</v>
@@ -6886,8 +7303,8 @@
       <c r="W49" s="25"/>
     </row>
     <row r="50" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="1">
-        <v>49</v>
+      <c r="A50" s="1" t="s">
+        <v>798</v>
       </c>
       <c r="B50" s="42" t="s">
         <v>45</v>
@@ -6954,8 +7371,8 @@
       <c r="W50" s="17"/>
     </row>
     <row r="51" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="1">
-        <v>50</v>
+      <c r="A51" s="1" t="s">
+        <v>799</v>
       </c>
       <c r="B51" s="36" t="s">
         <v>45</v>
@@ -7022,8 +7439,8 @@
       <c r="W51" s="25"/>
     </row>
     <row r="52" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="1">
-        <v>51</v>
+      <c r="A52" s="1" t="s">
+        <v>800</v>
       </c>
       <c r="B52" s="42" t="s">
         <v>45</v>
@@ -7092,8 +7509,8 @@
       <c r="W52" s="25"/>
     </row>
     <row r="53" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="1">
-        <v>52</v>
+      <c r="A53" s="1" t="s">
+        <v>801</v>
       </c>
       <c r="B53" s="36" t="s">
         <v>45</v>
@@ -7162,8 +7579,8 @@
       <c r="W53" s="25"/>
     </row>
     <row r="54" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="1">
-        <v>53</v>
+      <c r="A54" s="1" t="s">
+        <v>802</v>
       </c>
       <c r="B54" s="42" t="s">
         <v>45</v>
@@ -7230,8 +7647,8 @@
       <c r="W54" s="25"/>
     </row>
     <row r="55" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="1">
-        <v>54</v>
+      <c r="A55" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="B55" s="36" t="s">
         <v>45</v>
@@ -7300,8 +7717,8 @@
       <c r="W55" s="25"/>
     </row>
     <row r="56" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="1">
-        <v>55</v>
+      <c r="A56" s="1" t="s">
+        <v>804</v>
       </c>
       <c r="B56" s="42" t="s">
         <v>45</v>
@@ -7368,8 +7785,8 @@
       <c r="W56" s="25"/>
     </row>
     <row r="57" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="1">
-        <v>56</v>
+      <c r="A57" s="1" t="s">
+        <v>805</v>
       </c>
       <c r="B57" s="36" t="s">
         <v>45</v>
@@ -7438,8 +7855,8 @@
       <c r="W57" s="25"/>
     </row>
     <row r="58" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="1">
-        <v>57</v>
+      <c r="A58" s="1" t="s">
+        <v>806</v>
       </c>
       <c r="B58" s="42" t="s">
         <v>45</v>
@@ -7508,8 +7925,8 @@
       <c r="W58" s="25"/>
     </row>
     <row r="59" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="1">
-        <v>58</v>
+      <c r="A59" s="1" t="s">
+        <v>807</v>
       </c>
       <c r="B59" s="36" t="s">
         <v>45</v>
@@ -7578,8 +7995,8 @@
       <c r="W59" s="25"/>
     </row>
     <row r="60" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="1">
-        <v>59</v>
+      <c r="A60" s="1" t="s">
+        <v>808</v>
       </c>
       <c r="B60" s="42" t="s">
         <v>45</v>
@@ -7642,8 +8059,8 @@
       <c r="W60" s="25"/>
     </row>
     <row r="61" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="1">
-        <v>60</v>
+      <c r="A61" s="1" t="s">
+        <v>809</v>
       </c>
       <c r="B61" s="36" t="s">
         <v>45</v>
@@ -7712,8 +8129,8 @@
       <c r="W61" s="25"/>
     </row>
     <row r="62" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="1">
-        <v>61</v>
+      <c r="A62" s="1" t="s">
+        <v>810</v>
       </c>
       <c r="B62" s="42" t="s">
         <v>45</v>
@@ -7780,8 +8197,8 @@
       <c r="W62" s="25"/>
     </row>
     <row r="63" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="1">
-        <v>62</v>
+      <c r="A63" s="1" t="s">
+        <v>811</v>
       </c>
       <c r="B63" s="36" t="s">
         <v>45</v>
@@ -7848,8 +8265,8 @@
       <c r="W63" s="25"/>
     </row>
     <row r="64" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="1">
-        <v>63</v>
+      <c r="A64" s="1" t="s">
+        <v>812</v>
       </c>
       <c r="B64" s="42" t="s">
         <v>45</v>
@@ -7918,8 +8335,8 @@
       <c r="W64" s="25"/>
     </row>
     <row r="65" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="1">
-        <v>64</v>
+      <c r="A65" s="1" t="s">
+        <v>813</v>
       </c>
       <c r="B65" s="36" t="s">
         <v>45</v>
@@ -7986,8 +8403,8 @@
       <c r="W65" s="25"/>
     </row>
     <row r="66" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="1">
-        <v>65</v>
+      <c r="A66" s="1" t="s">
+        <v>814</v>
       </c>
       <c r="B66" s="42" t="s">
         <v>45</v>
@@ -8054,8 +8471,8 @@
       <c r="W66" s="25"/>
     </row>
     <row r="67" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="1">
-        <v>66</v>
+      <c r="A67" s="1" t="s">
+        <v>815</v>
       </c>
       <c r="B67" s="36" t="s">
         <v>45</v>
@@ -8124,8 +8541,8 @@
       <c r="W67" s="25"/>
     </row>
     <row r="68" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="1">
-        <v>67</v>
+      <c r="A68" s="1" t="s">
+        <v>816</v>
       </c>
       <c r="B68" s="42" t="s">
         <v>45</v>
@@ -8194,8 +8611,8 @@
       <c r="W68" s="25"/>
     </row>
     <row r="69" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="1">
-        <v>68</v>
+      <c r="A69" s="1" t="s">
+        <v>817</v>
       </c>
       <c r="B69" s="48" t="s">
         <v>45</v>
@@ -8264,8 +8681,8 @@
       <c r="W69" s="25"/>
     </row>
     <row r="70" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="1">
-        <v>69</v>
+      <c r="A70" s="1" t="s">
+        <v>818</v>
       </c>
       <c r="B70" s="49" t="s">
         <v>45</v>
@@ -8334,8 +8751,8 @@
       <c r="W70" s="25"/>
     </row>
     <row r="71" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="1">
-        <v>70</v>
+      <c r="A71" s="1" t="s">
+        <v>819</v>
       </c>
       <c r="B71" s="48" t="s">
         <v>45</v>
@@ -8404,8 +8821,8 @@
       <c r="W71" s="25"/>
     </row>
     <row r="72" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="1">
-        <v>71</v>
+      <c r="A72" s="1" t="s">
+        <v>820</v>
       </c>
       <c r="B72" s="49" t="s">
         <v>45</v>
@@ -8470,8 +8887,8 @@
       <c r="W72" s="25"/>
     </row>
     <row r="73" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="1">
-        <v>72</v>
+      <c r="A73" s="1" t="s">
+        <v>821</v>
       </c>
       <c r="B73" s="48" t="s">
         <v>45</v>
@@ -8540,8 +8957,8 @@
       <c r="W73" s="25"/>
     </row>
     <row r="74" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="1">
-        <v>73</v>
+      <c r="A74" s="1" t="s">
+        <v>822</v>
       </c>
       <c r="B74" s="49" t="s">
         <v>45</v>
@@ -8610,8 +9027,8 @@
       <c r="W74" s="25"/>
     </row>
     <row r="75" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="1">
-        <v>74</v>
+      <c r="A75" s="1" t="s">
+        <v>823</v>
       </c>
       <c r="B75" s="48" t="s">
         <v>45</v>
@@ -8680,8 +9097,8 @@
       <c r="W75" s="25"/>
     </row>
     <row r="76" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="1">
-        <v>75</v>
+      <c r="A76" s="1" t="s">
+        <v>824</v>
       </c>
       <c r="B76" s="49" t="s">
         <v>45</v>
@@ -8750,8 +9167,8 @@
       <c r="W76" s="25"/>
     </row>
     <row r="77" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="1">
-        <v>76</v>
+      <c r="A77" s="1" t="s">
+        <v>825</v>
       </c>
       <c r="B77" s="48" t="s">
         <v>45</v>
@@ -8820,8 +9237,8 @@
       <c r="W77" s="25"/>
     </row>
     <row r="78" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="1">
-        <v>77</v>
+      <c r="A78" s="1" t="s">
+        <v>826</v>
       </c>
       <c r="B78" s="49" t="s">
         <v>45</v>
@@ -8890,8 +9307,8 @@
       <c r="W78" s="25"/>
     </row>
     <row r="79" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="1">
-        <v>78</v>
+      <c r="A79" s="1" t="s">
+        <v>827</v>
       </c>
       <c r="B79" s="48" t="s">
         <v>45</v>
@@ -8960,8 +9377,8 @@
       <c r="W79" s="25"/>
     </row>
     <row r="80" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="1">
-        <v>79</v>
+      <c r="A80" s="1" t="s">
+        <v>828</v>
       </c>
       <c r="B80" s="49" t="s">
         <v>45</v>
@@ -9030,8 +9447,8 @@
       <c r="W80" s="25"/>
     </row>
     <row r="81" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="1">
-        <v>80</v>
+      <c r="A81" s="1" t="s">
+        <v>829</v>
       </c>
       <c r="B81" s="48" t="s">
         <v>45</v>
@@ -9100,8 +9517,8 @@
       <c r="W81" s="25"/>
     </row>
     <row r="82" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="1">
-        <v>81</v>
+      <c r="A82" s="1" t="s">
+        <v>830</v>
       </c>
       <c r="B82" s="49" t="s">
         <v>45</v>
@@ -9170,8 +9587,8 @@
       <c r="W82" s="25"/>
     </row>
     <row r="83" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="1">
-        <v>82</v>
+      <c r="A83" s="1" t="s">
+        <v>831</v>
       </c>
       <c r="B83" s="48" t="s">
         <v>45</v>
@@ -9238,8 +9655,8 @@
       <c r="W83" s="25"/>
     </row>
     <row r="84" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="1">
-        <v>83</v>
+      <c r="A84" s="1" t="s">
+        <v>832</v>
       </c>
       <c r="B84" s="49" t="s">
         <v>45</v>
@@ -9308,8 +9725,8 @@
       <c r="W84" s="25"/>
     </row>
     <row r="85" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="1">
-        <v>84</v>
+      <c r="A85" s="1" t="s">
+        <v>833</v>
       </c>
       <c r="B85" s="48" t="s">
         <v>45</v>
@@ -9378,8 +9795,8 @@
       <c r="W85" s="25"/>
     </row>
     <row r="86" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="1">
-        <v>85</v>
+      <c r="A86" s="1" t="s">
+        <v>834</v>
       </c>
       <c r="B86" s="49" t="s">
         <v>45</v>
@@ -9448,8 +9865,8 @@
       <c r="W86" s="25"/>
     </row>
     <row r="87" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="1">
-        <v>86</v>
+      <c r="A87" s="1" t="s">
+        <v>835</v>
       </c>
       <c r="B87" s="48" t="s">
         <v>45</v>
@@ -9518,8 +9935,8 @@
       <c r="W87" s="25"/>
     </row>
     <row r="88" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="1">
-        <v>87</v>
+      <c r="A88" s="1" t="s">
+        <v>836</v>
       </c>
       <c r="B88" s="49" t="s">
         <v>45</v>
@@ -9588,8 +10005,8 @@
       <c r="W88" s="25"/>
     </row>
     <row r="89" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="1">
-        <v>88</v>
+      <c r="A89" s="1" t="s">
+        <v>837</v>
       </c>
       <c r="B89" s="48" t="s">
         <v>45</v>
@@ -9658,8 +10075,8 @@
       <c r="W89" s="25"/>
     </row>
     <row r="90" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="1">
-        <v>89</v>
+      <c r="A90" s="1" t="s">
+        <v>838</v>
       </c>
       <c r="B90" s="49" t="s">
         <v>45</v>
@@ -9728,8 +10145,8 @@
       <c r="W90" s="25"/>
     </row>
     <row r="91" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="1">
-        <v>90</v>
+      <c r="A91" s="1" t="s">
+        <v>839</v>
       </c>
       <c r="B91" s="48" t="s">
         <v>45</v>
@@ -9798,8 +10215,8 @@
       <c r="W91" s="25"/>
     </row>
     <row r="92" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="1">
-        <v>91</v>
+      <c r="A92" s="1" t="s">
+        <v>840</v>
       </c>
       <c r="B92" s="49" t="s">
         <v>45</v>
@@ -9868,8 +10285,8 @@
       <c r="W92" s="25"/>
     </row>
     <row r="93" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="1">
-        <v>92</v>
+      <c r="A93" s="1" t="s">
+        <v>841</v>
       </c>
       <c r="B93" s="48" t="s">
         <v>45</v>
@@ -9938,8 +10355,8 @@
       <c r="W93" s="25"/>
     </row>
     <row r="94" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="1">
-        <v>93</v>
+      <c r="A94" s="1" t="s">
+        <v>842</v>
       </c>
       <c r="B94" s="49" t="s">
         <v>748</v>
@@ -10006,8 +10423,8 @@
       <c r="W94" s="25"/>
     </row>
     <row r="95" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="20">
-        <v>94</v>
+      <c r="A95" s="20" t="s">
+        <v>843</v>
       </c>
       <c r="B95" s="50" t="s">
         <v>748</v>
@@ -10074,8 +10491,8 @@
       <c r="W95" s="25"/>
     </row>
     <row r="96" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="20">
-        <v>95</v>
+      <c r="A96" s="20" t="s">
+        <v>844</v>
       </c>
       <c r="B96" s="56" t="s">
         <v>748</v>
@@ -10142,8 +10559,8 @@
       <c r="W96" s="25"/>
     </row>
     <row r="97" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="20">
-        <v>96</v>
+      <c r="A97" s="20" t="s">
+        <v>845</v>
       </c>
       <c r="B97" s="50" t="s">
         <v>748</v>
@@ -10210,8 +10627,8 @@
       <c r="W97" s="25"/>
     </row>
     <row r="98" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="20">
-        <v>97</v>
+      <c r="A98" s="20" t="s">
+        <v>846</v>
       </c>
       <c r="B98" s="56" t="s">
         <v>748</v>
@@ -10278,8 +10695,8 @@
       <c r="W98" s="25"/>
     </row>
     <row r="99" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="20">
-        <v>98</v>
+      <c r="A99" s="20" t="s">
+        <v>847</v>
       </c>
       <c r="B99" s="50" t="s">
         <v>748</v>
@@ -10346,8 +10763,8 @@
       <c r="W99" s="25"/>
     </row>
     <row r="100" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="20">
-        <v>99</v>
+      <c r="A100" s="20" t="s">
+        <v>848</v>
       </c>
       <c r="B100" s="56" t="s">
         <v>748</v>
@@ -10414,8 +10831,8 @@
       <c r="W100" s="25"/>
     </row>
     <row r="101" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="20">
-        <v>100</v>
+      <c r="A101" s="20" t="s">
+        <v>849</v>
       </c>
       <c r="B101" s="50" t="s">
         <v>748</v>
@@ -10482,8 +10899,8 @@
       <c r="W101" s="25"/>
     </row>
     <row r="102" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="20">
-        <v>101</v>
+      <c r="A102" s="20" t="s">
+        <v>850</v>
       </c>
       <c r="B102" s="56" t="s">
         <v>748</v>
@@ -10550,8 +10967,8 @@
       <c r="W102" s="25"/>
     </row>
     <row r="103" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="20">
-        <v>102</v>
+      <c r="A103" s="20" t="s">
+        <v>851</v>
       </c>
       <c r="B103" s="50" t="s">
         <v>748</v>
@@ -10618,8 +11035,8 @@
       <c r="W103" s="25"/>
     </row>
     <row r="104" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="20">
-        <v>103</v>
+      <c r="A104" s="20" t="s">
+        <v>852</v>
       </c>
       <c r="B104" s="56" t="s">
         <v>748</v>
@@ -10686,8 +11103,8 @@
       <c r="W104" s="25"/>
     </row>
     <row r="105" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="20">
-        <v>104</v>
+      <c r="A105" s="20" t="s">
+        <v>853</v>
       </c>
       <c r="B105" s="50" t="s">
         <v>748</v>
@@ -10754,8 +11171,8 @@
       <c r="W105" s="25"/>
     </row>
     <row r="106" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="20">
-        <v>105</v>
+      <c r="A106" s="20" t="s">
+        <v>854</v>
       </c>
       <c r="B106" s="56" t="s">
         <v>748</v>
@@ -10822,8 +11239,8 @@
       <c r="W106" s="25"/>
     </row>
     <row r="107" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="20">
-        <v>106</v>
+      <c r="A107" s="20" t="s">
+        <v>855</v>
       </c>
       <c r="B107" s="50" t="s">
         <v>748</v>
@@ -10890,8 +11307,8 @@
       <c r="W107" s="25"/>
     </row>
     <row r="108" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="20">
-        <v>107</v>
+      <c r="A108" s="20" t="s">
+        <v>856</v>
       </c>
       <c r="B108" s="56" t="s">
         <v>748</v>
@@ -10958,8 +11375,8 @@
       <c r="W108" s="25"/>
     </row>
     <row r="109" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="20">
-        <v>108</v>
+      <c r="A109" s="20" t="s">
+        <v>857</v>
       </c>
       <c r="B109" s="50" t="s">
         <v>748</v>
@@ -11026,8 +11443,8 @@
       <c r="W109" s="25"/>
     </row>
     <row r="110" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="20">
-        <v>109</v>
+      <c r="A110" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="B110" s="56" t="s">
         <v>748</v>
@@ -11094,8 +11511,8 @@
       <c r="W110" s="25"/>
     </row>
     <row r="111" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="20">
-        <v>110</v>
+      <c r="A111" s="20" t="s">
+        <v>859</v>
       </c>
       <c r="B111" s="50" t="s">
         <v>748</v>
@@ -11162,8 +11579,8 @@
       <c r="W111" s="25"/>
     </row>
     <row r="112" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="20">
-        <v>111</v>
+      <c r="A112" s="20" t="s">
+        <v>860</v>
       </c>
       <c r="B112" s="56" t="s">
         <v>748</v>
@@ -11230,8 +11647,8 @@
       <c r="W112" s="25"/>
     </row>
     <row r="113" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="20">
-        <v>112</v>
+      <c r="A113" s="20" t="s">
+        <v>861</v>
       </c>
       <c r="B113" s="50" t="s">
         <v>748</v>
@@ -11298,8 +11715,8 @@
       <c r="W113" s="25"/>
     </row>
     <row r="114" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="20">
-        <v>113</v>
+      <c r="A114" s="20" t="s">
+        <v>862</v>
       </c>
       <c r="B114" s="56" t="s">
         <v>748</v>
@@ -11366,8 +11783,8 @@
       <c r="W114" s="25"/>
     </row>
     <row r="115" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="20">
-        <v>114</v>
+      <c r="A115" s="20" t="s">
+        <v>863</v>
       </c>
       <c r="B115" s="50" t="s">
         <v>748</v>
@@ -11434,8 +11851,8 @@
       <c r="W115" s="25"/>
     </row>
     <row r="116" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="20">
-        <v>115</v>
+      <c r="A116" s="20" t="s">
+        <v>864</v>
       </c>
       <c r="B116" s="56" t="s">
         <v>748</v>
@@ -11502,8 +11919,8 @@
       <c r="W116" s="25"/>
     </row>
     <row r="117" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="20">
-        <v>116</v>
+      <c r="A117" s="20" t="s">
+        <v>865</v>
       </c>
       <c r="B117" s="50" t="s">
         <v>748</v>
@@ -11570,8 +11987,8 @@
       <c r="W117" s="25"/>
     </row>
     <row r="118" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A118" s="20">
-        <v>117</v>
+      <c r="A118" s="20" t="s">
+        <v>866</v>
       </c>
       <c r="B118" s="56" t="s">
         <v>748</v>
@@ -11638,8 +12055,8 @@
       <c r="W118" s="25"/>
     </row>
     <row r="119" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A119" s="20">
-        <v>118</v>
+      <c r="A119" s="20" t="s">
+        <v>867</v>
       </c>
       <c r="B119" s="50" t="s">
         <v>748</v>
@@ -11706,8 +12123,8 @@
       <c r="W119" s="25"/>
     </row>
     <row r="120" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A120" s="20">
-        <v>119</v>
+      <c r="A120" s="20" t="s">
+        <v>868</v>
       </c>
       <c r="B120" s="56" t="s">
         <v>748</v>
@@ -11774,8 +12191,8 @@
       <c r="W120" s="25"/>
     </row>
     <row r="121" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="20">
-        <v>120</v>
+      <c r="A121" s="20" t="s">
+        <v>869</v>
       </c>
       <c r="B121" s="55" t="s">
         <v>45</v>
@@ -11842,8 +12259,8 @@
       <c r="W121" s="25"/>
     </row>
     <row r="122" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="20">
-        <v>121</v>
+      <c r="A122" s="20" t="s">
+        <v>870</v>
       </c>
       <c r="B122" s="61" t="s">
         <v>45</v>
@@ -11909,8 +12326,8 @@
       </c>
     </row>
     <row r="123" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="20">
-        <v>122</v>
+      <c r="A123" s="20" t="s">
+        <v>871</v>
       </c>
       <c r="B123" s="55" t="s">
         <v>45</v>
@@ -11974,8 +12391,8 @@
       </c>
     </row>
     <row r="124" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="20">
-        <v>123</v>
+      <c r="A124" s="20" t="s">
+        <v>872</v>
       </c>
       <c r="B124" s="61" t="s">
         <v>45</v>
@@ -12041,8 +12458,8 @@
       </c>
     </row>
     <row r="125" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="20">
-        <v>124</v>
+      <c r="A125" s="20" t="s">
+        <v>873</v>
       </c>
       <c r="B125" s="55" t="s">
         <v>45</v>
@@ -12108,8 +12525,8 @@
       </c>
     </row>
     <row r="126" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A126" s="20">
-        <v>125</v>
+      <c r="A126" s="20" t="s">
+        <v>874</v>
       </c>
       <c r="B126" s="61" t="s">
         <v>45</v>
@@ -12163,8 +12580,8 @@
       </c>
     </row>
     <row r="127" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A127" s="20">
-        <v>126</v>
+      <c r="A127" s="20" t="s">
+        <v>875</v>
       </c>
       <c r="B127" s="55" t="s">
         <v>45</v>
@@ -12230,8 +12647,8 @@
       </c>
     </row>
     <row r="128" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="20">
-        <v>127</v>
+      <c r="A128" s="20" t="s">
+        <v>876</v>
       </c>
       <c r="B128" s="61" t="s">
         <v>45</v>
@@ -12297,8 +12714,8 @@
       </c>
     </row>
     <row r="129" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A129" s="20">
-        <v>128</v>
+      <c r="A129" s="20" t="s">
+        <v>877</v>
       </c>
       <c r="B129" s="55" t="s">
         <v>45</v>
@@ -12364,8 +12781,8 @@
       </c>
     </row>
     <row r="130" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A130" s="20">
-        <v>129</v>
+      <c r="A130" s="20" t="s">
+        <v>878</v>
       </c>
       <c r="B130" s="61" t="s">
         <v>45</v>
@@ -12431,8 +12848,8 @@
       </c>
     </row>
     <row r="131" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A131" s="20">
-        <v>130</v>
+      <c r="A131" s="20" t="s">
+        <v>879</v>
       </c>
       <c r="B131" s="55" t="s">
         <v>45</v>
@@ -12498,8 +12915,8 @@
       </c>
     </row>
     <row r="132" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="20">
-        <v>131</v>
+      <c r="A132" s="20" t="s">
+        <v>880</v>
       </c>
       <c r="B132" s="61" t="s">
         <v>45</v>
@@ -12565,8 +12982,8 @@
       </c>
     </row>
     <row r="133" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A133" s="20">
-        <v>132</v>
+      <c r="A133" s="20" t="s">
+        <v>881</v>
       </c>
       <c r="B133" s="55" t="s">
         <v>45</v>
@@ -12632,8 +13049,8 @@
       </c>
     </row>
     <row r="134" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A134" s="20">
-        <v>133</v>
+      <c r="A134" s="20" t="s">
+        <v>882</v>
       </c>
       <c r="B134" s="61" t="s">
         <v>45</v>
@@ -12699,8 +13116,8 @@
       </c>
     </row>
     <row r="135" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A135" s="20">
-        <v>134</v>
+      <c r="A135" s="20" t="s">
+        <v>883</v>
       </c>
       <c r="B135" s="55" t="s">
         <v>45</v>
@@ -12766,8 +13183,8 @@
       </c>
     </row>
     <row r="136" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A136" s="20">
-        <v>135</v>
+      <c r="A136" s="20" t="s">
+        <v>884</v>
       </c>
       <c r="B136" s="61" t="s">
         <v>45</v>
@@ -12833,8 +13250,8 @@
       </c>
     </row>
     <row r="137" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A137" s="20">
-        <v>136</v>
+      <c r="A137" s="20" t="s">
+        <v>885</v>
       </c>
       <c r="B137" s="55" t="s">
         <v>45</v>
@@ -12888,8 +13305,8 @@
       </c>
     </row>
     <row r="138" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A138" s="20">
-        <v>137</v>
+      <c r="A138" s="20" t="s">
+        <v>886</v>
       </c>
       <c r="B138" s="61" t="s">
         <v>45</v>
@@ -12943,8 +13360,8 @@
       </c>
     </row>
     <row r="139" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A139" s="20">
-        <v>138</v>
+      <c r="A139" s="20" t="s">
+        <v>887</v>
       </c>
       <c r="B139" s="55" t="s">
         <v>45</v>
@@ -13010,8 +13427,8 @@
       </c>
     </row>
     <row r="140" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A140" s="20">
-        <v>139</v>
+      <c r="A140" s="20" t="s">
+        <v>888</v>
       </c>
       <c r="B140" s="61" t="s">
         <v>45</v>
@@ -13105,7 +13522,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="I2:N140">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>P2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13544,7 +13961,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/US/October CMA/US October CMA Data.xlsx
+++ b/US/October CMA/US October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/US/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1809095C-331E-FA4C-B427-575B19AFBA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725D73EA-3A62-DD4A-B822-CEB06083DCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="891">
   <si>
     <t>Model</t>
   </si>
@@ -2706,6 +2706,12 @@
   </si>
   <si>
     <t>OYI76487</t>
+  </si>
+  <si>
+    <t>QVB46757</t>
+  </si>
+  <si>
+    <t>MJB56814</t>
   </si>
 </sst>
 </file>
@@ -2843,7 +2849,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2878,43 +2884,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FFD8E0E8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FFD8E0E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FFD8E0E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F4A58"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FFD8E0E8"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2985,7 +2954,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3056,31 +3025,79 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3090,19 +3107,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -3110,61 +3115,25 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -3172,7 +3141,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -3180,19 +3149,19 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -3200,7 +3169,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -3208,41 +3177,23 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3252,7 +3203,17 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{D605B4E0-7730-4D43-A011-6A0EF9292E1A}"/>
     <cellStyle name="Percent 2" xfId="4" xr:uid="{E6DE421D-B06A-DB4D-BCE7-D696BB42B3F4}"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="33">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3509,10 +3470,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Light and Airy" count="4" xr9:uid="{9857ACD9-B079-C44A-A030-69F7726DB419}">
-      <tableStyleElement type="wholeTable" dxfId="31"/>
-      <tableStyleElement type="headerRow" dxfId="30"/>
-      <tableStyleElement type="totalRow" dxfId="29"/>
-      <tableStyleElement type="firstRowStripe" dxfId="28"/>
+      <tableStyleElement type="wholeTable" dxfId="32"/>
+      <tableStyleElement type="headerRow" dxfId="31"/>
+      <tableStyleElement type="totalRow" dxfId="30"/>
+      <tableStyleElement type="firstRowStripe" dxfId="29"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3550,10 +3511,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C04EAAE0-8575-4C4D-8F7C-680B0F8FE844}" name="Table4" displayName="Table4" ref="A1:U141" totalsRowShown="0" headerRowDxfId="27" tableBorderDxfId="26">
-  <autoFilter ref="A1:U141" xr:uid="{C04EAAE0-8575-4C4D-8F7C-680B0F8FE844}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C04EAAE0-8575-4C4D-8F7C-680B0F8FE844}" name="Table4" displayName="Table4" ref="A1:U142" totalsRowShown="0" headerRowDxfId="28" tableBorderDxfId="27">
+  <autoFilter ref="A1:U142" xr:uid="{C04EAAE0-8575-4C4D-8F7C-680B0F8FE844}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C8800E54-CA52-2044-A16A-FF3249E700E8}" name="Key" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{C8800E54-CA52-2044-A16A-FF3249E700E8}" name="Key" dataDxfId="26"/>
     <tableColumn id="5" xr3:uid="{1508E423-CBEF-6F4B-9DCF-7D205ACAAA4A}" name="Class"/>
     <tableColumn id="6" xr3:uid="{AACC7F38-4163-B84F-88F9-448EEF83552D}" name="Period"/>
     <tableColumn id="7" xr3:uid="{1050C21B-C0F8-E841-8048-E0D87CBF2D06}" name="Grade"/>
@@ -3580,25 +3541,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Questions" displayName="Questions" ref="A1:Q8" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Part" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Stimulus" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Question" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Key" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Option_1" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Option_2" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Option_3" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Option_4" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Stimulus_type" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Source_type" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Task_model" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3608,7 +3569,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table1" displayName="Table1" ref="A1:B19">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Model"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Detail" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3619,7 +3580,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Standard"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Concept"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Specification" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3631,7 +3592,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{B9670A8F-2834-6A44-B0B5-70CE5D45B362}" name="Concatenated" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3862,7 +3823,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W141"/>
+  <dimension ref="A1:W142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="21" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" style="20" bestFit="1" customWidth="1"/>
@@ -3879,7 +3840,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="18" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="64" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -13494,43 +13455,155 @@
       </c>
     </row>
     <row r="141" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A141" s="71"/>
-      <c r="B141" s="64"/>
-      <c r="C141" s="65"/>
-      <c r="D141" s="65"/>
-      <c r="E141" s="66"/>
-      <c r="F141" s="67"/>
-      <c r="G141" s="68">
-        <f>AVERAGE(Scores!$G$2:$G$140)</f>
-        <v>3.5323741007194243</v>
-      </c>
-      <c r="H141" s="64"/>
-      <c r="I141" s="69"/>
-      <c r="J141" s="65"/>
-      <c r="K141" s="65"/>
-      <c r="L141" s="65"/>
-      <c r="M141" s="65"/>
-      <c r="N141" s="65"/>
-      <c r="O141" s="69"/>
-      <c r="P141" s="69"/>
-      <c r="Q141" s="65"/>
-      <c r="R141" s="65"/>
-      <c r="S141" s="65"/>
-      <c r="T141" s="65"/>
-      <c r="U141" s="65"/>
+      <c r="A141" s="20" t="s">
+        <v>889</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C141" s="20">
+        <v>4</v>
+      </c>
+      <c r="D141" s="20">
+        <v>9</v>
+      </c>
+      <c r="E141" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F141" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G141" s="20">
+        <v>3</v>
+      </c>
+      <c r="H141" s="65"/>
+      <c r="I141" s="20">
+        <v>2</v>
+      </c>
+      <c r="J141" s="20">
+        <v>1</v>
+      </c>
+      <c r="K141" s="20">
+        <v>3</v>
+      </c>
+      <c r="L141" s="20">
+        <v>3</v>
+      </c>
+      <c r="M141" s="20">
+        <v>3</v>
+      </c>
+      <c r="N141" s="20">
+        <v>2</v>
+      </c>
+      <c r="O141" s="22">
+        <v>1</v>
+      </c>
+      <c r="P141" s="46">
+        <f>IF(I141=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q141" s="43">
+        <f>IF(J141=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R141" s="43">
+        <f>IF(K141=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S141" s="43">
+        <f>IF(L141=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T141" s="43">
+        <f>IF(M141=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U141" s="43">
+        <f>IF(N141=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="20" t="s">
+        <v>890</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C142" s="20">
+        <v>4</v>
+      </c>
+      <c r="D142" s="20">
+        <v>9</v>
+      </c>
+      <c r="E142" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F142" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G142" s="20">
+        <v>1</v>
+      </c>
+      <c r="H142" s="65"/>
+      <c r="I142" s="20">
+        <v>2</v>
+      </c>
+      <c r="J142" s="20">
+        <v>4</v>
+      </c>
+      <c r="K142" s="20">
+        <v>3</v>
+      </c>
+      <c r="L142" s="20">
+        <v>1</v>
+      </c>
+      <c r="M142" s="20">
+        <v>3</v>
+      </c>
+      <c r="N142" s="20">
+        <v>3</v>
+      </c>
+      <c r="O142" s="22">
+        <v>1</v>
+      </c>
+      <c r="P142" s="46">
+        <f>IF(I142=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q142" s="43">
+        <f>IF(J142=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R142" s="43">
+        <f>IF(K142=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S142" s="43">
+        <f>IF(L142=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T142" s="43">
+        <f>IF(M142=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U142" s="43">
+        <f>IF(N142=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
-  <conditionalFormatting sqref="I2:N140">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="I2:N142">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
       <formula>P2=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B140" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B142" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Bermejo,Dushin,Klein / Cooper,Kovelsky"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H140" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H142" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -13663,8 +13736,8 @@
         <v>743</v>
       </c>
       <c r="P2" s="15">
-        <f t="array" ref="P2">AVERAGE(INDEX(Scores!$B$2:$U$140,0,MATCH("Q"&amp;$A2,Scores!$B$1:$U$1,0)))</f>
-        <v>0.52517985611510787</v>
+        <f t="array" ref="P2">AVERAGE(INDEX(Scores!$B$2:$U$142,0,MATCH("Q"&amp;$A2,Scores!$B$1:$U$1,0)))</f>
+        <v>0.51773049645390068</v>
       </c>
       <c r="Q2" s="13"/>
     </row>
@@ -13715,8 +13788,8 @@
         <v>743</v>
       </c>
       <c r="P3" s="15">
-        <f t="array" ref="P3">AVERAGE(INDEX(Scores!$B$2:$U$140,0,MATCH("Q"&amp;$A3,Scores!$B$1:$U$1,0)))</f>
-        <v>0.49640287769784175</v>
+        <f t="array" ref="P3">AVERAGE(INDEX(Scores!$B$2:$U$142,0,MATCH("Q"&amp;$A3,Scores!$B$1:$U$1,0)))</f>
+        <v>0.49645390070921985</v>
       </c>
       <c r="Q3" s="13"/>
     </row>
@@ -13767,8 +13840,8 @@
         <v>745</v>
       </c>
       <c r="P4" s="15">
-        <f t="array" ref="P4">AVERAGE(INDEX(Scores!$B$2:$U$140,0,MATCH("Q"&amp;$A4,Scores!$B$1:$U$1,0)))</f>
-        <v>0.79856115107913672</v>
+        <f t="array" ref="P4">AVERAGE(INDEX(Scores!$B$2:$U$142,0,MATCH("Q"&amp;$A4,Scores!$B$1:$U$1,0)))</f>
+        <v>0.8014184397163121</v>
       </c>
       <c r="Q4" s="13"/>
     </row>
@@ -13819,8 +13892,8 @@
         <v>745</v>
       </c>
       <c r="P5" s="15">
-        <f t="array" ref="P5">AVERAGE(INDEX(Scores!$B$2:$U$140,0,MATCH("Q"&amp;$A5,Scores!$B$1:$U$1,0)))</f>
-        <v>0.73381294964028776</v>
+        <f t="array" ref="P5">AVERAGE(INDEX(Scores!$B$2:$U$142,0,MATCH("Q"&amp;$A5,Scores!$B$1:$U$1,0)))</f>
+        <v>0.72340425531914898</v>
       </c>
       <c r="Q5" s="13"/>
     </row>
@@ -13871,8 +13944,8 @@
         <v>746</v>
       </c>
       <c r="P6" s="15">
-        <f t="array" ref="P6">AVERAGE(INDEX(Scores!$B$2:$U$140,0,MATCH("Q"&amp;$A6,Scores!$B$1:$U$1,0)))</f>
-        <v>0.34532374100719426</v>
+        <f t="array" ref="P6">AVERAGE(INDEX(Scores!$B$2:$U$142,0,MATCH("Q"&amp;$A6,Scores!$B$1:$U$1,0)))</f>
+        <v>0.3546099290780142</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
@@ -13923,8 +13996,8 @@
         <v>746</v>
       </c>
       <c r="P7" s="15">
-        <f t="array" ref="P7">AVERAGE(INDEX(Scores!$B$2:$U$140,0,MATCH("Q"&amp;$A7,Scores!$B$1:$U$1,0)))</f>
-        <v>0.67625899280575541</v>
+        <f t="array" ref="P7">AVERAGE(INDEX(Scores!$B$2:$U$142,0,MATCH("Q"&amp;$A7,Scores!$B$1:$U$1,0)))</f>
+        <v>0.67375886524822692</v>
       </c>
       <c r="Q7" s="13"/>
     </row>
@@ -13961,7 +14034,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:I8">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>"Option_"&amp;$E2=F$1</formula>
     </cfRule>
   </conditionalFormatting>
